--- a/output/2025-08-22.xlsx
+++ b/output/2025-08-22.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="F14" t="n">
-        <v>7.01</v>
+        <v>7.72</v>
       </c>
       <c r="G14" t="n">
-        <v>167</v>
+        <v>168.4</v>
       </c>
       <c r="H14" t="n">
-        <v>90.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.07</v>
+        <v>74.27</v>
       </c>
       <c r="K14" t="n">
-        <v>-88.06</v>
+        <v>-52.64</v>
       </c>
       <c r="L14" t="n">
-        <v>88.09</v>
+        <v>91.03</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:01:29</t>
+          <t>06:00:52</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.55</v>
+        <v>1.81</v>
       </c>
       <c r="F15" t="n">
-        <v>7.45</v>
+        <v>7.64</v>
       </c>
       <c r="G15" t="n">
-        <v>156.4</v>
+        <v>160.8</v>
       </c>
       <c r="H15" t="n">
-        <v>88.5</v>
+        <v>90.5</v>
       </c>
       <c r="I15" t="n">
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-18.32</v>
+        <v>-161.5</v>
       </c>
       <c r="K15" t="n">
-        <v>-100.88</v>
+        <v>-11.8</v>
       </c>
       <c r="L15" t="n">
-        <v>102.53</v>
+        <v>161.93</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:03:10</t>
+          <t>06:03:27</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.78</v>
+        <v>1.51</v>
       </c>
       <c r="F16" t="n">
-        <v>8.15</v>
+        <v>7.43</v>
       </c>
       <c r="G16" t="n">
-        <v>167.2</v>
+        <v>171.8</v>
       </c>
       <c r="H16" t="n">
-        <v>78.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-39.89</v>
+        <v>-104.77</v>
       </c>
       <c r="K16" t="n">
-        <v>135.09</v>
+        <v>-24.31</v>
       </c>
       <c r="L16" t="n">
-        <v>140.86</v>
+        <v>107.56</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:08:23</t>
+          <t>06:06:49</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="F17" t="n">
-        <v>7.51</v>
+        <v>7.96</v>
       </c>
       <c r="G17" t="n">
-        <v>161</v>
+        <v>171.3</v>
       </c>
       <c r="H17" t="n">
-        <v>92.3</v>
+        <v>91.5</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>-94.29000000000001</v>
+        <v>183.19</v>
       </c>
       <c r="K17" t="n">
-        <v>-164.36</v>
+        <v>201.96</v>
       </c>
       <c r="L17" t="n">
-        <v>189.49</v>
+        <v>272.66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:10:30</t>
+          <t>06:08:25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="F18" t="n">
-        <v>7.5</v>
+        <v>7.53</v>
       </c>
       <c r="G18" t="n">
-        <v>166.9</v>
+        <v>165.8</v>
       </c>
       <c r="H18" t="n">
-        <v>84.40000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="I18" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-25.2</v>
+        <v>-143.4</v>
       </c>
       <c r="K18" t="n">
-        <v>173.8</v>
+        <v>1.2</v>
       </c>
       <c r="L18" t="n">
-        <v>175.61</v>
+        <v>143.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:11:31</t>
+          <t>06:10:31</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.64</v>
+        <v>2.01</v>
       </c>
       <c r="F19" t="n">
-        <v>7.77</v>
+        <v>7.23</v>
       </c>
       <c r="G19" t="n">
-        <v>178.1</v>
+        <v>150.3</v>
       </c>
       <c r="H19" t="n">
-        <v>85.90000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="I19" t="n">
         <v>17</v>
       </c>
       <c r="J19" t="n">
-        <v>3.44</v>
+        <v>83.41</v>
       </c>
       <c r="K19" t="n">
-        <v>-18.41</v>
+        <v>-94.03</v>
       </c>
       <c r="L19" t="n">
-        <v>18.73</v>
+        <v>125.69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:14:16</t>
+          <t>06:15:48</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="F20" t="n">
-        <v>7.26</v>
+        <v>7.82</v>
       </c>
       <c r="G20" t="n">
-        <v>156.4</v>
+        <v>155.3</v>
       </c>
       <c r="H20" t="n">
-        <v>92.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="I20" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.53</v>
+        <v>-33.73</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.52</v>
+        <v>-67.58</v>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>75.53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:16:11</t>
+          <t>06:18:04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="F21" t="n">
-        <v>7.27</v>
+        <v>7.28</v>
       </c>
       <c r="G21" t="n">
-        <v>168.2</v>
+        <v>157.1</v>
       </c>
       <c r="H21" t="n">
-        <v>79</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>-70.15000000000001</v>
+        <v>-160.24</v>
       </c>
       <c r="K21" t="n">
-        <v>178.24</v>
+        <v>-190.19</v>
       </c>
       <c r="L21" t="n">
-        <v>191.54</v>
+        <v>248.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:18:27</t>
+          <t>06:19:33</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="F22" t="n">
-        <v>8.449999999999999</v>
+        <v>7.61</v>
       </c>
       <c r="G22" t="n">
-        <v>157</v>
+        <v>158.9</v>
       </c>
       <c r="H22" t="n">
-        <v>85</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.08</v>
+        <v>277.92</v>
       </c>
       <c r="K22" t="n">
-        <v>-395.72</v>
+        <v>-45.56</v>
       </c>
       <c r="L22" t="n">
-        <v>395.73</v>
+        <v>281.63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:23:04</t>
+          <t>06:24:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="F23" t="n">
-        <v>7.12</v>
+        <v>7.86</v>
       </c>
       <c r="G23" t="n">
-        <v>162.3</v>
+        <v>165.6</v>
       </c>
       <c r="H23" t="n">
-        <v>89.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-67.56</v>
+        <v>-565.3200000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-101.46</v>
+        <v>15.07</v>
       </c>
       <c r="L23" t="n">
-        <v>121.89</v>
+        <v>565.52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:24:47</t>
+          <t>06:25:56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="F24" t="n">
-        <v>7.2</v>
+        <v>7.03</v>
       </c>
       <c r="G24" t="n">
-        <v>165.5</v>
+        <v>156.4</v>
       </c>
       <c r="H24" t="n">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>157.2</v>
+        <v>548.75</v>
       </c>
       <c r="K24" t="n">
-        <v>-44.67</v>
+        <v>-335.25</v>
       </c>
       <c r="L24" t="n">
-        <v>163.42</v>
+        <v>643.0599999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:27:02</t>
+          <t>06:28:19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="F25" t="n">
-        <v>7.46</v>
+        <v>7.35</v>
       </c>
       <c r="G25" t="n">
-        <v>164.2</v>
+        <v>174.4</v>
       </c>
       <c r="H25" t="n">
-        <v>83.40000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J25" t="n">
-        <v>155.14</v>
+        <v>-105.11</v>
       </c>
       <c r="K25" t="n">
-        <v>206.9</v>
+        <v>-42.14</v>
       </c>
       <c r="L25" t="n">
-        <v>258.6</v>
+        <v>113.25</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:32:26</t>
+          <t>06:34:14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.55</v>
+        <v>1.79</v>
       </c>
       <c r="F26" t="n">
-        <v>7.26</v>
+        <v>7.13</v>
       </c>
       <c r="G26" t="n">
-        <v>166.5</v>
+        <v>156.3</v>
       </c>
       <c r="H26" t="n">
-        <v>89.2</v>
+        <v>89.3</v>
       </c>
       <c r="I26" t="n">
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>11.88</v>
+        <v>113.41</v>
       </c>
       <c r="K26" t="n">
-        <v>74.08</v>
+        <v>11.82</v>
       </c>
       <c r="L26" t="n">
-        <v>75.03</v>
+        <v>114.03</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:34:25</t>
+          <t>06:36:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.26</v>
+        <v>2.05</v>
       </c>
       <c r="F27" t="n">
-        <v>7.53</v>
+        <v>6.89</v>
       </c>
       <c r="G27" t="n">
-        <v>157.2</v>
+        <v>160.4</v>
       </c>
       <c r="H27" t="n">
-        <v>88.3</v>
+        <v>87</v>
       </c>
       <c r="I27" t="n">
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>214</v>
+        <v>505.65</v>
       </c>
       <c r="K27" t="n">
-        <v>-203.35</v>
+        <v>-229.93</v>
       </c>
       <c r="L27" t="n">
-        <v>295.21</v>
+        <v>555.48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:36:43</t>
+          <t>06:37:27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="F28" t="n">
-        <v>8.19</v>
+        <v>7.55</v>
       </c>
       <c r="G28" t="n">
-        <v>171.2</v>
+        <v>159.6</v>
       </c>
       <c r="H28" t="n">
-        <v>90.3</v>
+        <v>90.5</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>443.24</v>
+        <v>201.44</v>
       </c>
       <c r="K28" t="n">
-        <v>-329.24</v>
+        <v>49.47</v>
       </c>
       <c r="L28" t="n">
-        <v>552.14</v>
+        <v>207.42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:43:12</t>
+          <t>06:47:16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="F29" t="n">
-        <v>6.92</v>
+        <v>7.52</v>
       </c>
       <c r="G29" t="n">
-        <v>157</v>
+        <v>157.5</v>
       </c>
       <c r="H29" t="n">
-        <v>81.7</v>
+        <v>90.8</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-36.85</v>
       </c>
       <c r="K29" t="n">
-        <v>-106.37</v>
+        <v>112.03</v>
       </c>
       <c r="L29" t="n">
-        <v>106.37</v>
+        <v>117.94</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:45:10</t>
+          <t>06:48:30</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.46</v>
+        <v>1.47</v>
       </c>
       <c r="F30" t="n">
-        <v>7.5</v>
+        <v>7.45</v>
       </c>
       <c r="G30" t="n">
-        <v>166.7</v>
+        <v>169.5</v>
       </c>
       <c r="H30" t="n">
-        <v>81.59999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-25.64</v>
+        <v>-7.98</v>
       </c>
       <c r="K30" t="n">
-        <v>132.99</v>
+        <v>16.5</v>
       </c>
       <c r="L30" t="n">
-        <v>135.44</v>
+        <v>18.32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:45:57</t>
+          <t>06:49:39</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="F31" t="n">
-        <v>7.17</v>
+        <v>7.72</v>
       </c>
       <c r="G31" t="n">
-        <v>155.8</v>
+        <v>163.7</v>
       </c>
       <c r="H31" t="n">
-        <v>87.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>39.49</v>
+        <v>-90.22</v>
       </c>
       <c r="K31" t="n">
-        <v>-162.43</v>
+        <v>47.18</v>
       </c>
       <c r="L31" t="n">
-        <v>167.16</v>
+        <v>101.81</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:50:56</t>
+          <t>06:54:57</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.23</v>
+        <v>1.74</v>
       </c>
       <c r="F32" t="n">
-        <v>6.9</v>
+        <v>7.63</v>
       </c>
       <c r="G32" t="n">
-        <v>160.6</v>
+        <v>161.9</v>
       </c>
       <c r="H32" t="n">
-        <v>91.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>-140.08</v>
+        <v>157.68</v>
       </c>
       <c r="K32" t="n">
-        <v>-53.19</v>
+        <v>-169.51</v>
       </c>
       <c r="L32" t="n">
-        <v>149.84</v>
+        <v>231.51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:51:55</t>
+          <t>06:57:19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="F33" t="n">
-        <v>7.62</v>
+        <v>7.46</v>
       </c>
       <c r="G33" t="n">
-        <v>157.1</v>
+        <v>167.7</v>
       </c>
       <c r="H33" t="n">
-        <v>88.59999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>74.06999999999999</v>
+        <v>66.81</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.11</v>
+        <v>108.17</v>
       </c>
       <c r="L33" t="n">
-        <v>74.23999999999999</v>
+        <v>127.14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:53:38</t>
+          <t>06:58:24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="F34" t="n">
-        <v>7.86</v>
+        <v>6.95</v>
       </c>
       <c r="G34" t="n">
-        <v>148.9</v>
+        <v>144.5</v>
       </c>
       <c r="H34" t="n">
-        <v>83</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>23.94</v>
+        <v>112.58</v>
       </c>
       <c r="K34" t="n">
-        <v>-54.65</v>
+        <v>-64.26000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>59.66</v>
+        <v>129.63</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>06:57:41</t>
+          <t>07:03:01</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="F35" t="n">
-        <v>7.52</v>
+        <v>7.45</v>
       </c>
       <c r="G35" t="n">
-        <v>165.2</v>
+        <v>156</v>
       </c>
       <c r="H35" t="n">
-        <v>83.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>132.15</v>
+        <v>-34.34</v>
       </c>
       <c r="K35" t="n">
-        <v>-218.98</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>255.77</v>
+        <v>82.48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>06:59:25</t>
+          <t>07:05:20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="F36" t="n">
-        <v>7.36</v>
+        <v>7</v>
       </c>
       <c r="G36" t="n">
-        <v>155.7</v>
+        <v>152.9</v>
       </c>
       <c r="H36" t="n">
-        <v>80.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I36" t="n">
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-164.79</v>
+        <v>-199.48</v>
       </c>
       <c r="K36" t="n">
-        <v>166.67</v>
+        <v>10.25</v>
       </c>
       <c r="L36" t="n">
-        <v>234.38</v>
+        <v>199.74</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:01:14</t>
+          <t>07:06:28</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="F37" t="n">
-        <v>7.14</v>
+        <v>7.92</v>
       </c>
       <c r="G37" t="n">
-        <v>153.5</v>
+        <v>155.4</v>
       </c>
       <c r="H37" t="n">
-        <v>95.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="I37" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>-138.87</v>
+        <v>15.67</v>
       </c>
       <c r="K37" t="n">
-        <v>50.41</v>
+        <v>387.71</v>
       </c>
       <c r="L37" t="n">
-        <v>147.74</v>
+        <v>388.03</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:05:44</t>
+          <t>07:10:50</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="F38" t="n">
-        <v>7.95</v>
+        <v>7.45</v>
       </c>
       <c r="G38" t="n">
-        <v>157.5</v>
+        <v>158.5</v>
       </c>
       <c r="H38" t="n">
-        <v>82.7</v>
+        <v>86.3</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>232.35</v>
+        <v>-81.22</v>
       </c>
       <c r="K38" t="n">
-        <v>60.94</v>
+        <v>-80.11</v>
       </c>
       <c r="L38" t="n">
-        <v>240.21</v>
+        <v>114.08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:07:02</t>
+          <t>07:13:01</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="F39" t="n">
-        <v>7.38</v>
+        <v>7.45</v>
       </c>
       <c r="G39" t="n">
-        <v>170.1</v>
+        <v>162.6</v>
       </c>
       <c r="H39" t="n">
-        <v>93.09999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>320.04</v>
+        <v>-166.27</v>
       </c>
       <c r="K39" t="n">
-        <v>-132.63</v>
+        <v>-150.54</v>
       </c>
       <c r="L39" t="n">
-        <v>346.44</v>
+        <v>224.29</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:07:48</t>
+          <t>07:14:06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.48</v>
+        <v>1.51</v>
       </c>
       <c r="F40" t="n">
-        <v>7.25</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>162.9</v>
+        <v>172.6</v>
       </c>
       <c r="H40" t="n">
-        <v>91</v>
+        <v>89.3</v>
       </c>
       <c r="I40" t="n">
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-255.01</v>
+        <v>-133.37</v>
       </c>
       <c r="K40" t="n">
-        <v>113.27</v>
+        <v>-350.63</v>
       </c>
       <c r="L40" t="n">
-        <v>279.04</v>
+        <v>375.14</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:13:21</t>
+          <t>07:18:04</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.8</v>
+        <v>1.61</v>
       </c>
       <c r="F41" t="n">
-        <v>7.63</v>
+        <v>7.86</v>
       </c>
       <c r="G41" t="n">
-        <v>155.1</v>
+        <v>161.3</v>
       </c>
       <c r="H41" t="n">
-        <v>83</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I41" t="n">
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>-348.8</v>
+        <v>47.05</v>
       </c>
       <c r="K41" t="n">
-        <v>-207.06</v>
+        <v>548.61</v>
       </c>
       <c r="L41" t="n">
-        <v>405.63</v>
+        <v>550.63</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:15:27</t>
+          <t>07:19:20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.97</v>
+        <v>1.44</v>
       </c>
       <c r="F42" t="n">
-        <v>7.18</v>
+        <v>7.89</v>
       </c>
       <c r="G42" t="n">
-        <v>176.3</v>
+        <v>172.1</v>
       </c>
       <c r="H42" t="n">
-        <v>81.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-114.7</v>
+        <v>3.48</v>
       </c>
       <c r="K42" t="n">
-        <v>-240.79</v>
+        <v>-460.9</v>
       </c>
       <c r="L42" t="n">
-        <v>266.71</v>
+        <v>460.91</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:17:46</t>
+          <t>07:21:53</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="F43" t="n">
-        <v>6.67</v>
+        <v>7.33</v>
       </c>
       <c r="G43" t="n">
-        <v>165.1</v>
+        <v>174.7</v>
       </c>
       <c r="H43" t="n">
-        <v>85.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>-179.65</v>
+        <v>87.7</v>
       </c>
       <c r="K43" t="n">
-        <v>-791.17</v>
+        <v>-443.89</v>
       </c>
       <c r="L43" t="n">
-        <v>811.3099999999999</v>
+        <v>452.47</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:26:29</t>
+          <t>07:32:11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="F44" t="n">
-        <v>8.01</v>
+        <v>7.07</v>
       </c>
       <c r="G44" t="n">
-        <v>149.8</v>
+        <v>153.7</v>
       </c>
       <c r="H44" t="n">
-        <v>86.09999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-21.12</v>
+        <v>-69.15000000000001</v>
       </c>
       <c r="K44" t="n">
-        <v>27.32</v>
+        <v>98.11</v>
       </c>
       <c r="L44" t="n">
-        <v>34.53</v>
+        <v>120.03</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:28:50</t>
+          <t>07:34:36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.91</v>
+        <v>1.31</v>
       </c>
       <c r="F45" t="n">
-        <v>7.2</v>
+        <v>7.36</v>
       </c>
       <c r="G45" t="n">
-        <v>165.6</v>
+        <v>160.1</v>
       </c>
       <c r="H45" t="n">
-        <v>88.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>-98.54000000000001</v>
+        <v>52.65</v>
       </c>
       <c r="K45" t="n">
-        <v>-12.97</v>
+        <v>44.6</v>
       </c>
       <c r="L45" t="n">
-        <v>99.39</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:30:10</t>
+          <t>07:36:31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.26</v>
+        <v>1.76</v>
       </c>
       <c r="F46" t="n">
-        <v>8.210000000000001</v>
+        <v>7.29</v>
       </c>
       <c r="G46" t="n">
-        <v>165.3</v>
+        <v>156.7</v>
       </c>
       <c r="H46" t="n">
-        <v>91.8</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I46" t="n">
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-38.66</v>
+        <v>-42.95</v>
       </c>
       <c r="K46" t="n">
-        <v>35.35</v>
+        <v>29.45</v>
       </c>
       <c r="L46" t="n">
-        <v>52.39</v>
+        <v>52.08</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:33:02</t>
+          <t>07:40:51</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.81</v>
+        <v>2.51</v>
       </c>
       <c r="F47" t="n">
-        <v>8.06</v>
+        <v>7.71</v>
       </c>
       <c r="G47" t="n">
-        <v>141.4</v>
+        <v>162.6</v>
       </c>
       <c r="H47" t="n">
-        <v>91</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>91.14</v>
+        <v>130.85</v>
       </c>
       <c r="K47" t="n">
-        <v>4.44</v>
+        <v>4.48</v>
       </c>
       <c r="L47" t="n">
-        <v>91.25</v>
+        <v>130.92</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:34:13</t>
+          <t>07:41:58</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.13</v>
+        <v>1.6</v>
       </c>
       <c r="F48" t="n">
-        <v>7.46</v>
+        <v>7.77</v>
       </c>
       <c r="G48" t="n">
-        <v>153.1</v>
+        <v>153</v>
       </c>
       <c r="H48" t="n">
-        <v>87.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="I48" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-62.08</v>
+        <v>-22.09</v>
       </c>
       <c r="K48" t="n">
-        <v>66.34</v>
+        <v>124.55</v>
       </c>
       <c r="L48" t="n">
-        <v>90.84999999999999</v>
+        <v>126.49</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:35:22</t>
+          <t>07:43:13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="F49" t="n">
-        <v>8.23</v>
+        <v>7.21</v>
       </c>
       <c r="G49" t="n">
-        <v>164.3</v>
+        <v>148.8</v>
       </c>
       <c r="H49" t="n">
-        <v>86.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>76.03</v>
+        <v>-202.28</v>
       </c>
       <c r="K49" t="n">
-        <v>-161.1</v>
+        <v>-164.9</v>
       </c>
       <c r="L49" t="n">
-        <v>178.14</v>
+        <v>260.98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:41:41</t>
+          <t>07:46:56</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="F50" t="n">
-        <v>6.9</v>
+        <v>7.42</v>
       </c>
       <c r="G50" t="n">
-        <v>154</v>
+        <v>157.1</v>
       </c>
       <c r="H50" t="n">
-        <v>98.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="I50" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>148.99</v>
+        <v>-90.81999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-153.27</v>
+        <v>-19.58</v>
       </c>
       <c r="L50" t="n">
-        <v>213.75</v>
+        <v>92.91</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:42:11</t>
+          <t>07:48:21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.19</v>
+        <v>1.89</v>
       </c>
       <c r="F51" t="n">
-        <v>7.52</v>
+        <v>7.6</v>
       </c>
       <c r="G51" t="n">
-        <v>173.3</v>
+        <v>142</v>
       </c>
       <c r="H51" t="n">
-        <v>87.59999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I51" t="n">
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>-23.87</v>
+        <v>107.54</v>
       </c>
       <c r="K51" t="n">
-        <v>146.96</v>
+        <v>19.6</v>
       </c>
       <c r="L51" t="n">
-        <v>148.89</v>
+        <v>109.31</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:44:15</t>
+          <t>07:50:22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.37</v>
+        <v>2.12</v>
       </c>
       <c r="F52" t="n">
-        <v>6.91</v>
+        <v>7.13</v>
       </c>
       <c r="G52" t="n">
-        <v>150.4</v>
+        <v>167.4</v>
       </c>
       <c r="H52" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>-76.34</v>
+        <v>124.75</v>
       </c>
       <c r="K52" t="n">
-        <v>32.2</v>
+        <v>-40.27</v>
       </c>
       <c r="L52" t="n">
-        <v>82.84999999999999</v>
+        <v>131.09</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:49:15</t>
+          <t>07:56:09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.01</v>
+        <v>3.55</v>
       </c>
       <c r="F53" t="n">
-        <v>7.27</v>
+        <v>7.62</v>
       </c>
       <c r="G53" t="n">
-        <v>168</v>
+        <v>168.4</v>
       </c>
       <c r="H53" t="n">
-        <v>87.5</v>
+        <v>84.3</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>183.08</v>
+        <v>228.8</v>
       </c>
       <c r="K53" t="n">
-        <v>87.93000000000001</v>
+        <v>-126.89</v>
       </c>
       <c r="L53" t="n">
-        <v>203.1</v>
+        <v>261.63</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:50:38</t>
+          <t>07:57:52</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="F54" t="n">
-        <v>7.39</v>
+        <v>7.95</v>
       </c>
       <c r="G54" t="n">
-        <v>169</v>
+        <v>154.6</v>
       </c>
       <c r="H54" t="n">
-        <v>93.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I54" t="n">
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>-86.76000000000001</v>
+        <v>70.61</v>
       </c>
       <c r="K54" t="n">
-        <v>103.25</v>
+        <v>154.71</v>
       </c>
       <c r="L54" t="n">
-        <v>134.86</v>
+        <v>170.06</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:51:24</t>
+          <t>07:58:44</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="F55" t="n">
-        <v>6.99</v>
+        <v>7.23</v>
       </c>
       <c r="G55" t="n">
-        <v>155.8</v>
+        <v>152.2</v>
       </c>
       <c r="H55" t="n">
-        <v>91.09999999999999</v>
+        <v>84.7</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>46.31</v>
+        <v>-252.88</v>
       </c>
       <c r="K55" t="n">
-        <v>157.38</v>
+        <v>402.84</v>
       </c>
       <c r="L55" t="n">
-        <v>164.06</v>
+        <v>475.64</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:55:32</t>
+          <t>08:03:17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.13</v>
+        <v>1.54</v>
       </c>
       <c r="F56" t="n">
-        <v>7.18</v>
+        <v>7.08</v>
       </c>
       <c r="G56" t="n">
-        <v>169.6</v>
+        <v>153.8</v>
       </c>
       <c r="H56" t="n">
-        <v>77.7</v>
+        <v>82</v>
       </c>
       <c r="I56" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>607.01</v>
+        <v>297.06</v>
       </c>
       <c r="K56" t="n">
-        <v>-103.55</v>
+        <v>161.63</v>
       </c>
       <c r="L56" t="n">
-        <v>615.78</v>
+        <v>338.18</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:57:15</t>
+          <t>08:05:16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="F57" t="n">
-        <v>7.29</v>
+        <v>7.23</v>
       </c>
       <c r="G57" t="n">
-        <v>153.1</v>
+        <v>162.5</v>
       </c>
       <c r="H57" t="n">
-        <v>84.7</v>
+        <v>86.8</v>
       </c>
       <c r="I57" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-99.06</v>
+        <v>-184.24</v>
       </c>
       <c r="K57" t="n">
-        <v>-51.81</v>
+        <v>278.19</v>
       </c>
       <c r="L57" t="n">
-        <v>111.8</v>
+        <v>333.67</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>07:59:03</t>
+          <t>08:07:20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="F58" t="n">
-        <v>7.36</v>
+        <v>7.62</v>
       </c>
       <c r="G58" t="n">
-        <v>163.3</v>
+        <v>166.7</v>
       </c>
       <c r="H58" t="n">
-        <v>80.3</v>
+        <v>84</v>
       </c>
       <c r="I58" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>217.67</v>
+        <v>-290.48</v>
       </c>
       <c r="K58" t="n">
-        <v>41.9</v>
+        <v>-393.78</v>
       </c>
       <c r="L58" t="n">
-        <v>221.66</v>
+        <v>489.33</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:11:29</t>
+          <t>08:18:53</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.75</v>
+        <v>2.11</v>
       </c>
       <c r="F59" t="n">
-        <v>7.24</v>
+        <v>7.36</v>
       </c>
       <c r="G59" t="n">
-        <v>162.3</v>
+        <v>171.6</v>
       </c>
       <c r="H59" t="n">
-        <v>86.90000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="I59" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>8.460000000000001</v>
+        <v>-114.01</v>
       </c>
       <c r="K59" t="n">
-        <v>40.77</v>
+        <v>-60.15</v>
       </c>
       <c r="L59" t="n">
-        <v>41.63</v>
+        <v>128.91</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:13:37</t>
+          <t>08:19:38</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="F60" t="n">
-        <v>7.48</v>
+        <v>7.77</v>
       </c>
       <c r="G60" t="n">
-        <v>161.5</v>
+        <v>159.8</v>
       </c>
       <c r="H60" t="n">
-        <v>85.8</v>
+        <v>86.8</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>104.83</v>
+        <v>105.43</v>
       </c>
       <c r="K60" t="n">
-        <v>-35.93</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>110.82</v>
+        <v>130.55</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:15:35</t>
+          <t>08:20:50</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.69</v>
+        <v>2.19</v>
       </c>
       <c r="F61" t="n">
-        <v>7.7</v>
+        <v>7.22</v>
       </c>
       <c r="G61" t="n">
-        <v>165.3</v>
+        <v>160.4</v>
       </c>
       <c r="H61" t="n">
-        <v>89.3</v>
+        <v>89.8</v>
       </c>
       <c r="I61" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>93.06999999999999</v>
+        <v>37.12</v>
       </c>
       <c r="K61" t="n">
-        <v>14.26</v>
+        <v>-77.36</v>
       </c>
       <c r="L61" t="n">
-        <v>94.16</v>
+        <v>85.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:20:33</t>
+          <t>08:26:56</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.08</v>
+        <v>1.71</v>
       </c>
       <c r="F62" t="n">
-        <v>7.7</v>
+        <v>7.74</v>
       </c>
       <c r="G62" t="n">
-        <v>163.8</v>
+        <v>154.2</v>
       </c>
       <c r="H62" t="n">
-        <v>83.5</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I62" t="n">
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-38.71</v>
+        <v>-44.68</v>
       </c>
       <c r="K62" t="n">
-        <v>-168.22</v>
+        <v>49.07</v>
       </c>
       <c r="L62" t="n">
-        <v>172.62</v>
+        <v>66.36</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:22:00</t>
+          <t>08:27:34</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="F63" t="n">
-        <v>7.99</v>
+        <v>7.7</v>
       </c>
       <c r="G63" t="n">
-        <v>162.5</v>
+        <v>157.2</v>
       </c>
       <c r="H63" t="n">
-        <v>83.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="I63" t="n">
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-6.17</v>
+        <v>-122.04</v>
       </c>
       <c r="K63" t="n">
-        <v>22.9</v>
+        <v>-149.16</v>
       </c>
       <c r="L63" t="n">
-        <v>23.72</v>
+        <v>192.73</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:23:28</t>
+          <t>08:29:04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="F64" t="n">
-        <v>7.58</v>
+        <v>7.29</v>
       </c>
       <c r="G64" t="n">
-        <v>153.8</v>
+        <v>152.3</v>
       </c>
       <c r="H64" t="n">
-        <v>85.7</v>
+        <v>84</v>
       </c>
       <c r="I64" t="n">
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-89.75</v>
+        <v>-36.08</v>
       </c>
       <c r="K64" t="n">
-        <v>13.86</v>
+        <v>128.96</v>
       </c>
       <c r="L64" t="n">
-        <v>90.81</v>
+        <v>133.91</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:26:59</t>
+          <t>08:32:04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.13</v>
+        <v>1.97</v>
       </c>
       <c r="F65" t="n">
-        <v>8.18</v>
+        <v>7.01</v>
       </c>
       <c r="G65" t="n">
-        <v>163.2</v>
+        <v>168.7</v>
       </c>
       <c r="H65" t="n">
-        <v>80.09999999999999</v>
+        <v>85.3</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>53.81</v>
+        <v>-81.52</v>
       </c>
       <c r="K65" t="n">
-        <v>-164.49</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>173.06</v>
+        <v>105.72</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:28:38</t>
+          <t>08:33:03</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="F66" t="n">
-        <v>7.26</v>
+        <v>6.88</v>
       </c>
       <c r="G66" t="n">
-        <v>187.2</v>
+        <v>162.6</v>
       </c>
       <c r="H66" t="n">
-        <v>80.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I66" t="n">
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-165.75</v>
+        <v>-360.29</v>
       </c>
       <c r="K66" t="n">
-        <v>16.49</v>
+        <v>169.44</v>
       </c>
       <c r="L66" t="n">
-        <v>166.57</v>
+        <v>398.15</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:30:33</t>
+          <t>08:35:44</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="F67" t="n">
-        <v>8.24</v>
+        <v>7.19</v>
       </c>
       <c r="G67" t="n">
-        <v>155.4</v>
+        <v>164.3</v>
       </c>
       <c r="H67" t="n">
-        <v>81.3</v>
+        <v>88.2</v>
       </c>
       <c r="I67" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-63.63</v>
+        <v>-226.42</v>
       </c>
       <c r="K67" t="n">
-        <v>-335.12</v>
+        <v>-61.79</v>
       </c>
       <c r="L67" t="n">
-        <v>341.11</v>
+        <v>234.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:34:06</t>
+          <t>08:39:58</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.68</v>
+        <v>2.37</v>
       </c>
       <c r="F68" t="n">
-        <v>7.09</v>
+        <v>7.67</v>
       </c>
       <c r="G68" t="n">
-        <v>173.7</v>
+        <v>160.3</v>
       </c>
       <c r="H68" t="n">
-        <v>88.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>45.26</v>
+        <v>-373.25</v>
       </c>
       <c r="K68" t="n">
-        <v>-256.36</v>
+        <v>-271.9</v>
       </c>
       <c r="L68" t="n">
-        <v>260.32</v>
+        <v>461.78</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:35:50</t>
+          <t>08:42:04</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.29</v>
+        <v>1.46</v>
       </c>
       <c r="F69" t="n">
-        <v>7.38</v>
+        <v>7.46</v>
       </c>
       <c r="G69" t="n">
-        <v>163.1</v>
+        <v>162.4</v>
       </c>
       <c r="H69" t="n">
-        <v>86.2</v>
+        <v>91.2</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>-104.64</v>
+        <v>194.57</v>
       </c>
       <c r="K69" t="n">
-        <v>165.74</v>
+        <v>29.71</v>
       </c>
       <c r="L69" t="n">
-        <v>196</v>
+        <v>196.82</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:38:03</t>
+          <t>08:44:00</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.14</v>
+        <v>2.03</v>
       </c>
       <c r="F70" t="n">
-        <v>7.58</v>
+        <v>7.66</v>
       </c>
       <c r="G70" t="n">
-        <v>168</v>
+        <v>160.8</v>
       </c>
       <c r="H70" t="n">
-        <v>83.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="I70" t="n">
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>74.06</v>
+        <v>-334.26</v>
       </c>
       <c r="K70" t="n">
-        <v>364.33</v>
+        <v>-76.06</v>
       </c>
       <c r="L70" t="n">
-        <v>371.78</v>
+        <v>342.81</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:42:45</t>
+          <t>08:49:37</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.96</v>
+        <v>2.82</v>
       </c>
       <c r="F71" t="n">
-        <v>7.34</v>
+        <v>7.65</v>
       </c>
       <c r="G71" t="n">
-        <v>155.6</v>
+        <v>168.6</v>
       </c>
       <c r="H71" t="n">
-        <v>85.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="I71" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>193.5</v>
+        <v>-677.55</v>
       </c>
       <c r="K71" t="n">
-        <v>-28.5</v>
+        <v>646.59</v>
       </c>
       <c r="L71" t="n">
-        <v>195.59</v>
+        <v>936.5599999999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:44:48</t>
+          <t>08:50:20</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="F72" t="n">
-        <v>7.32</v>
+        <v>8.32</v>
       </c>
       <c r="G72" t="n">
-        <v>162.7</v>
+        <v>160.1</v>
       </c>
       <c r="H72" t="n">
-        <v>85.90000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>318.87</v>
+        <v>-74.58</v>
       </c>
       <c r="K72" t="n">
-        <v>195.53</v>
+        <v>-182.81</v>
       </c>
       <c r="L72" t="n">
-        <v>374.05</v>
+        <v>197.43</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:47:04</t>
+          <t>08:52:01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.92</v>
+        <v>2.28</v>
       </c>
       <c r="F73" t="n">
-        <v>7.61</v>
+        <v>7.22</v>
       </c>
       <c r="G73" t="n">
-        <v>157.7</v>
+        <v>156</v>
       </c>
       <c r="H73" t="n">
-        <v>87.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="I73" t="n">
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>28.48</v>
+        <v>363.84</v>
       </c>
       <c r="K73" t="n">
-        <v>7.64</v>
+        <v>45.87</v>
       </c>
       <c r="L73" t="n">
-        <v>29.49</v>
+        <v>366.72</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:57:31</t>
+          <t>09:03:01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3148,31 +3148,31 @@
         <v>1.91</v>
       </c>
       <c r="F74" t="n">
-        <v>8.41</v>
+        <v>7.62</v>
       </c>
       <c r="G74" t="n">
-        <v>171.6</v>
+        <v>176.3</v>
       </c>
       <c r="H74" t="n">
-        <v>90.09999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I74" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>-71.31</v>
+        <v>19.45</v>
       </c>
       <c r="K74" t="n">
-        <v>54.26</v>
+        <v>-87.18000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>89.61</v>
+        <v>89.31999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>08:59:44</t>
+          <t>09:04:19</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.29</v>
+        <v>2.07</v>
       </c>
       <c r="F75" t="n">
-        <v>7.41</v>
+        <v>7.83</v>
       </c>
       <c r="G75" t="n">
-        <v>158.1</v>
+        <v>157.4</v>
       </c>
       <c r="H75" t="n">
-        <v>84.5</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>51.83</v>
+        <v>-18.62</v>
       </c>
       <c r="K75" t="n">
-        <v>15.99</v>
+        <v>-231.62</v>
       </c>
       <c r="L75" t="n">
-        <v>54.24</v>
+        <v>232.37</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:02:05</t>
+          <t>09:05:41</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.29</v>
+        <v>3.27</v>
       </c>
       <c r="F76" t="n">
-        <v>7.37</v>
+        <v>7.94</v>
       </c>
       <c r="G76" t="n">
-        <v>138.4</v>
+        <v>161.9</v>
       </c>
       <c r="H76" t="n">
-        <v>84.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-43.36</v>
+        <v>-36.2</v>
       </c>
       <c r="K76" t="n">
-        <v>-69.68000000000001</v>
+        <v>-230.86</v>
       </c>
       <c r="L76" t="n">
-        <v>82.06999999999999</v>
+        <v>233.68</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:07:19</t>
+          <t>09:09:57</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="F77" t="n">
-        <v>7.82</v>
+        <v>7.23</v>
       </c>
       <c r="G77" t="n">
-        <v>161.5</v>
+        <v>158.6</v>
       </c>
       <c r="H77" t="n">
-        <v>81.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I77" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>42.25</v>
+        <v>240.86</v>
       </c>
       <c r="K77" t="n">
-        <v>-43.5</v>
+        <v>-424.53</v>
       </c>
       <c r="L77" t="n">
-        <v>60.64</v>
+        <v>488.1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:09:02</t>
+          <t>09:11:13</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="F78" t="n">
-        <v>7.38</v>
+        <v>7.97</v>
       </c>
       <c r="G78" t="n">
-        <v>166.1</v>
+        <v>166.2</v>
       </c>
       <c r="H78" t="n">
-        <v>85.8</v>
+        <v>84.8</v>
       </c>
       <c r="I78" t="n">
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>21.27</v>
+        <v>-86.76000000000001</v>
       </c>
       <c r="K78" t="n">
-        <v>-236</v>
+        <v>122.24</v>
       </c>
       <c r="L78" t="n">
-        <v>236.96</v>
+        <v>149.9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:10:41</t>
+          <t>09:12:40</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.03</v>
+        <v>2.18</v>
       </c>
       <c r="F79" t="n">
-        <v>7.78</v>
+        <v>7.88</v>
       </c>
       <c r="G79" t="n">
-        <v>159.4</v>
+        <v>166.9</v>
       </c>
       <c r="H79" t="n">
-        <v>88.3</v>
+        <v>86.7</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>12.52</v>
+        <v>44.6</v>
       </c>
       <c r="K79" t="n">
-        <v>-44.89</v>
+        <v>71.05</v>
       </c>
       <c r="L79" t="n">
-        <v>46.6</v>
+        <v>83.89</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:15:48</t>
+          <t>09:17:07</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3400,31 +3400,31 @@
         <v>1.95</v>
       </c>
       <c r="F80" t="n">
-        <v>7.23</v>
+        <v>7.81</v>
       </c>
       <c r="G80" t="n">
-        <v>167.2</v>
+        <v>160.9</v>
       </c>
       <c r="H80" t="n">
-        <v>87.8</v>
+        <v>82.8</v>
       </c>
       <c r="I80" t="n">
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>155.55</v>
+        <v>163.51</v>
       </c>
       <c r="K80" t="n">
-        <v>125.46</v>
+        <v>26.72</v>
       </c>
       <c r="L80" t="n">
-        <v>199.84</v>
+        <v>165.68</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:17:50</t>
+          <t>09:18:16</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="F81" t="n">
-        <v>7.95</v>
+        <v>7.59</v>
       </c>
       <c r="G81" t="n">
-        <v>159.2</v>
+        <v>160.7</v>
       </c>
       <c r="H81" t="n">
-        <v>87.2</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I81" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>68.25</v>
+        <v>417.99</v>
       </c>
       <c r="K81" t="n">
-        <v>44.37</v>
+        <v>6.02</v>
       </c>
       <c r="L81" t="n">
-        <v>81.40000000000001</v>
+        <v>418.03</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:19:03</t>
+          <t>09:19:50</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.11</v>
+        <v>2.04</v>
       </c>
       <c r="F82" t="n">
-        <v>6.94</v>
+        <v>7.35</v>
       </c>
       <c r="G82" t="n">
-        <v>167.5</v>
+        <v>152.9</v>
       </c>
       <c r="H82" t="n">
-        <v>89</v>
+        <v>87.7</v>
       </c>
       <c r="I82" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-63.4</v>
+        <v>-150.39</v>
       </c>
       <c r="K82" t="n">
-        <v>186.23</v>
+        <v>133.01</v>
       </c>
       <c r="L82" t="n">
-        <v>196.73</v>
+        <v>200.77</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:23:20</t>
+          <t>09:24:03</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="F83" t="n">
-        <v>7.66</v>
+        <v>6.9</v>
       </c>
       <c r="G83" t="n">
-        <v>157.1</v>
+        <v>162.4</v>
       </c>
       <c r="H83" t="n">
-        <v>85.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I83" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>123.22</v>
+        <v>-340.95</v>
       </c>
       <c r="K83" t="n">
-        <v>-218</v>
+        <v>-233.87</v>
       </c>
       <c r="L83" t="n">
-        <v>250.41</v>
+        <v>413.45</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:25:27</t>
+          <t>09:26:22</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="F84" t="n">
-        <v>7.76</v>
+        <v>7.83</v>
       </c>
       <c r="G84" t="n">
-        <v>168.8</v>
+        <v>176.7</v>
       </c>
       <c r="H84" t="n">
-        <v>79.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>-272.29</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>341.9</v>
+        <v>-44.08</v>
       </c>
       <c r="L84" t="n">
-        <v>437.08</v>
+        <v>82.06</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:26:15</t>
+          <t>09:27:08</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="F85" t="n">
-        <v>7.57</v>
+        <v>7.26</v>
       </c>
       <c r="G85" t="n">
-        <v>171.2</v>
+        <v>173.5</v>
       </c>
       <c r="H85" t="n">
-        <v>88.7</v>
+        <v>81</v>
       </c>
       <c r="I85" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>280.58</v>
+        <v>63.15</v>
       </c>
       <c r="K85" t="n">
-        <v>91.23</v>
+        <v>320.76</v>
       </c>
       <c r="L85" t="n">
-        <v>295.04</v>
+        <v>326.92</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:30:07</t>
+          <t>09:33:10</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="F86" t="n">
-        <v>7.71</v>
+        <v>7.7</v>
       </c>
       <c r="G86" t="n">
-        <v>158.5</v>
+        <v>170.1</v>
       </c>
       <c r="H86" t="n">
-        <v>90.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-91.98</v>
+        <v>-195.14</v>
       </c>
       <c r="K86" t="n">
-        <v>189.38</v>
+        <v>-618.96</v>
       </c>
       <c r="L86" t="n">
-        <v>210.54</v>
+        <v>648.99</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:31:51</t>
+          <t>09:35:27</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.92</v>
+        <v>2.53</v>
       </c>
       <c r="F87" t="n">
-        <v>7.29</v>
+        <v>7.21</v>
       </c>
       <c r="G87" t="n">
-        <v>174.9</v>
+        <v>158</v>
       </c>
       <c r="H87" t="n">
-        <v>86.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I87" t="n">
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>161.02</v>
+        <v>236.71</v>
       </c>
       <c r="K87" t="n">
-        <v>-497.72</v>
+        <v>229.25</v>
       </c>
       <c r="L87" t="n">
-        <v>523.12</v>
+        <v>329.53</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:33:28</t>
+          <t>09:37:35</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.49</v>
+        <v>2.23</v>
       </c>
       <c r="F88" t="n">
-        <v>7.7</v>
+        <v>7.29</v>
       </c>
       <c r="G88" t="n">
-        <v>159.9</v>
+        <v>171</v>
       </c>
       <c r="H88" t="n">
-        <v>91.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="I88" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>-340.36</v>
+        <v>375.58</v>
       </c>
       <c r="K88" t="n">
-        <v>-168.64</v>
+        <v>-50.39</v>
       </c>
       <c r="L88" t="n">
-        <v>379.85</v>
+        <v>378.95</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-22.xlsx
+++ b/output/2025-08-22.xlsx
@@ -640,13 +640,13 @@
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>74.27</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-52.64</v>
+        <v>-56.06</v>
       </c>
       <c r="L14" t="n">
-        <v>91.03</v>
+        <v>96.95</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-161.5</v>
+        <v>-137</v>
       </c>
       <c r="K15" t="n">
-        <v>-11.8</v>
+        <v>-10.01</v>
       </c>
       <c r="L15" t="n">
-        <v>161.93</v>
+        <v>137.37</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-104.77</v>
+        <v>-108.81</v>
       </c>
       <c r="K16" t="n">
-        <v>-24.31</v>
+        <v>-25.25</v>
       </c>
       <c r="L16" t="n">
-        <v>107.56</v>
+        <v>111.7</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>183.19</v>
+        <v>154.39</v>
       </c>
       <c r="K17" t="n">
-        <v>201.96</v>
+        <v>170.21</v>
       </c>
       <c r="L17" t="n">
-        <v>272.66</v>
+        <v>229.8</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-143.4</v>
+        <v>-129.48</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="L18" t="n">
-        <v>143.4</v>
+        <v>129.49</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>17</v>
       </c>
       <c r="J19" t="n">
-        <v>83.41</v>
+        <v>87.73</v>
       </c>
       <c r="K19" t="n">
-        <v>-94.03</v>
+        <v>-98.89</v>
       </c>
       <c r="L19" t="n">
-        <v>125.69</v>
+        <v>132.19</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-33.73</v>
+        <v>-54.67</v>
       </c>
       <c r="K20" t="n">
-        <v>-67.58</v>
+        <v>-109.56</v>
       </c>
       <c r="L20" t="n">
-        <v>75.53</v>
+        <v>122.44</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>-160.24</v>
+        <v>-164.58</v>
       </c>
       <c r="K21" t="n">
-        <v>-190.19</v>
+        <v>-195.33</v>
       </c>
       <c r="L21" t="n">
-        <v>248.7</v>
+        <v>255.42</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>277.92</v>
+        <v>264.89</v>
       </c>
       <c r="K22" t="n">
-        <v>-45.56</v>
+        <v>-43.42</v>
       </c>
       <c r="L22" t="n">
-        <v>281.63</v>
+        <v>268.43</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-565.3200000000001</v>
+        <v>-503.18</v>
       </c>
       <c r="K23" t="n">
-        <v>15.07</v>
+        <v>13.41</v>
       </c>
       <c r="L23" t="n">
-        <v>565.52</v>
+        <v>503.36</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>548.75</v>
+        <v>557.05</v>
       </c>
       <c r="K24" t="n">
-        <v>-335.25</v>
+        <v>-340.32</v>
       </c>
       <c r="L24" t="n">
-        <v>643.0599999999999</v>
+        <v>652.78</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>17</v>
       </c>
       <c r="J25" t="n">
-        <v>-105.11</v>
+        <v>-200.1</v>
       </c>
       <c r="K25" t="n">
-        <v>-42.14</v>
+        <v>-80.22</v>
       </c>
       <c r="L25" t="n">
-        <v>113.25</v>
+        <v>215.58</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>113.41</v>
+        <v>262.27</v>
       </c>
       <c r="K26" t="n">
-        <v>11.82</v>
+        <v>27.33</v>
       </c>
       <c r="L26" t="n">
-        <v>114.03</v>
+        <v>263.69</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>505.65</v>
+        <v>536.64</v>
       </c>
       <c r="K27" t="n">
-        <v>-229.93</v>
+        <v>-244.03</v>
       </c>
       <c r="L27" t="n">
-        <v>555.48</v>
+        <v>589.52</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>201.44</v>
+        <v>331.18</v>
       </c>
       <c r="K28" t="n">
-        <v>49.47</v>
+        <v>81.33</v>
       </c>
       <c r="L28" t="n">
-        <v>207.42</v>
+        <v>341.02</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-36.85</v>
+        <v>-32.92</v>
       </c>
       <c r="K29" t="n">
-        <v>112.03</v>
+        <v>100.06</v>
       </c>
       <c r="L29" t="n">
-        <v>117.94</v>
+        <v>105.34</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-7.98</v>
+        <v>-19.88</v>
       </c>
       <c r="K30" t="n">
-        <v>16.5</v>
+        <v>41.1</v>
       </c>
       <c r="L30" t="n">
-        <v>18.32</v>
+        <v>45.66</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-90.22</v>
+        <v>-88.18000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>47.18</v>
+        <v>46.11</v>
       </c>
       <c r="L31" t="n">
-        <v>101.81</v>
+        <v>99.51000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>157.68</v>
+        <v>139.31</v>
       </c>
       <c r="K32" t="n">
-        <v>-169.51</v>
+        <v>-149.76</v>
       </c>
       <c r="L32" t="n">
-        <v>231.51</v>
+        <v>204.54</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>66.81</v>
+        <v>66.13</v>
       </c>
       <c r="K33" t="n">
-        <v>108.17</v>
+        <v>107.08</v>
       </c>
       <c r="L33" t="n">
-        <v>127.14</v>
+        <v>125.85</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>112.58</v>
+        <v>115.22</v>
       </c>
       <c r="K34" t="n">
-        <v>-64.26000000000001</v>
+        <v>-65.76000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>129.63</v>
+        <v>132.67</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-34.34</v>
+        <v>-50.86</v>
       </c>
       <c r="K35" t="n">
-        <v>74.98999999999999</v>
+        <v>111.06</v>
       </c>
       <c r="L35" t="n">
-        <v>82.48</v>
+        <v>122.15</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-199.48</v>
+        <v>-222.68</v>
       </c>
       <c r="K36" t="n">
-        <v>10.25</v>
+        <v>11.44</v>
       </c>
       <c r="L36" t="n">
-        <v>199.74</v>
+        <v>222.98</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>15.67</v>
+        <v>15.05</v>
       </c>
       <c r="K37" t="n">
-        <v>387.71</v>
+        <v>372.37</v>
       </c>
       <c r="L37" t="n">
-        <v>388.03</v>
+        <v>372.67</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-81.22</v>
+        <v>-131.33</v>
       </c>
       <c r="K38" t="n">
-        <v>-80.11</v>
+        <v>-129.53</v>
       </c>
       <c r="L38" t="n">
-        <v>114.08</v>
+        <v>184.46</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-166.27</v>
+        <v>-222.06</v>
       </c>
       <c r="K39" t="n">
-        <v>-150.54</v>
+        <v>-201.05</v>
       </c>
       <c r="L39" t="n">
-        <v>224.29</v>
+        <v>299.56</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-133.37</v>
+        <v>-160.28</v>
       </c>
       <c r="K40" t="n">
-        <v>-350.63</v>
+        <v>-421.39</v>
       </c>
       <c r="L40" t="n">
-        <v>375.14</v>
+        <v>450.84</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>47.05</v>
+        <v>58.37</v>
       </c>
       <c r="K41" t="n">
-        <v>548.61</v>
+        <v>680.67</v>
       </c>
       <c r="L41" t="n">
-        <v>550.63</v>
+        <v>683.17</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>3.48</v>
+        <v>4.58</v>
       </c>
       <c r="K42" t="n">
-        <v>-460.9</v>
+        <v>-607.36</v>
       </c>
       <c r="L42" t="n">
-        <v>460.91</v>
+        <v>607.37</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>87.7</v>
+        <v>111.68</v>
       </c>
       <c r="K43" t="n">
-        <v>-443.89</v>
+        <v>-565.25</v>
       </c>
       <c r="L43" t="n">
-        <v>452.47</v>
+        <v>576.17</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-69.15000000000001</v>
+        <v>-56.18</v>
       </c>
       <c r="K44" t="n">
-        <v>98.11</v>
+        <v>79.70999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>120.03</v>
+        <v>97.52</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>52.65</v>
+        <v>63.88</v>
       </c>
       <c r="K45" t="n">
-        <v>44.6</v>
+        <v>54.1</v>
       </c>
       <c r="L45" t="n">
-        <v>69</v>
+        <v>83.70999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-42.95</v>
+        <v>-56.28</v>
       </c>
       <c r="K46" t="n">
-        <v>29.45</v>
+        <v>38.59</v>
       </c>
       <c r="L46" t="n">
-        <v>52.08</v>
+        <v>68.23999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>130.85</v>
+        <v>154.34</v>
       </c>
       <c r="K47" t="n">
-        <v>4.48</v>
+        <v>5.29</v>
       </c>
       <c r="L47" t="n">
-        <v>130.92</v>
+        <v>154.43</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-22.09</v>
+        <v>-22.04</v>
       </c>
       <c r="K48" t="n">
-        <v>124.55</v>
+        <v>124.29</v>
       </c>
       <c r="L48" t="n">
-        <v>126.49</v>
+        <v>126.22</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-202.28</v>
+        <v>-188.15</v>
       </c>
       <c r="K49" t="n">
-        <v>-164.9</v>
+        <v>-153.38</v>
       </c>
       <c r="L49" t="n">
-        <v>260.98</v>
+        <v>242.74</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>-90.81999999999999</v>
+        <v>-143.03</v>
       </c>
       <c r="K50" t="n">
-        <v>-19.58</v>
+        <v>-30.84</v>
       </c>
       <c r="L50" t="n">
-        <v>92.91</v>
+        <v>146.32</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>107.54</v>
+        <v>142.54</v>
       </c>
       <c r="K51" t="n">
-        <v>19.6</v>
+        <v>25.98</v>
       </c>
       <c r="L51" t="n">
-        <v>109.31</v>
+        <v>144.89</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>124.75</v>
+        <v>168.46</v>
       </c>
       <c r="K52" t="n">
-        <v>-40.27</v>
+        <v>-54.37</v>
       </c>
       <c r="L52" t="n">
-        <v>131.09</v>
+        <v>177.02</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>228.8</v>
+        <v>371.42</v>
       </c>
       <c r="K53" t="n">
-        <v>-126.89</v>
+        <v>-205.98</v>
       </c>
       <c r="L53" t="n">
-        <v>261.63</v>
+        <v>424.71</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>70.61</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>154.71</v>
+        <v>205.32</v>
       </c>
       <c r="L54" t="n">
-        <v>170.06</v>
+        <v>225.7</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>-252.88</v>
+        <v>-247.7</v>
       </c>
       <c r="K55" t="n">
-        <v>402.84</v>
+        <v>394.58</v>
       </c>
       <c r="L55" t="n">
-        <v>475.64</v>
+        <v>465.88</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>297.06</v>
+        <v>417.18</v>
       </c>
       <c r="K56" t="n">
-        <v>161.63</v>
+        <v>226.99</v>
       </c>
       <c r="L56" t="n">
-        <v>338.18</v>
+        <v>474.94</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-184.24</v>
+        <v>-267.12</v>
       </c>
       <c r="K57" t="n">
-        <v>278.19</v>
+        <v>403.35</v>
       </c>
       <c r="L57" t="n">
-        <v>333.67</v>
+        <v>483.79</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-290.48</v>
+        <v>-344.44</v>
       </c>
       <c r="K58" t="n">
-        <v>-393.78</v>
+        <v>-466.93</v>
       </c>
       <c r="L58" t="n">
-        <v>489.33</v>
+        <v>580.23</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-114.01</v>
+        <v>-85.62</v>
       </c>
       <c r="K59" t="n">
-        <v>-60.15</v>
+        <v>-45.17</v>
       </c>
       <c r="L59" t="n">
-        <v>128.91</v>
+        <v>96.81</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>105.43</v>
+        <v>89.45</v>
       </c>
       <c r="K60" t="n">
-        <v>76.98999999999999</v>
+        <v>65.33</v>
       </c>
       <c r="L60" t="n">
-        <v>130.55</v>
+        <v>110.77</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>37.12</v>
+        <v>38.55</v>
       </c>
       <c r="K61" t="n">
-        <v>-77.36</v>
+        <v>-80.34</v>
       </c>
       <c r="L61" t="n">
-        <v>85.8</v>
+        <v>89.11</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-44.68</v>
+        <v>-63.69</v>
       </c>
       <c r="K62" t="n">
-        <v>49.07</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>66.36</v>
+        <v>94.61</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-122.04</v>
+        <v>-116.56</v>
       </c>
       <c r="K63" t="n">
-        <v>-149.16</v>
+        <v>-142.46</v>
       </c>
       <c r="L63" t="n">
-        <v>192.73</v>
+        <v>184.06</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-36.08</v>
+        <v>-33.06</v>
       </c>
       <c r="K64" t="n">
-        <v>128.96</v>
+        <v>118.16</v>
       </c>
       <c r="L64" t="n">
-        <v>133.91</v>
+        <v>122.7</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>-81.52</v>
+        <v>-118.37</v>
       </c>
       <c r="K65" t="n">
-        <v>67.31999999999999</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>105.72</v>
+        <v>153.52</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-360.29</v>
+        <v>-326.29</v>
       </c>
       <c r="K66" t="n">
-        <v>169.44</v>
+        <v>153.46</v>
       </c>
       <c r="L66" t="n">
-        <v>398.15</v>
+        <v>360.58</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-226.42</v>
+        <v>-187.7</v>
       </c>
       <c r="K67" t="n">
-        <v>-61.79</v>
+        <v>-51.23</v>
       </c>
       <c r="L67" t="n">
-        <v>234.7</v>
+        <v>194.57</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-373.25</v>
+        <v>-361.41</v>
       </c>
       <c r="K68" t="n">
-        <v>-271.9</v>
+        <v>-263.28</v>
       </c>
       <c r="L68" t="n">
-        <v>461.78</v>
+        <v>447.14</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>194.57</v>
+        <v>261.25</v>
       </c>
       <c r="K69" t="n">
-        <v>29.71</v>
+        <v>39.89</v>
       </c>
       <c r="L69" t="n">
-        <v>196.82</v>
+        <v>264.28</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-334.26</v>
+        <v>-338.7</v>
       </c>
       <c r="K70" t="n">
-        <v>-76.06</v>
+        <v>-77.06999999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>342.81</v>
+        <v>347.35</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>-677.55</v>
+        <v>-735.55</v>
       </c>
       <c r="K71" t="n">
-        <v>646.59</v>
+        <v>701.9400000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>936.5599999999999</v>
+        <v>1016.73</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>-74.58</v>
+        <v>-130.11</v>
       </c>
       <c r="K72" t="n">
-        <v>-182.81</v>
+        <v>-318.94</v>
       </c>
       <c r="L72" t="n">
-        <v>197.43</v>
+        <v>344.46</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>363.84</v>
+        <v>468.59</v>
       </c>
       <c r="K73" t="n">
-        <v>45.87</v>
+        <v>59.08</v>
       </c>
       <c r="L73" t="n">
-        <v>366.72</v>
+        <v>472.3</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>19.45</v>
+        <v>18.99</v>
       </c>
       <c r="K74" t="n">
-        <v>-87.18000000000001</v>
+        <v>-85.11</v>
       </c>
       <c r="L74" t="n">
-        <v>89.31999999999999</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-18.62</v>
+        <v>-12.13</v>
       </c>
       <c r="K75" t="n">
-        <v>-231.62</v>
+        <v>-150.87</v>
       </c>
       <c r="L75" t="n">
-        <v>232.37</v>
+        <v>151.36</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-36.2</v>
+        <v>-39.41</v>
       </c>
       <c r="K76" t="n">
-        <v>-230.86</v>
+        <v>-251.32</v>
       </c>
       <c r="L76" t="n">
-        <v>233.68</v>
+        <v>254.4</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>240.86</v>
+        <v>180.29</v>
       </c>
       <c r="K77" t="n">
-        <v>-424.53</v>
+        <v>-317.77</v>
       </c>
       <c r="L77" t="n">
-        <v>488.1</v>
+        <v>365.35</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-86.76000000000001</v>
+        <v>-87.67</v>
       </c>
       <c r="K78" t="n">
-        <v>122.24</v>
+        <v>123.52</v>
       </c>
       <c r="L78" t="n">
-        <v>149.9</v>
+        <v>151.47</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>44.6</v>
+        <v>53.63</v>
       </c>
       <c r="K79" t="n">
-        <v>71.05</v>
+        <v>85.44</v>
       </c>
       <c r="L79" t="n">
-        <v>83.89</v>
+        <v>100.87</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>163.51</v>
+        <v>185.46</v>
       </c>
       <c r="K80" t="n">
-        <v>26.72</v>
+        <v>30.3</v>
       </c>
       <c r="L80" t="n">
-        <v>165.68</v>
+        <v>187.92</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>417.99</v>
+        <v>405.31</v>
       </c>
       <c r="K81" t="n">
-        <v>6.02</v>
+        <v>5.83</v>
       </c>
       <c r="L81" t="n">
-        <v>418.03</v>
+        <v>405.35</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-150.39</v>
+        <v>-148.99</v>
       </c>
       <c r="K82" t="n">
-        <v>133.01</v>
+        <v>131.78</v>
       </c>
       <c r="L82" t="n">
-        <v>200.77</v>
+        <v>198.91</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>-340.95</v>
+        <v>-350.5</v>
       </c>
       <c r="K83" t="n">
-        <v>-233.87</v>
+        <v>-240.41</v>
       </c>
       <c r="L83" t="n">
-        <v>413.45</v>
+        <v>425.02</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>69.20999999999999</v>
+        <v>142.11</v>
       </c>
       <c r="K84" t="n">
-        <v>-44.08</v>
+        <v>-90.51000000000001</v>
       </c>
       <c r="L84" t="n">
-        <v>82.06</v>
+        <v>168.49</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>63.15</v>
+        <v>66.59</v>
       </c>
       <c r="K85" t="n">
-        <v>320.76</v>
+        <v>338.25</v>
       </c>
       <c r="L85" t="n">
-        <v>326.92</v>
+        <v>344.75</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-195.14</v>
+        <v>-204.21</v>
       </c>
       <c r="K86" t="n">
-        <v>-618.96</v>
+        <v>-647.75</v>
       </c>
       <c r="L86" t="n">
-        <v>648.99</v>
+        <v>679.1799999999999</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>236.71</v>
+        <v>381.91</v>
       </c>
       <c r="K87" t="n">
-        <v>229.25</v>
+        <v>369.86</v>
       </c>
       <c r="L87" t="n">
-        <v>329.53</v>
+        <v>531.65</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>375.58</v>
+        <v>517.04</v>
       </c>
       <c r="K88" t="n">
-        <v>-50.39</v>
+        <v>-69.37</v>
       </c>
       <c r="L88" t="n">
-        <v>378.95</v>
+        <v>521.67</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-22.xlsx
+++ b/output/2025-08-22.xlsx
@@ -640,13 +640,13 @@
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>79.09999999999999</v>
+        <v>53.87</v>
       </c>
       <c r="K14" t="n">
-        <v>-56.06</v>
+        <v>-38.18</v>
       </c>
       <c r="L14" t="n">
-        <v>96.95</v>
+        <v>66.03</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-137</v>
+        <v>-90.16</v>
       </c>
       <c r="K15" t="n">
-        <v>-10.01</v>
+        <v>-6.59</v>
       </c>
       <c r="L15" t="n">
-        <v>137.37</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-108.81</v>
+        <v>-72.09</v>
       </c>
       <c r="K16" t="n">
-        <v>-25.25</v>
+        <v>-16.73</v>
       </c>
       <c r="L16" t="n">
-        <v>111.7</v>
+        <v>74.01000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>154.39</v>
+        <v>102.94</v>
       </c>
       <c r="K17" t="n">
-        <v>170.21</v>
+        <v>113.48</v>
       </c>
       <c r="L17" t="n">
-        <v>229.8</v>
+        <v>153.21</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-129.48</v>
+        <v>-94.7</v>
       </c>
       <c r="K18" t="n">
-        <v>1.08</v>
+        <v>0.79</v>
       </c>
       <c r="L18" t="n">
-        <v>129.49</v>
+        <v>94.7</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>17</v>
       </c>
       <c r="J19" t="n">
-        <v>87.73</v>
+        <v>59.97</v>
       </c>
       <c r="K19" t="n">
-        <v>-98.89</v>
+        <v>-67.59999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>132.19</v>
+        <v>90.37</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-54.67</v>
+        <v>-33.73</v>
       </c>
       <c r="K20" t="n">
-        <v>-109.56</v>
+        <v>-67.59</v>
       </c>
       <c r="L20" t="n">
-        <v>122.44</v>
+        <v>75.53</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>-164.58</v>
+        <v>-92.84</v>
       </c>
       <c r="K21" t="n">
-        <v>-195.33</v>
+        <v>-110.19</v>
       </c>
       <c r="L21" t="n">
-        <v>255.42</v>
+        <v>144.09</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>264.89</v>
+        <v>157.65</v>
       </c>
       <c r="K22" t="n">
-        <v>-43.42</v>
+        <v>-25.84</v>
       </c>
       <c r="L22" t="n">
-        <v>268.43</v>
+        <v>159.76</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-503.18</v>
+        <v>-294.25</v>
       </c>
       <c r="K23" t="n">
-        <v>13.41</v>
+        <v>7.84</v>
       </c>
       <c r="L23" t="n">
-        <v>503.36</v>
+        <v>294.35</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>557.05</v>
+        <v>262.77</v>
       </c>
       <c r="K24" t="n">
-        <v>-340.32</v>
+        <v>-160.53</v>
       </c>
       <c r="L24" t="n">
-        <v>652.78</v>
+        <v>307.92</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>17</v>
       </c>
       <c r="J25" t="n">
-        <v>-200.1</v>
+        <v>-96.72</v>
       </c>
       <c r="K25" t="n">
-        <v>-80.22</v>
+        <v>-38.77</v>
       </c>
       <c r="L25" t="n">
-        <v>215.58</v>
+        <v>104.21</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>262.27</v>
+        <v>126.04</v>
       </c>
       <c r="K26" t="n">
-        <v>27.33</v>
+        <v>13.14</v>
       </c>
       <c r="L26" t="n">
-        <v>263.69</v>
+        <v>126.72</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>536.64</v>
+        <v>277.56</v>
       </c>
       <c r="K27" t="n">
-        <v>-244.03</v>
+        <v>-126.22</v>
       </c>
       <c r="L27" t="n">
-        <v>589.52</v>
+        <v>304.91</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>331.18</v>
+        <v>159.61</v>
       </c>
       <c r="K28" t="n">
-        <v>81.33</v>
+        <v>39.2</v>
       </c>
       <c r="L28" t="n">
-        <v>341.02</v>
+        <v>164.35</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-32.92</v>
+        <v>-23.86</v>
       </c>
       <c r="K29" t="n">
-        <v>100.06</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>105.34</v>
+        <v>76.36</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-19.88</v>
+        <v>-13.82</v>
       </c>
       <c r="K30" t="n">
-        <v>41.1</v>
+        <v>28.57</v>
       </c>
       <c r="L30" t="n">
-        <v>45.66</v>
+        <v>31.74</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-88.18000000000001</v>
+        <v>-58.01</v>
       </c>
       <c r="K31" t="n">
-        <v>46.11</v>
+        <v>30.33</v>
       </c>
       <c r="L31" t="n">
-        <v>99.51000000000001</v>
+        <v>65.45999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>139.31</v>
+        <v>90.03</v>
       </c>
       <c r="K32" t="n">
-        <v>-149.76</v>
+        <v>-96.79000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>204.54</v>
+        <v>132.19</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>66.13</v>
+        <v>46.95</v>
       </c>
       <c r="K33" t="n">
-        <v>107.08</v>
+        <v>76.02</v>
       </c>
       <c r="L33" t="n">
-        <v>125.85</v>
+        <v>89.34999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>115.22</v>
+        <v>82.2</v>
       </c>
       <c r="K34" t="n">
-        <v>-65.76000000000001</v>
+        <v>-46.91</v>
       </c>
       <c r="L34" t="n">
-        <v>132.67</v>
+        <v>94.64</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-50.86</v>
+        <v>-31.93</v>
       </c>
       <c r="K35" t="n">
-        <v>111.06</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>122.15</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-222.68</v>
+        <v>-131.24</v>
       </c>
       <c r="K36" t="n">
-        <v>11.44</v>
+        <v>6.74</v>
       </c>
       <c r="L36" t="n">
-        <v>222.98</v>
+        <v>131.42</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>15.05</v>
+        <v>8.75</v>
       </c>
       <c r="K37" t="n">
-        <v>372.37</v>
+        <v>216.35</v>
       </c>
       <c r="L37" t="n">
-        <v>372.67</v>
+        <v>216.53</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-131.33</v>
+        <v>-75.93000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>-129.53</v>
+        <v>-74.89</v>
       </c>
       <c r="L38" t="n">
-        <v>184.46</v>
+        <v>106.65</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-222.06</v>
+        <v>-109.88</v>
       </c>
       <c r="K39" t="n">
-        <v>-201.05</v>
+        <v>-99.48</v>
       </c>
       <c r="L39" t="n">
-        <v>299.56</v>
+        <v>148.22</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-160.28</v>
+        <v>-75.7</v>
       </c>
       <c r="K40" t="n">
-        <v>-421.39</v>
+        <v>-199.01</v>
       </c>
       <c r="L40" t="n">
-        <v>450.84</v>
+        <v>212.92</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>58.37</v>
+        <v>25.47</v>
       </c>
       <c r="K41" t="n">
-        <v>680.67</v>
+        <v>297.06</v>
       </c>
       <c r="L41" t="n">
-        <v>683.17</v>
+        <v>298.15</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>4.58</v>
+        <v>2</v>
       </c>
       <c r="K42" t="n">
-        <v>-607.36</v>
+        <v>-265.76</v>
       </c>
       <c r="L42" t="n">
-        <v>607.37</v>
+        <v>265.77</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>111.68</v>
+        <v>49.76</v>
       </c>
       <c r="K43" t="n">
-        <v>-565.25</v>
+        <v>-251.86</v>
       </c>
       <c r="L43" t="n">
-        <v>576.17</v>
+        <v>256.73</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-56.18</v>
+        <v>-42.22</v>
       </c>
       <c r="K44" t="n">
-        <v>79.70999999999999</v>
+        <v>59.9</v>
       </c>
       <c r="L44" t="n">
-        <v>97.52</v>
+        <v>73.28</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>63.88</v>
+        <v>42.52</v>
       </c>
       <c r="K45" t="n">
-        <v>54.1</v>
+        <v>36.02</v>
       </c>
       <c r="L45" t="n">
-        <v>83.70999999999999</v>
+        <v>55.73</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-56.28</v>
+        <v>-37.94</v>
       </c>
       <c r="K46" t="n">
-        <v>38.59</v>
+        <v>26.01</v>
       </c>
       <c r="L46" t="n">
-        <v>68.23999999999999</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>154.34</v>
+        <v>102.75</v>
       </c>
       <c r="K47" t="n">
-        <v>5.29</v>
+        <v>3.52</v>
       </c>
       <c r="L47" t="n">
-        <v>154.43</v>
+        <v>102.81</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-22.04</v>
+        <v>-15.42</v>
       </c>
       <c r="K48" t="n">
-        <v>124.29</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>126.22</v>
+        <v>88.29000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-188.15</v>
+        <v>-127.08</v>
       </c>
       <c r="K49" t="n">
-        <v>-153.38</v>
+        <v>-103.6</v>
       </c>
       <c r="L49" t="n">
-        <v>242.74</v>
+        <v>163.96</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>-143.03</v>
+        <v>-81.02</v>
       </c>
       <c r="K50" t="n">
-        <v>-30.84</v>
+        <v>-17.47</v>
       </c>
       <c r="L50" t="n">
-        <v>146.32</v>
+        <v>82.88</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>142.54</v>
+        <v>87.87</v>
       </c>
       <c r="K51" t="n">
-        <v>25.98</v>
+        <v>16.01</v>
       </c>
       <c r="L51" t="n">
-        <v>144.89</v>
+        <v>89.31999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>168.46</v>
+        <v>100.69</v>
       </c>
       <c r="K52" t="n">
-        <v>-54.37</v>
+        <v>-32.5</v>
       </c>
       <c r="L52" t="n">
-        <v>177.02</v>
+        <v>105.8</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>371.42</v>
+        <v>188.39</v>
       </c>
       <c r="K53" t="n">
-        <v>-205.98</v>
+        <v>-104.48</v>
       </c>
       <c r="L53" t="n">
-        <v>424.71</v>
+        <v>215.42</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>93.70999999999999</v>
+        <v>50.18</v>
       </c>
       <c r="K54" t="n">
-        <v>205.32</v>
+        <v>109.94</v>
       </c>
       <c r="L54" t="n">
-        <v>225.7</v>
+        <v>120.85</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>-247.7</v>
+        <v>-132.7</v>
       </c>
       <c r="K55" t="n">
-        <v>394.58</v>
+        <v>211.39</v>
       </c>
       <c r="L55" t="n">
-        <v>465.88</v>
+        <v>249.59</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>417.18</v>
+        <v>191.03</v>
       </c>
       <c r="K56" t="n">
-        <v>226.99</v>
+        <v>103.94</v>
       </c>
       <c r="L56" t="n">
-        <v>474.94</v>
+        <v>217.47</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-267.12</v>
+        <v>-117.54</v>
       </c>
       <c r="K57" t="n">
-        <v>403.35</v>
+        <v>177.49</v>
       </c>
       <c r="L57" t="n">
-        <v>483.79</v>
+        <v>212.88</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-344.44</v>
+        <v>-165.84</v>
       </c>
       <c r="K58" t="n">
-        <v>-466.93</v>
+        <v>-224.82</v>
       </c>
       <c r="L58" t="n">
-        <v>580.23</v>
+        <v>279.36</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-85.62</v>
+        <v>-73.88</v>
       </c>
       <c r="K59" t="n">
-        <v>-45.17</v>
+        <v>-38.98</v>
       </c>
       <c r="L59" t="n">
-        <v>96.81</v>
+        <v>83.54000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>89.45</v>
+        <v>62.4</v>
       </c>
       <c r="K60" t="n">
-        <v>65.33</v>
+        <v>45.57</v>
       </c>
       <c r="L60" t="n">
-        <v>110.77</v>
+        <v>77.27</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>38.55</v>
+        <v>28.9</v>
       </c>
       <c r="K61" t="n">
-        <v>-80.34</v>
+        <v>-60.22</v>
       </c>
       <c r="L61" t="n">
-        <v>89.11</v>
+        <v>66.8</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-63.69</v>
+        <v>-41.22</v>
       </c>
       <c r="K62" t="n">
-        <v>69.95999999999999</v>
+        <v>45.28</v>
       </c>
       <c r="L62" t="n">
-        <v>94.61</v>
+        <v>61.23</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-116.56</v>
+        <v>-78.42</v>
       </c>
       <c r="K63" t="n">
-        <v>-142.46</v>
+        <v>-95.84999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>184.06</v>
+        <v>123.85</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-33.06</v>
+        <v>-25.48</v>
       </c>
       <c r="K64" t="n">
-        <v>118.16</v>
+        <v>91.09</v>
       </c>
       <c r="L64" t="n">
-        <v>122.7</v>
+        <v>94.59</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>-118.37</v>
+        <v>-69.31999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>97.76000000000001</v>
+        <v>57.25</v>
       </c>
       <c r="L65" t="n">
-        <v>153.52</v>
+        <v>89.90000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-326.29</v>
+        <v>-194.11</v>
       </c>
       <c r="K66" t="n">
-        <v>153.46</v>
+        <v>91.29000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>360.58</v>
+        <v>214.5</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-187.7</v>
+        <v>-117.9</v>
       </c>
       <c r="K67" t="n">
-        <v>-51.23</v>
+        <v>-32.18</v>
       </c>
       <c r="L67" t="n">
-        <v>194.57</v>
+        <v>122.21</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-361.41</v>
+        <v>-207.8</v>
       </c>
       <c r="K68" t="n">
-        <v>-263.28</v>
+        <v>-151.38</v>
       </c>
       <c r="L68" t="n">
-        <v>447.14</v>
+        <v>257.09</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>261.25</v>
+        <v>136.27</v>
       </c>
       <c r="K69" t="n">
-        <v>39.89</v>
+        <v>20.81</v>
       </c>
       <c r="L69" t="n">
-        <v>264.28</v>
+        <v>137.85</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-338.7</v>
+        <v>-189.34</v>
       </c>
       <c r="K70" t="n">
-        <v>-77.06999999999999</v>
+        <v>-43.08</v>
       </c>
       <c r="L70" t="n">
-        <v>347.35</v>
+        <v>194.18</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>-735.55</v>
+        <v>-355.26</v>
       </c>
       <c r="K71" t="n">
-        <v>701.9400000000001</v>
+        <v>339.03</v>
       </c>
       <c r="L71" t="n">
-        <v>1016.73</v>
+        <v>491.07</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>-130.11</v>
+        <v>-60.43</v>
       </c>
       <c r="K72" t="n">
-        <v>-318.94</v>
+        <v>-148.12</v>
       </c>
       <c r="L72" t="n">
-        <v>344.46</v>
+        <v>159.97</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>468.59</v>
+        <v>235.77</v>
       </c>
       <c r="K73" t="n">
-        <v>59.08</v>
+        <v>29.72</v>
       </c>
       <c r="L73" t="n">
-        <v>472.3</v>
+        <v>237.63</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>18.99</v>
+        <v>13.57</v>
       </c>
       <c r="K74" t="n">
-        <v>-85.11</v>
+        <v>-60.8</v>
       </c>
       <c r="L74" t="n">
-        <v>87.2</v>
+        <v>62.29</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-12.13</v>
+        <v>-10.25</v>
       </c>
       <c r="K75" t="n">
-        <v>-150.87</v>
+        <v>-127.55</v>
       </c>
       <c r="L75" t="n">
-        <v>151.36</v>
+        <v>127.96</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-39.41</v>
+        <v>-25.18</v>
       </c>
       <c r="K76" t="n">
-        <v>-251.32</v>
+        <v>-160.59</v>
       </c>
       <c r="L76" t="n">
-        <v>254.4</v>
+        <v>162.55</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>180.29</v>
+        <v>121.01</v>
       </c>
       <c r="K77" t="n">
-        <v>-317.77</v>
+        <v>-213.28</v>
       </c>
       <c r="L77" t="n">
-        <v>365.35</v>
+        <v>245.22</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-87.67</v>
+        <v>-59.11</v>
       </c>
       <c r="K78" t="n">
-        <v>123.52</v>
+        <v>83.27</v>
       </c>
       <c r="L78" t="n">
-        <v>151.47</v>
+        <v>102.12</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>53.63</v>
+        <v>40.19</v>
       </c>
       <c r="K79" t="n">
-        <v>85.44</v>
+        <v>64.02</v>
       </c>
       <c r="L79" t="n">
-        <v>100.87</v>
+        <v>75.59</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>185.46</v>
+        <v>113.42</v>
       </c>
       <c r="K80" t="n">
-        <v>30.3</v>
+        <v>18.53</v>
       </c>
       <c r="L80" t="n">
-        <v>187.92</v>
+        <v>114.92</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>405.31</v>
+        <v>232.86</v>
       </c>
       <c r="K81" t="n">
-        <v>5.83</v>
+        <v>3.35</v>
       </c>
       <c r="L81" t="n">
-        <v>405.35</v>
+        <v>232.88</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-148.99</v>
+        <v>-98.89</v>
       </c>
       <c r="K82" t="n">
-        <v>131.78</v>
+        <v>87.45999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>198.91</v>
+        <v>132.02</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>-350.5</v>
+        <v>-185.02</v>
       </c>
       <c r="K83" t="n">
-        <v>-240.41</v>
+        <v>-126.91</v>
       </c>
       <c r="L83" t="n">
-        <v>425.02</v>
+        <v>224.36</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>142.11</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>-90.51000000000001</v>
+        <v>-48.08</v>
       </c>
       <c r="L84" t="n">
-        <v>168.49</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>66.59</v>
+        <v>35.8</v>
       </c>
       <c r="K85" t="n">
-        <v>338.25</v>
+        <v>181.86</v>
       </c>
       <c r="L85" t="n">
-        <v>344.75</v>
+        <v>185.35</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-204.21</v>
+        <v>-103.99</v>
       </c>
       <c r="K86" t="n">
-        <v>-647.75</v>
+        <v>-329.85</v>
       </c>
       <c r="L86" t="n">
-        <v>679.1799999999999</v>
+        <v>345.85</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>381.91</v>
+        <v>170.49</v>
       </c>
       <c r="K87" t="n">
-        <v>369.86</v>
+        <v>165.11</v>
       </c>
       <c r="L87" t="n">
-        <v>531.65</v>
+        <v>237.33</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>517.04</v>
+        <v>242.14</v>
       </c>
       <c r="K88" t="n">
-        <v>-69.37</v>
+        <v>-32.49</v>
       </c>
       <c r="L88" t="n">
-        <v>521.67</v>
+        <v>244.31</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-22.xlsx
+++ b/output/2025-08-22.xlsx
@@ -640,13 +640,13 @@
         <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>53.87</v>
+        <v>55.5</v>
       </c>
       <c r="K14" t="n">
-        <v>-38.18</v>
+        <v>-39.33</v>
       </c>
       <c r="L14" t="n">
-        <v>66.03</v>
+        <v>68.03</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-90.16</v>
+        <v>-96.98</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.59</v>
+        <v>-7.08</v>
       </c>
       <c r="L15" t="n">
-        <v>90.40000000000001</v>
+        <v>97.23999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-72.09</v>
+        <v>-75.42</v>
       </c>
       <c r="K16" t="n">
-        <v>-16.73</v>
+        <v>-17.5</v>
       </c>
       <c r="L16" t="n">
-        <v>74.01000000000001</v>
+        <v>77.42</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>102.94</v>
+        <v>112.51</v>
       </c>
       <c r="K17" t="n">
-        <v>113.48</v>
+        <v>124.04</v>
       </c>
       <c r="L17" t="n">
-        <v>153.21</v>
+        <v>167.46</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>-94.7</v>
+        <v>-100.96</v>
       </c>
       <c r="K18" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="L18" t="n">
-        <v>94.7</v>
+        <v>100.96</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>17</v>
       </c>
       <c r="J19" t="n">
-        <v>59.97</v>
+        <v>65.59</v>
       </c>
       <c r="K19" t="n">
-        <v>-67.59999999999999</v>
+        <v>-73.94</v>
       </c>
       <c r="L19" t="n">
-        <v>90.37</v>
+        <v>98.84</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>20</v>
       </c>
       <c r="J20" t="n">
-        <v>-33.73</v>
+        <v>-38.23</v>
       </c>
       <c r="K20" t="n">
-        <v>-67.59</v>
+        <v>-76.59999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>75.53</v>
+        <v>85.61</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>17</v>
       </c>
       <c r="J21" t="n">
-        <v>-92.84</v>
+        <v>-106.86</v>
       </c>
       <c r="K21" t="n">
-        <v>-110.19</v>
+        <v>-126.82</v>
       </c>
       <c r="L21" t="n">
-        <v>144.09</v>
+        <v>165.84</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>19</v>
       </c>
       <c r="J22" t="n">
-        <v>157.65</v>
+        <v>177.88</v>
       </c>
       <c r="K22" t="n">
-        <v>-25.84</v>
+        <v>-29.16</v>
       </c>
       <c r="L22" t="n">
-        <v>159.76</v>
+        <v>180.25</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-294.25</v>
+        <v>-340.9</v>
       </c>
       <c r="K23" t="n">
-        <v>7.84</v>
+        <v>9.09</v>
       </c>
       <c r="L23" t="n">
-        <v>294.35</v>
+        <v>341.02</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>262.77</v>
+        <v>313.85</v>
       </c>
       <c r="K24" t="n">
-        <v>-160.53</v>
+        <v>-191.74</v>
       </c>
       <c r="L24" t="n">
-        <v>307.92</v>
+        <v>367.78</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>17</v>
       </c>
       <c r="J25" t="n">
-        <v>-96.72</v>
+        <v>-115.9</v>
       </c>
       <c r="K25" t="n">
-        <v>-38.77</v>
+        <v>-46.46</v>
       </c>
       <c r="L25" t="n">
-        <v>104.21</v>
+        <v>124.87</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>126.04</v>
+        <v>150.4</v>
       </c>
       <c r="K26" t="n">
-        <v>13.14</v>
+        <v>15.67</v>
       </c>
       <c r="L26" t="n">
-        <v>126.72</v>
+        <v>151.21</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>277.56</v>
+        <v>327.72</v>
       </c>
       <c r="K27" t="n">
-        <v>-126.22</v>
+        <v>-149.02</v>
       </c>
       <c r="L27" t="n">
-        <v>304.91</v>
+        <v>360.01</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>159.61</v>
+        <v>191.01</v>
       </c>
       <c r="K28" t="n">
-        <v>39.2</v>
+        <v>46.91</v>
       </c>
       <c r="L28" t="n">
-        <v>164.35</v>
+        <v>196.68</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-23.86</v>
+        <v>-25.73</v>
       </c>
       <c r="K29" t="n">
-        <v>72.54000000000001</v>
+        <v>78.20999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>76.36</v>
+        <v>82.33</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>-13.82</v>
+        <v>-14.43</v>
       </c>
       <c r="K30" t="n">
-        <v>28.57</v>
+        <v>29.84</v>
       </c>
       <c r="L30" t="n">
-        <v>31.74</v>
+        <v>33.15</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>-58.01</v>
+        <v>-61.79</v>
       </c>
       <c r="K31" t="n">
-        <v>30.33</v>
+        <v>32.31</v>
       </c>
       <c r="L31" t="n">
-        <v>65.45999999999999</v>
+        <v>69.73</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>90.03</v>
+        <v>97.81</v>
       </c>
       <c r="K32" t="n">
-        <v>-96.79000000000001</v>
+        <v>-105.15</v>
       </c>
       <c r="L32" t="n">
-        <v>132.19</v>
+        <v>143.61</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>46.95</v>
+        <v>51.02</v>
       </c>
       <c r="K33" t="n">
-        <v>76.02</v>
+        <v>82.61</v>
       </c>
       <c r="L33" t="n">
-        <v>89.34999999999999</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>18</v>
       </c>
       <c r="J34" t="n">
-        <v>82.2</v>
+        <v>89.81999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-46.91</v>
+        <v>-51.27</v>
       </c>
       <c r="L34" t="n">
-        <v>94.64</v>
+        <v>103.42</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>-31.93</v>
+        <v>-35.73</v>
       </c>
       <c r="K35" t="n">
-        <v>69.73999999999999</v>
+        <v>78.03</v>
       </c>
       <c r="L35" t="n">
-        <v>76.7</v>
+        <v>85.81999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>-131.24</v>
+        <v>-151.69</v>
       </c>
       <c r="K36" t="n">
-        <v>6.74</v>
+        <v>7.8</v>
       </c>
       <c r="L36" t="n">
-        <v>131.42</v>
+        <v>151.89</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>8.75</v>
+        <v>10.15</v>
       </c>
       <c r="K37" t="n">
-        <v>216.35</v>
+        <v>251.07</v>
       </c>
       <c r="L37" t="n">
-        <v>216.53</v>
+        <v>251.28</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>-75.93000000000001</v>
+        <v>-88.95999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>-74.89</v>
+        <v>-87.73999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>106.65</v>
+        <v>124.95</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>18</v>
       </c>
       <c r="J39" t="n">
-        <v>-109.88</v>
+        <v>-130.89</v>
       </c>
       <c r="K39" t="n">
-        <v>-99.48</v>
+        <v>-118.51</v>
       </c>
       <c r="L39" t="n">
-        <v>148.22</v>
+        <v>176.57</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>16</v>
       </c>
       <c r="J40" t="n">
-        <v>-75.7</v>
+        <v>-90.98</v>
       </c>
       <c r="K40" t="n">
-        <v>-199.01</v>
+        <v>-239.2</v>
       </c>
       <c r="L40" t="n">
-        <v>212.92</v>
+        <v>255.92</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>16</v>
       </c>
       <c r="J41" t="n">
-        <v>25.47</v>
+        <v>30.67</v>
       </c>
       <c r="K41" t="n">
-        <v>297.06</v>
+        <v>357.59</v>
       </c>
       <c r="L41" t="n">
-        <v>298.15</v>
+        <v>358.9</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="K42" t="n">
-        <v>-265.76</v>
+        <v>-322.76</v>
       </c>
       <c r="L42" t="n">
-        <v>265.77</v>
+        <v>322.77</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>49.76</v>
+        <v>60.2</v>
       </c>
       <c r="K43" t="n">
-        <v>-251.86</v>
+        <v>-304.72</v>
       </c>
       <c r="L43" t="n">
-        <v>256.73</v>
+        <v>310.61</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>21</v>
       </c>
       <c r="J44" t="n">
-        <v>-42.22</v>
+        <v>-44.16</v>
       </c>
       <c r="K44" t="n">
-        <v>59.9</v>
+        <v>62.65</v>
       </c>
       <c r="L44" t="n">
-        <v>73.28</v>
+        <v>76.65000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>42.52</v>
+        <v>44.09</v>
       </c>
       <c r="K45" t="n">
-        <v>36.02</v>
+        <v>37.34</v>
       </c>
       <c r="L45" t="n">
-        <v>55.73</v>
+        <v>57.77</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>17</v>
       </c>
       <c r="J46" t="n">
-        <v>-37.94</v>
+        <v>-40.39</v>
       </c>
       <c r="K46" t="n">
-        <v>26.01</v>
+        <v>27.69</v>
       </c>
       <c r="L46" t="n">
-        <v>46</v>
+        <v>48.97</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>17</v>
       </c>
       <c r="J47" t="n">
-        <v>102.75</v>
+        <v>113.95</v>
       </c>
       <c r="K47" t="n">
-        <v>3.52</v>
+        <v>3.91</v>
       </c>
       <c r="L47" t="n">
-        <v>102.81</v>
+        <v>114.02</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>19</v>
       </c>
       <c r="J48" t="n">
-        <v>-15.42</v>
+        <v>-16.66</v>
       </c>
       <c r="K48" t="n">
-        <v>86.93000000000001</v>
+        <v>93.92</v>
       </c>
       <c r="L48" t="n">
-        <v>88.29000000000001</v>
+        <v>95.39</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>18</v>
       </c>
       <c r="J49" t="n">
-        <v>-127.08</v>
+        <v>-139.5</v>
       </c>
       <c r="K49" t="n">
-        <v>-103.6</v>
+        <v>-113.73</v>
       </c>
       <c r="L49" t="n">
-        <v>163.96</v>
+        <v>179.99</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>17</v>
       </c>
       <c r="J50" t="n">
-        <v>-81.02</v>
+        <v>-93.31999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-17.47</v>
+        <v>-20.12</v>
       </c>
       <c r="L50" t="n">
-        <v>82.88</v>
+        <v>95.47</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>20</v>
       </c>
       <c r="J51" t="n">
-        <v>87.87</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>16.01</v>
+        <v>18.17</v>
       </c>
       <c r="L51" t="n">
-        <v>89.31999999999999</v>
+        <v>101.35</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>16</v>
       </c>
       <c r="J52" t="n">
-        <v>100.69</v>
+        <v>116.28</v>
       </c>
       <c r="K52" t="n">
-        <v>-32.5</v>
+        <v>-37.53</v>
       </c>
       <c r="L52" t="n">
-        <v>105.8</v>
+        <v>122.19</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>188.39</v>
+        <v>218.04</v>
       </c>
       <c r="K53" t="n">
-        <v>-104.48</v>
+        <v>-120.92</v>
       </c>
       <c r="L53" t="n">
-        <v>215.42</v>
+        <v>249.33</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>50.18</v>
+        <v>59.11</v>
       </c>
       <c r="K54" t="n">
-        <v>109.94</v>
+        <v>129.51</v>
       </c>
       <c r="L54" t="n">
-        <v>120.85</v>
+        <v>142.37</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>-132.7</v>
+        <v>-157.09</v>
       </c>
       <c r="K55" t="n">
-        <v>211.39</v>
+        <v>250.25</v>
       </c>
       <c r="L55" t="n">
-        <v>249.59</v>
+        <v>295.47</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>191.03</v>
+        <v>228.06</v>
       </c>
       <c r="K56" t="n">
-        <v>103.94</v>
+        <v>124.09</v>
       </c>
       <c r="L56" t="n">
-        <v>217.47</v>
+        <v>259.63</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-117.54</v>
+        <v>-141.95</v>
       </c>
       <c r="K57" t="n">
-        <v>177.49</v>
+        <v>214.34</v>
       </c>
       <c r="L57" t="n">
-        <v>212.88</v>
+        <v>257.09</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>18</v>
       </c>
       <c r="J58" t="n">
-        <v>-165.84</v>
+        <v>-197.46</v>
       </c>
       <c r="K58" t="n">
-        <v>-224.82</v>
+        <v>-267.69</v>
       </c>
       <c r="L58" t="n">
-        <v>279.36</v>
+        <v>332.64</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-73.88</v>
+        <v>-77.87</v>
       </c>
       <c r="K59" t="n">
-        <v>-38.98</v>
+        <v>-41.08</v>
       </c>
       <c r="L59" t="n">
-        <v>83.54000000000001</v>
+        <v>88.04000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>18</v>
       </c>
       <c r="J60" t="n">
-        <v>62.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>45.57</v>
+        <v>48.49</v>
       </c>
       <c r="L60" t="n">
-        <v>77.27</v>
+        <v>82.22</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>28.9</v>
+        <v>31.12</v>
       </c>
       <c r="K61" t="n">
-        <v>-60.22</v>
+        <v>-64.84</v>
       </c>
       <c r="L61" t="n">
-        <v>66.8</v>
+        <v>71.93000000000001</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-41.22</v>
+        <v>-44.56</v>
       </c>
       <c r="K62" t="n">
-        <v>45.28</v>
+        <v>48.94</v>
       </c>
       <c r="L62" t="n">
-        <v>61.23</v>
+        <v>66.19</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>16</v>
       </c>
       <c r="J63" t="n">
-        <v>-78.42</v>
+        <v>-85.84999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>-95.84999999999999</v>
+        <v>-104.93</v>
       </c>
       <c r="L63" t="n">
-        <v>123.85</v>
+        <v>135.57</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>-25.48</v>
+        <v>-27.36</v>
       </c>
       <c r="K64" t="n">
-        <v>91.09</v>
+        <v>97.81</v>
       </c>
       <c r="L64" t="n">
-        <v>94.59</v>
+        <v>101.56</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>17</v>
       </c>
       <c r="J65" t="n">
-        <v>-69.31999999999999</v>
+        <v>-79.56</v>
       </c>
       <c r="K65" t="n">
-        <v>57.25</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>89.90000000000001</v>
+        <v>103.18</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-194.11</v>
+        <v>-223.01</v>
       </c>
       <c r="K66" t="n">
-        <v>91.29000000000001</v>
+        <v>104.88</v>
       </c>
       <c r="L66" t="n">
-        <v>214.5</v>
+        <v>246.44</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-117.9</v>
+        <v>-134.15</v>
       </c>
       <c r="K67" t="n">
-        <v>-32.18</v>
+        <v>-36.61</v>
       </c>
       <c r="L67" t="n">
-        <v>122.21</v>
+        <v>139.06</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-207.8</v>
+        <v>-241.59</v>
       </c>
       <c r="K68" t="n">
-        <v>-151.38</v>
+        <v>-175.99</v>
       </c>
       <c r="L68" t="n">
-        <v>257.09</v>
+        <v>298.9</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>20</v>
       </c>
       <c r="J69" t="n">
-        <v>136.27</v>
+        <v>161.54</v>
       </c>
       <c r="K69" t="n">
-        <v>20.81</v>
+        <v>24.66</v>
       </c>
       <c r="L69" t="n">
-        <v>137.85</v>
+        <v>163.41</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>-189.34</v>
+        <v>-223.05</v>
       </c>
       <c r="K70" t="n">
-        <v>-43.08</v>
+        <v>-50.75</v>
       </c>
       <c r="L70" t="n">
-        <v>194.18</v>
+        <v>228.75</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>-355.26</v>
+        <v>-415.47</v>
       </c>
       <c r="K71" t="n">
-        <v>339.03</v>
+        <v>396.48</v>
       </c>
       <c r="L71" t="n">
-        <v>491.07</v>
+        <v>574.29</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>18</v>
       </c>
       <c r="J72" t="n">
-        <v>-60.43</v>
+        <v>-72.67</v>
       </c>
       <c r="K72" t="n">
-        <v>-148.12</v>
+        <v>-178.12</v>
       </c>
       <c r="L72" t="n">
-        <v>159.97</v>
+        <v>192.37</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>20</v>
       </c>
       <c r="J73" t="n">
-        <v>235.77</v>
+        <v>277.92</v>
       </c>
       <c r="K73" t="n">
-        <v>29.72</v>
+        <v>35.04</v>
       </c>
       <c r="L73" t="n">
-        <v>237.63</v>
+        <v>280.12</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>18</v>
       </c>
       <c r="J74" t="n">
-        <v>13.57</v>
+        <v>14.41</v>
       </c>
       <c r="K74" t="n">
-        <v>-60.8</v>
+        <v>-64.56999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>62.29</v>
+        <v>66.16</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>21</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.25</v>
+        <v>-10.73</v>
       </c>
       <c r="K75" t="n">
-        <v>-127.55</v>
+        <v>-133.47</v>
       </c>
       <c r="L75" t="n">
-        <v>127.96</v>
+        <v>133.9</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>-25.18</v>
+        <v>-27.11</v>
       </c>
       <c r="K76" t="n">
-        <v>-160.59</v>
+        <v>-172.87</v>
       </c>
       <c r="L76" t="n">
-        <v>162.55</v>
+        <v>174.98</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>16</v>
       </c>
       <c r="J77" t="n">
-        <v>121.01</v>
+        <v>132.57</v>
       </c>
       <c r="K77" t="n">
-        <v>-213.28</v>
+        <v>-233.67</v>
       </c>
       <c r="L77" t="n">
-        <v>245.22</v>
+        <v>268.66</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>-59.11</v>
+        <v>-64.81999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>83.27</v>
+        <v>91.33</v>
       </c>
       <c r="L78" t="n">
-        <v>102.12</v>
+        <v>112</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>40.19</v>
+        <v>43.6</v>
       </c>
       <c r="K79" t="n">
-        <v>64.02</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>75.59</v>
+        <v>82.01000000000001</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>19</v>
       </c>
       <c r="J80" t="n">
-        <v>113.42</v>
+        <v>128.68</v>
       </c>
       <c r="K80" t="n">
-        <v>18.53</v>
+        <v>21.03</v>
       </c>
       <c r="L80" t="n">
-        <v>114.92</v>
+        <v>130.39</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>232.86</v>
+        <v>269.76</v>
       </c>
       <c r="K81" t="n">
-        <v>3.35</v>
+        <v>3.88</v>
       </c>
       <c r="L81" t="n">
-        <v>232.88</v>
+        <v>269.79</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-98.89</v>
+        <v>-111.95</v>
       </c>
       <c r="K82" t="n">
-        <v>87.45999999999999</v>
+        <v>99.01000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>132.02</v>
+        <v>149.45</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>17</v>
       </c>
       <c r="J83" t="n">
-        <v>-185.02</v>
+        <v>-219.52</v>
       </c>
       <c r="K83" t="n">
-        <v>-126.91</v>
+        <v>-150.57</v>
       </c>
       <c r="L83" t="n">
-        <v>224.36</v>
+        <v>266.2</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>20</v>
       </c>
       <c r="J84" t="n">
-        <v>75.48999999999999</v>
+        <v>89.22</v>
       </c>
       <c r="K84" t="n">
-        <v>-48.08</v>
+        <v>-56.83</v>
       </c>
       <c r="L84" t="n">
-        <v>89.5</v>
+        <v>105.78</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>35.8</v>
+        <v>41.79</v>
       </c>
       <c r="K85" t="n">
-        <v>181.86</v>
+        <v>212.28</v>
       </c>
       <c r="L85" t="n">
-        <v>185.35</v>
+        <v>216.35</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-103.99</v>
+        <v>-123.71</v>
       </c>
       <c r="K86" t="n">
-        <v>-329.85</v>
+        <v>-392.41</v>
       </c>
       <c r="L86" t="n">
-        <v>345.85</v>
+        <v>411.45</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>170.49</v>
+        <v>204.06</v>
       </c>
       <c r="K87" t="n">
-        <v>165.11</v>
+        <v>197.62</v>
       </c>
       <c r="L87" t="n">
-        <v>237.33</v>
+        <v>284.06</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>17</v>
       </c>
       <c r="J88" t="n">
-        <v>242.14</v>
+        <v>289.46</v>
       </c>
       <c r="K88" t="n">
-        <v>-32.49</v>
+        <v>-38.84</v>
       </c>
       <c r="L88" t="n">
-        <v>244.31</v>
+        <v>292.05</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-22.xlsx
+++ b/output/2025-08-22.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="F14" t="n">
-        <v>7.72</v>
+        <v>8.18</v>
       </c>
       <c r="G14" t="n">
-        <v>168.4</v>
+        <v>162.3</v>
       </c>
       <c r="H14" t="n">
-        <v>81.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>55.5</v>
+        <v>-10.41</v>
       </c>
       <c r="K14" t="n">
-        <v>-39.33</v>
+        <v>41.25</v>
       </c>
       <c r="L14" t="n">
-        <v>68.03</v>
+        <v>42.55</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:00:52</t>
+          <t>06:02:45</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="F15" t="n">
-        <v>7.64</v>
+        <v>7.19</v>
       </c>
       <c r="G15" t="n">
-        <v>160.8</v>
+        <v>164.9</v>
       </c>
       <c r="H15" t="n">
-        <v>90.5</v>
+        <v>76.7</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>-96.98</v>
+        <v>5.37</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.08</v>
+        <v>-31.78</v>
       </c>
       <c r="L15" t="n">
-        <v>97.23999999999999</v>
+        <v>32.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:03:27</t>
+          <t>06:03:24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.51</v>
+        <v>3.03</v>
       </c>
       <c r="F16" t="n">
-        <v>7.43</v>
+        <v>7.46</v>
       </c>
       <c r="G16" t="n">
-        <v>171.8</v>
+        <v>161.1</v>
       </c>
       <c r="H16" t="n">
-        <v>81.40000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-75.42</v>
+        <v>-42.77</v>
       </c>
       <c r="K16" t="n">
-        <v>-17.5</v>
+        <v>57.12</v>
       </c>
       <c r="L16" t="n">
-        <v>77.42</v>
+        <v>71.36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:06:49</t>
+          <t>06:07:18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="F17" t="n">
-        <v>7.96</v>
+        <v>7.86</v>
       </c>
       <c r="G17" t="n">
-        <v>171.3</v>
+        <v>171.9</v>
       </c>
       <c r="H17" t="n">
-        <v>91.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>112.51</v>
+        <v>52.85</v>
       </c>
       <c r="K17" t="n">
-        <v>124.04</v>
+        <v>12.03</v>
       </c>
       <c r="L17" t="n">
-        <v>167.46</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:08:25</t>
+          <t>06:10:00</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.82</v>
+        <v>1.46</v>
       </c>
       <c r="F18" t="n">
-        <v>7.53</v>
+        <v>7.78</v>
       </c>
       <c r="G18" t="n">
-        <v>165.8</v>
+        <v>133.9</v>
       </c>
       <c r="H18" t="n">
-        <v>83.5</v>
+        <v>79.3</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>-100.96</v>
+        <v>18.46</v>
       </c>
       <c r="K18" t="n">
-        <v>0.84</v>
+        <v>65.25</v>
       </c>
       <c r="L18" t="n">
-        <v>100.96</v>
+        <v>67.81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:10:31</t>
+          <t>06:11:16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.01</v>
+        <v>1.73</v>
       </c>
       <c r="F19" t="n">
-        <v>7.23</v>
+        <v>7.6</v>
       </c>
       <c r="G19" t="n">
-        <v>150.3</v>
+        <v>160.1</v>
       </c>
       <c r="H19" t="n">
-        <v>86.5</v>
+        <v>84</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>65.59</v>
+        <v>-24.59</v>
       </c>
       <c r="K19" t="n">
-        <v>-73.94</v>
+        <v>-38.53</v>
       </c>
       <c r="L19" t="n">
-        <v>98.84</v>
+        <v>45.71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:15:48</t>
+          <t>06:17:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="F20" t="n">
-        <v>7.82</v>
+        <v>7.58</v>
       </c>
       <c r="G20" t="n">
-        <v>155.3</v>
+        <v>159.9</v>
       </c>
       <c r="H20" t="n">
-        <v>85.2</v>
+        <v>94.2</v>
       </c>
       <c r="I20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>-38.23</v>
+        <v>152.99</v>
       </c>
       <c r="K20" t="n">
-        <v>-76.59999999999999</v>
+        <v>-53.2</v>
       </c>
       <c r="L20" t="n">
-        <v>85.61</v>
+        <v>161.97</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:18:04</t>
+          <t>06:19:28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.84</v>
+        <v>1.47</v>
       </c>
       <c r="F21" t="n">
-        <v>7.28</v>
+        <v>7.95</v>
       </c>
       <c r="G21" t="n">
-        <v>157.1</v>
+        <v>149.9</v>
       </c>
       <c r="H21" t="n">
-        <v>87.40000000000001</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-106.86</v>
+        <v>-6.61</v>
       </c>
       <c r="K21" t="n">
-        <v>-126.82</v>
+        <v>-110.88</v>
       </c>
       <c r="L21" t="n">
-        <v>165.84</v>
+        <v>111.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:19:33</t>
+          <t>06:20:49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="F22" t="n">
-        <v>7.61</v>
+        <v>7.92</v>
       </c>
       <c r="G22" t="n">
-        <v>158.9</v>
+        <v>153.6</v>
       </c>
       <c r="H22" t="n">
-        <v>78.59999999999999</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>177.88</v>
+        <v>16.89</v>
       </c>
       <c r="K22" t="n">
-        <v>-29.16</v>
+        <v>59.31</v>
       </c>
       <c r="L22" t="n">
-        <v>180.25</v>
+        <v>61.67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:24:30</t>
+          <t>06:26:38</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.24</v>
+        <v>1.73</v>
       </c>
       <c r="F23" t="n">
-        <v>7.86</v>
+        <v>7.7</v>
       </c>
       <c r="G23" t="n">
-        <v>165.6</v>
+        <v>168.5</v>
       </c>
       <c r="H23" t="n">
-        <v>82.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>-340.9</v>
+        <v>3.68</v>
       </c>
       <c r="K23" t="n">
-        <v>9.09</v>
+        <v>-138.87</v>
       </c>
       <c r="L23" t="n">
-        <v>341.02</v>
+        <v>138.92</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:25:56</t>
+          <t>06:28:26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.72</v>
+        <v>2.03</v>
       </c>
       <c r="F24" t="n">
-        <v>7.03</v>
+        <v>7.78</v>
       </c>
       <c r="G24" t="n">
-        <v>156.4</v>
+        <v>155.9</v>
       </c>
       <c r="H24" t="n">
-        <v>84.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>313.85</v>
+        <v>-120.92</v>
       </c>
       <c r="K24" t="n">
-        <v>-191.74</v>
+        <v>58.34</v>
       </c>
       <c r="L24" t="n">
-        <v>367.78</v>
+        <v>134.26</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:28:19</t>
+          <t>06:30:03</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.45</v>
+        <v>2.23</v>
       </c>
       <c r="F25" t="n">
-        <v>7.35</v>
+        <v>7.29</v>
       </c>
       <c r="G25" t="n">
-        <v>174.4</v>
+        <v>178.4</v>
       </c>
       <c r="H25" t="n">
-        <v>89.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="I25" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>-115.9</v>
+        <v>13.02</v>
       </c>
       <c r="K25" t="n">
-        <v>-46.46</v>
+        <v>106.57</v>
       </c>
       <c r="L25" t="n">
-        <v>124.87</v>
+        <v>107.36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:34:14</t>
+          <t>06:33:48</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.79</v>
+        <v>2.08</v>
       </c>
       <c r="F26" t="n">
-        <v>7.13</v>
+        <v>7.89</v>
       </c>
       <c r="G26" t="n">
-        <v>156.3</v>
+        <v>162</v>
       </c>
       <c r="H26" t="n">
-        <v>89.3</v>
+        <v>86.5</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>150.4</v>
+        <v>54.25</v>
       </c>
       <c r="K26" t="n">
-        <v>15.67</v>
+        <v>146.72</v>
       </c>
       <c r="L26" t="n">
-        <v>151.21</v>
+        <v>156.43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:36:17</t>
+          <t>06:35:08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.05</v>
+        <v>1.46</v>
       </c>
       <c r="F27" t="n">
-        <v>6.89</v>
+        <v>7.55</v>
       </c>
       <c r="G27" t="n">
-        <v>160.4</v>
+        <v>160</v>
       </c>
       <c r="H27" t="n">
-        <v>87</v>
+        <v>86.7</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>327.72</v>
+        <v>302.73</v>
       </c>
       <c r="K27" t="n">
-        <v>-149.02</v>
+        <v>142.07</v>
       </c>
       <c r="L27" t="n">
-        <v>360.01</v>
+        <v>334.41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:37:27</t>
+          <t>06:36:58</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="F28" t="n">
         <v>7.55</v>
       </c>
       <c r="G28" t="n">
-        <v>159.6</v>
+        <v>160.3</v>
       </c>
       <c r="H28" t="n">
-        <v>90.5</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>191.01</v>
+        <v>78.23</v>
       </c>
       <c r="K28" t="n">
-        <v>46.91</v>
+        <v>150.24</v>
       </c>
       <c r="L28" t="n">
-        <v>196.68</v>
+        <v>169.39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:47:16</t>
+          <t>06:49:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.02</v>
+        <v>1.28</v>
       </c>
       <c r="F29" t="n">
-        <v>7.52</v>
+        <v>7.79</v>
       </c>
       <c r="G29" t="n">
-        <v>157.5</v>
+        <v>155.1</v>
       </c>
       <c r="H29" t="n">
-        <v>90.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-25.73</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>78.20999999999999</v>
+        <v>-43.81</v>
       </c>
       <c r="L29" t="n">
-        <v>82.33</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:48:30</t>
+          <t>06:52:13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.47</v>
+        <v>1.82</v>
       </c>
       <c r="F30" t="n">
-        <v>7.45</v>
+        <v>7.48</v>
       </c>
       <c r="G30" t="n">
-        <v>169.5</v>
+        <v>167.2</v>
       </c>
       <c r="H30" t="n">
-        <v>87.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-14.43</v>
+        <v>-15.91</v>
       </c>
       <c r="K30" t="n">
-        <v>29.84</v>
+        <v>53.32</v>
       </c>
       <c r="L30" t="n">
-        <v>33.15</v>
+        <v>55.65</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:49:39</t>
+          <t>06:52:57</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="F31" t="n">
-        <v>7.72</v>
+        <v>7.6</v>
       </c>
       <c r="G31" t="n">
-        <v>163.7</v>
+        <v>157.8</v>
       </c>
       <c r="H31" t="n">
-        <v>82.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="I31" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-61.79</v>
+        <v>-25.52</v>
       </c>
       <c r="K31" t="n">
-        <v>32.31</v>
+        <v>-40.69</v>
       </c>
       <c r="L31" t="n">
-        <v>69.73</v>
+        <v>48.03</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:54:57</t>
+          <t>06:57:05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="F32" t="n">
-        <v>7.63</v>
+        <v>7.18</v>
       </c>
       <c r="G32" t="n">
-        <v>161.9</v>
+        <v>159.3</v>
       </c>
       <c r="H32" t="n">
-        <v>82.59999999999999</v>
+        <v>92</v>
       </c>
       <c r="I32" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>97.81</v>
+        <v>15.67</v>
       </c>
       <c r="K32" t="n">
-        <v>-105.15</v>
+        <v>77.03</v>
       </c>
       <c r="L32" t="n">
-        <v>143.61</v>
+        <v>78.61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:57:19</t>
+          <t>06:58:23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.96</v>
+        <v>1.81</v>
       </c>
       <c r="F33" t="n">
-        <v>7.46</v>
+        <v>8.27</v>
       </c>
       <c r="G33" t="n">
-        <v>167.7</v>
+        <v>170</v>
       </c>
       <c r="H33" t="n">
-        <v>88.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>51.02</v>
+        <v>42.21</v>
       </c>
       <c r="K33" t="n">
-        <v>82.61</v>
+        <v>-19.41</v>
       </c>
       <c r="L33" t="n">
-        <v>97.09999999999999</v>
+        <v>46.46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:58:24</t>
+          <t>07:00:37</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.16</v>
+        <v>1.81</v>
       </c>
       <c r="F34" t="n">
-        <v>6.95</v>
+        <v>7.75</v>
       </c>
       <c r="G34" t="n">
-        <v>144.5</v>
+        <v>163</v>
       </c>
       <c r="H34" t="n">
-        <v>86.09999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>89.81999999999999</v>
+        <v>-35.48</v>
       </c>
       <c r="K34" t="n">
-        <v>-51.27</v>
+        <v>13.56</v>
       </c>
       <c r="L34" t="n">
-        <v>103.42</v>
+        <v>37.98</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:03:01</t>
+          <t>07:06:02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="F35" t="n">
-        <v>7.45</v>
+        <v>7.7</v>
       </c>
       <c r="G35" t="n">
-        <v>156</v>
+        <v>165.7</v>
       </c>
       <c r="H35" t="n">
-        <v>78.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>-35.73</v>
+        <v>60</v>
       </c>
       <c r="K35" t="n">
-        <v>78.03</v>
+        <v>56.38</v>
       </c>
       <c r="L35" t="n">
-        <v>85.81999999999999</v>
+        <v>82.33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:05:20</t>
+          <t>07:06:32</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.07</v>
+        <v>2.32</v>
       </c>
       <c r="F36" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
       <c r="G36" t="n">
-        <v>152.9</v>
+        <v>157.1</v>
       </c>
       <c r="H36" t="n">
-        <v>87.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>-151.69</v>
+        <v>93.81</v>
       </c>
       <c r="K36" t="n">
-        <v>7.8</v>
+        <v>-45.18</v>
       </c>
       <c r="L36" t="n">
-        <v>151.89</v>
+        <v>104.12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:06:28</t>
+          <t>07:08:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.3</v>
+        <v>1.96</v>
       </c>
       <c r="F37" t="n">
-        <v>7.92</v>
+        <v>7.44</v>
       </c>
       <c r="G37" t="n">
-        <v>155.4</v>
+        <v>148</v>
       </c>
       <c r="H37" t="n">
-        <v>90.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>10.15</v>
+        <v>1.69</v>
       </c>
       <c r="K37" t="n">
-        <v>251.07</v>
+        <v>0.63</v>
       </c>
       <c r="L37" t="n">
-        <v>251.28</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:10:50</t>
+          <t>07:14:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="F38" t="n">
-        <v>7.45</v>
+        <v>7.36</v>
       </c>
       <c r="G38" t="n">
-        <v>158.5</v>
+        <v>182.9</v>
       </c>
       <c r="H38" t="n">
-        <v>86.3</v>
+        <v>86.5</v>
       </c>
       <c r="I38" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-88.95999999999999</v>
+        <v>-126.54</v>
       </c>
       <c r="K38" t="n">
-        <v>-87.73999999999999</v>
+        <v>52.75</v>
       </c>
       <c r="L38" t="n">
-        <v>124.95</v>
+        <v>137.09</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:13:01</t>
+          <t>07:15:19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="F39" t="n">
-        <v>7.45</v>
+        <v>7.12</v>
       </c>
       <c r="G39" t="n">
-        <v>162.6</v>
+        <v>172.6</v>
       </c>
       <c r="H39" t="n">
-        <v>88.59999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="I39" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-130.89</v>
+        <v>-192.3</v>
       </c>
       <c r="K39" t="n">
-        <v>-118.51</v>
+        <v>-58.42</v>
       </c>
       <c r="L39" t="n">
-        <v>176.57</v>
+        <v>200.98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:14:06</t>
+          <t>07:17:15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.51</v>
+        <v>2.01</v>
       </c>
       <c r="F40" t="n">
-        <v>8.130000000000001</v>
+        <v>7.21</v>
       </c>
       <c r="G40" t="n">
-        <v>172.6</v>
+        <v>144.1</v>
       </c>
       <c r="H40" t="n">
-        <v>89.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-90.98</v>
+        <v>68.22</v>
       </c>
       <c r="K40" t="n">
-        <v>-239.2</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>255.92</v>
+        <v>93.83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:18:04</t>
+          <t>07:22:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="F41" t="n">
-        <v>7.86</v>
+        <v>6.93</v>
       </c>
       <c r="G41" t="n">
-        <v>161.3</v>
+        <v>151.9</v>
       </c>
       <c r="H41" t="n">
-        <v>82.59999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>30.67</v>
+        <v>-137.51</v>
       </c>
       <c r="K41" t="n">
-        <v>357.59</v>
+        <v>231.56</v>
       </c>
       <c r="L41" t="n">
-        <v>358.9</v>
+        <v>269.31</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:19:20</t>
+          <t>07:23:54</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.44</v>
+        <v>2.54</v>
       </c>
       <c r="F42" t="n">
-        <v>7.89</v>
+        <v>7.91</v>
       </c>
       <c r="G42" t="n">
-        <v>172.1</v>
+        <v>147.4</v>
       </c>
       <c r="H42" t="n">
-        <v>88.40000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>2.43</v>
+        <v>-210.37</v>
       </c>
       <c r="K42" t="n">
-        <v>-322.76</v>
+        <v>2.19</v>
       </c>
       <c r="L42" t="n">
-        <v>322.77</v>
+        <v>210.38</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:21:53</t>
+          <t>07:24:32</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="F43" t="n">
-        <v>7.33</v>
+        <v>7.18</v>
       </c>
       <c r="G43" t="n">
-        <v>174.7</v>
+        <v>159.5</v>
       </c>
       <c r="H43" t="n">
-        <v>90.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>60.2</v>
+        <v>147.15</v>
       </c>
       <c r="K43" t="n">
-        <v>-304.72</v>
+        <v>40.52</v>
       </c>
       <c r="L43" t="n">
-        <v>310.61</v>
+        <v>152.62</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:32:11</t>
+          <t>07:36:20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.86</v>
+        <v>2.88</v>
       </c>
       <c r="F44" t="n">
-        <v>7.07</v>
+        <v>7.73</v>
       </c>
       <c r="G44" t="n">
-        <v>153.7</v>
+        <v>158.1</v>
       </c>
       <c r="H44" t="n">
-        <v>83.59999999999999</v>
+        <v>86.8</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-44.16</v>
+        <v>-18.51</v>
       </c>
       <c r="K44" t="n">
-        <v>62.65</v>
+        <v>60.35</v>
       </c>
       <c r="L44" t="n">
-        <v>76.65000000000001</v>
+        <v>63.12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:34:36</t>
+          <t>07:37:07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.31</v>
+        <v>2.14</v>
       </c>
       <c r="F45" t="n">
-        <v>7.36</v>
+        <v>7.38</v>
       </c>
       <c r="G45" t="n">
-        <v>160.1</v>
+        <v>151.8</v>
       </c>
       <c r="H45" t="n">
-        <v>83</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>44.09</v>
+        <v>0.34</v>
       </c>
       <c r="K45" t="n">
-        <v>37.34</v>
+        <v>43.2</v>
       </c>
       <c r="L45" t="n">
-        <v>57.77</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:36:31</t>
+          <t>07:38:48</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="F46" t="n">
-        <v>7.29</v>
+        <v>7.98</v>
       </c>
       <c r="G46" t="n">
-        <v>156.7</v>
+        <v>160.7</v>
       </c>
       <c r="H46" t="n">
-        <v>87.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>-40.39</v>
+        <v>32.19</v>
       </c>
       <c r="K46" t="n">
-        <v>27.69</v>
+        <v>-59.99</v>
       </c>
       <c r="L46" t="n">
-        <v>48.97</v>
+        <v>68.08</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:40:51</t>
+          <t>07:42:57</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.51</v>
+        <v>1.75</v>
       </c>
       <c r="F47" t="n">
-        <v>7.71</v>
+        <v>6.98</v>
       </c>
       <c r="G47" t="n">
-        <v>162.6</v>
+        <v>159.9</v>
       </c>
       <c r="H47" t="n">
-        <v>88.90000000000001</v>
+        <v>85.5</v>
       </c>
       <c r="I47" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>113.95</v>
+        <v>33.03</v>
       </c>
       <c r="K47" t="n">
-        <v>3.91</v>
+        <v>71.95999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>114.02</v>
+        <v>79.17</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:41:58</t>
+          <t>07:44:31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="F48" t="n">
-        <v>7.77</v>
+        <v>7.99</v>
       </c>
       <c r="G48" t="n">
-        <v>153</v>
+        <v>149.1</v>
       </c>
       <c r="H48" t="n">
-        <v>88.7</v>
+        <v>87.2</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>-16.66</v>
+        <v>32.22</v>
       </c>
       <c r="K48" t="n">
-        <v>93.92</v>
+        <v>27.66</v>
       </c>
       <c r="L48" t="n">
-        <v>95.39</v>
+        <v>42.47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:43:13</t>
+          <t>07:46:14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.6</v>
+        <v>2.85</v>
       </c>
       <c r="F49" t="n">
-        <v>7.21</v>
+        <v>7.06</v>
       </c>
       <c r="G49" t="n">
-        <v>148.8</v>
+        <v>176.4</v>
       </c>
       <c r="H49" t="n">
-        <v>83.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="I49" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-139.5</v>
+        <v>-79.19</v>
       </c>
       <c r="K49" t="n">
-        <v>-113.73</v>
+        <v>-94.75</v>
       </c>
       <c r="L49" t="n">
-        <v>179.99</v>
+        <v>123.49</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:46:56</t>
+          <t>07:49:56</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="F50" t="n">
-        <v>7.42</v>
+        <v>7.75</v>
       </c>
       <c r="G50" t="n">
-        <v>157.1</v>
+        <v>168.8</v>
       </c>
       <c r="H50" t="n">
-        <v>88</v>
+        <v>85.2</v>
       </c>
       <c r="I50" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-93.31999999999999</v>
+        <v>-32.04</v>
       </c>
       <c r="K50" t="n">
-        <v>-20.12</v>
+        <v>119.63</v>
       </c>
       <c r="L50" t="n">
-        <v>95.47</v>
+        <v>123.84</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:48:21</t>
+          <t>07:51:43</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.89</v>
+        <v>2.07</v>
       </c>
       <c r="F51" t="n">
-        <v>7.6</v>
+        <v>7.42</v>
       </c>
       <c r="G51" t="n">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="H51" t="n">
-        <v>86.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>99.70999999999999</v>
+        <v>-110.06</v>
       </c>
       <c r="K51" t="n">
-        <v>18.17</v>
+        <v>-45.92</v>
       </c>
       <c r="L51" t="n">
-        <v>101.35</v>
+        <v>119.25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:50:22</t>
+          <t>07:53:59</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="F52" t="n">
-        <v>7.13</v>
+        <v>7.26</v>
       </c>
       <c r="G52" t="n">
-        <v>167.4</v>
+        <v>162.4</v>
       </c>
       <c r="H52" t="n">
-        <v>87</v>
+        <v>83.8</v>
       </c>
       <c r="I52" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>116.28</v>
+        <v>-88.62</v>
       </c>
       <c r="K52" t="n">
-        <v>-37.53</v>
+        <v>-16.94</v>
       </c>
       <c r="L52" t="n">
-        <v>122.19</v>
+        <v>90.23</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:56:09</t>
+          <t>07:59:04</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.55</v>
+        <v>1.97</v>
       </c>
       <c r="F53" t="n">
-        <v>7.62</v>
+        <v>7.08</v>
       </c>
       <c r="G53" t="n">
-        <v>168.4</v>
+        <v>159.4</v>
       </c>
       <c r="H53" t="n">
-        <v>84.3</v>
+        <v>86.3</v>
       </c>
       <c r="I53" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>218.04</v>
+        <v>156.23</v>
       </c>
       <c r="K53" t="n">
-        <v>-120.92</v>
+        <v>-18.52</v>
       </c>
       <c r="L53" t="n">
-        <v>249.33</v>
+        <v>157.32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:57:52</t>
+          <t>08:00:10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.83</v>
+        <v>1.59</v>
       </c>
       <c r="F54" t="n">
-        <v>7.95</v>
+        <v>7.48</v>
       </c>
       <c r="G54" t="n">
-        <v>154.6</v>
+        <v>173.5</v>
       </c>
       <c r="H54" t="n">
-        <v>90.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>59.11</v>
+        <v>-87.98999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>129.51</v>
+        <v>107.49</v>
       </c>
       <c r="L54" t="n">
-        <v>142.37</v>
+        <v>138.91</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:58:44</t>
+          <t>08:01:50</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="F55" t="n">
-        <v>7.23</v>
+        <v>7.22</v>
       </c>
       <c r="G55" t="n">
-        <v>152.2</v>
+        <v>154.8</v>
       </c>
       <c r="H55" t="n">
-        <v>84.7</v>
+        <v>86.8</v>
       </c>
       <c r="I55" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>-157.09</v>
+        <v>54.06</v>
       </c>
       <c r="K55" t="n">
-        <v>250.25</v>
+        <v>-103.98</v>
       </c>
       <c r="L55" t="n">
-        <v>295.47</v>
+        <v>117.19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:03:17</t>
+          <t>08:07:07</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.54</v>
+        <v>2.4</v>
       </c>
       <c r="F56" t="n">
-        <v>7.08</v>
+        <v>6.99</v>
       </c>
       <c r="G56" t="n">
-        <v>153.8</v>
+        <v>158.4</v>
       </c>
       <c r="H56" t="n">
-        <v>82</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>228.06</v>
+        <v>101.1</v>
       </c>
       <c r="K56" t="n">
-        <v>124.09</v>
+        <v>-26.1</v>
       </c>
       <c r="L56" t="n">
-        <v>259.63</v>
+        <v>104.42</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:05:16</t>
+          <t>08:10:00</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="F57" t="n">
-        <v>7.23</v>
+        <v>7.75</v>
       </c>
       <c r="G57" t="n">
-        <v>162.5</v>
+        <v>163</v>
       </c>
       <c r="H57" t="n">
-        <v>86.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>-141.95</v>
+        <v>107.94</v>
       </c>
       <c r="K57" t="n">
-        <v>214.34</v>
+        <v>-172.03</v>
       </c>
       <c r="L57" t="n">
-        <v>257.09</v>
+        <v>203.09</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:07:20</t>
+          <t>08:10:50</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.09</v>
+        <v>1.88</v>
       </c>
       <c r="F58" t="n">
-        <v>7.62</v>
+        <v>8.32</v>
       </c>
       <c r="G58" t="n">
-        <v>166.7</v>
+        <v>154.7</v>
       </c>
       <c r="H58" t="n">
-        <v>84</v>
+        <v>89.7</v>
       </c>
       <c r="I58" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>-197.46</v>
+        <v>135.82</v>
       </c>
       <c r="K58" t="n">
-        <v>-267.69</v>
+        <v>-92.87</v>
       </c>
       <c r="L58" t="n">
-        <v>332.64</v>
+        <v>164.53</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:18:53</t>
+          <t>08:22:02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="F59" t="n">
-        <v>7.36</v>
+        <v>7.62</v>
       </c>
       <c r="G59" t="n">
-        <v>171.6</v>
+        <v>172.2</v>
       </c>
       <c r="H59" t="n">
-        <v>89.3</v>
+        <v>88</v>
       </c>
       <c r="I59" t="n">
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>-77.87</v>
+        <v>4.1</v>
       </c>
       <c r="K59" t="n">
-        <v>-41.08</v>
+        <v>-43.31</v>
       </c>
       <c r="L59" t="n">
-        <v>88.04000000000001</v>
+        <v>43.5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:19:38</t>
+          <t>08:24:29</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="F60" t="n">
-        <v>7.77</v>
+        <v>7.05</v>
       </c>
       <c r="G60" t="n">
-        <v>159.8</v>
+        <v>147.7</v>
       </c>
       <c r="H60" t="n">
-        <v>86.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>66.40000000000001</v>
+        <v>-5.54</v>
       </c>
       <c r="K60" t="n">
-        <v>48.49</v>
+        <v>-55.47</v>
       </c>
       <c r="L60" t="n">
-        <v>82.22</v>
+        <v>55.74</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:20:50</t>
+          <t>08:26:33</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.19</v>
+        <v>1.78</v>
       </c>
       <c r="F61" t="n">
-        <v>7.22</v>
+        <v>8.01</v>
       </c>
       <c r="G61" t="n">
-        <v>160.4</v>
+        <v>157.3</v>
       </c>
       <c r="H61" t="n">
-        <v>89.8</v>
+        <v>76.8</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>31.12</v>
+        <v>21.95</v>
       </c>
       <c r="K61" t="n">
-        <v>-64.84</v>
+        <v>29.37</v>
       </c>
       <c r="L61" t="n">
-        <v>71.93000000000001</v>
+        <v>36.67</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:26:56</t>
+          <t>08:30:58</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="F62" t="n">
-        <v>7.74</v>
+        <v>7.34</v>
       </c>
       <c r="G62" t="n">
-        <v>154.2</v>
+        <v>162.9</v>
       </c>
       <c r="H62" t="n">
-        <v>79.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-44.56</v>
+        <v>-64.28</v>
       </c>
       <c r="K62" t="n">
-        <v>48.94</v>
+        <v>33.64</v>
       </c>
       <c r="L62" t="n">
-        <v>66.19</v>
+        <v>72.56</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:27:34</t>
+          <t>08:31:39</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.24</v>
+        <v>1.65</v>
       </c>
       <c r="F63" t="n">
-        <v>7.7</v>
+        <v>6.82</v>
       </c>
       <c r="G63" t="n">
-        <v>157.2</v>
+        <v>158.1</v>
       </c>
       <c r="H63" t="n">
-        <v>80.09999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-85.84999999999999</v>
+        <v>-50.15</v>
       </c>
       <c r="K63" t="n">
-        <v>-104.93</v>
+        <v>37.18</v>
       </c>
       <c r="L63" t="n">
-        <v>135.57</v>
+        <v>62.43</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:29:04</t>
+          <t>08:33:43</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="F64" t="n">
-        <v>7.29</v>
+        <v>7.54</v>
       </c>
       <c r="G64" t="n">
-        <v>152.3</v>
+        <v>158.6</v>
       </c>
       <c r="H64" t="n">
-        <v>84</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-27.36</v>
+        <v>-45.46</v>
       </c>
       <c r="K64" t="n">
-        <v>97.81</v>
+        <v>46.73</v>
       </c>
       <c r="L64" t="n">
-        <v>101.56</v>
+        <v>65.19</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:32:04</t>
+          <t>08:37:38</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.97</v>
+        <v>2.27</v>
       </c>
       <c r="F65" t="n">
-        <v>7.01</v>
+        <v>7.37</v>
       </c>
       <c r="G65" t="n">
-        <v>168.7</v>
+        <v>166.3</v>
       </c>
       <c r="H65" t="n">
-        <v>85.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-79.56</v>
+        <v>82.77</v>
       </c>
       <c r="K65" t="n">
-        <v>65.70999999999999</v>
+        <v>29.87</v>
       </c>
       <c r="L65" t="n">
-        <v>103.18</v>
+        <v>88</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:33:03</t>
+          <t>08:39:24</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="F66" t="n">
-        <v>6.88</v>
+        <v>7.47</v>
       </c>
       <c r="G66" t="n">
-        <v>162.6</v>
+        <v>161.6</v>
       </c>
       <c r="H66" t="n">
-        <v>83.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>-223.01</v>
+        <v>139.07</v>
       </c>
       <c r="K66" t="n">
-        <v>104.88</v>
+        <v>29.94</v>
       </c>
       <c r="L66" t="n">
-        <v>246.44</v>
+        <v>142.26</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:35:44</t>
+          <t>08:40:05</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="F67" t="n">
-        <v>7.19</v>
+        <v>7.32</v>
       </c>
       <c r="G67" t="n">
-        <v>164.3</v>
+        <v>162.7</v>
       </c>
       <c r="H67" t="n">
-        <v>88.2</v>
+        <v>90.2</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-134.15</v>
+        <v>-28.42</v>
       </c>
       <c r="K67" t="n">
-        <v>-36.61</v>
+        <v>109.29</v>
       </c>
       <c r="L67" t="n">
-        <v>139.06</v>
+        <v>112.92</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:39:58</t>
+          <t>08:44:55</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.37</v>
+        <v>2.23</v>
       </c>
       <c r="F68" t="n">
-        <v>7.67</v>
+        <v>7</v>
       </c>
       <c r="G68" t="n">
-        <v>160.3</v>
+        <v>164.4</v>
       </c>
       <c r="H68" t="n">
-        <v>86.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-241.59</v>
+        <v>-78.75</v>
       </c>
       <c r="K68" t="n">
-        <v>-175.99</v>
+        <v>-78.39</v>
       </c>
       <c r="L68" t="n">
-        <v>298.9</v>
+        <v>111.12</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:42:04</t>
+          <t>08:46:48</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.46</v>
+        <v>1.87</v>
       </c>
       <c r="F69" t="n">
-        <v>7.46</v>
+        <v>7.47</v>
       </c>
       <c r="G69" t="n">
-        <v>162.4</v>
+        <v>164.7</v>
       </c>
       <c r="H69" t="n">
-        <v>91.2</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>161.54</v>
+        <v>67.06</v>
       </c>
       <c r="K69" t="n">
-        <v>24.66</v>
+        <v>-67.31</v>
       </c>
       <c r="L69" t="n">
-        <v>163.41</v>
+        <v>95.02</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:44:00</t>
+          <t>08:48:41</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="F70" t="n">
-        <v>7.66</v>
+        <v>7.7</v>
       </c>
       <c r="G70" t="n">
-        <v>160.8</v>
+        <v>149.9</v>
       </c>
       <c r="H70" t="n">
-        <v>89.3</v>
+        <v>93.8</v>
       </c>
       <c r="I70" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-223.05</v>
+        <v>-16.43</v>
       </c>
       <c r="K70" t="n">
-        <v>-50.75</v>
+        <v>-141.06</v>
       </c>
       <c r="L70" t="n">
-        <v>228.75</v>
+        <v>142.01</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:49:37</t>
+          <t>08:53:54</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.82</v>
+        <v>1.61</v>
       </c>
       <c r="F71" t="n">
-        <v>7.65</v>
+        <v>7.72</v>
       </c>
       <c r="G71" t="n">
-        <v>168.6</v>
+        <v>153.9</v>
       </c>
       <c r="H71" t="n">
-        <v>82.5</v>
+        <v>91</v>
       </c>
       <c r="I71" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-415.47</v>
+        <v>-89.51000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>396.48</v>
+        <v>-149.66</v>
       </c>
       <c r="L71" t="n">
-        <v>574.29</v>
+        <v>174.38</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:50:20</t>
+          <t>08:55:49</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.93</v>
+        <v>2.14</v>
       </c>
       <c r="F72" t="n">
-        <v>8.32</v>
+        <v>7.51</v>
       </c>
       <c r="G72" t="n">
-        <v>160.1</v>
+        <v>166.7</v>
       </c>
       <c r="H72" t="n">
-        <v>89.90000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>-72.67</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>-178.12</v>
+        <v>-99.31</v>
       </c>
       <c r="L72" t="n">
-        <v>192.37</v>
+        <v>140.39</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:52:01</t>
+          <t>08:57:47</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.28</v>
+        <v>1.41</v>
       </c>
       <c r="F73" t="n">
-        <v>7.22</v>
+        <v>7.47</v>
       </c>
       <c r="G73" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="H73" t="n">
-        <v>84.5</v>
+        <v>82</v>
       </c>
       <c r="I73" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>277.92</v>
+        <v>115.32</v>
       </c>
       <c r="K73" t="n">
-        <v>35.04</v>
+        <v>-37.62</v>
       </c>
       <c r="L73" t="n">
-        <v>280.12</v>
+        <v>121.3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:03:01</t>
+          <t>09:07:44</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="F74" t="n">
-        <v>7.62</v>
+        <v>8.02</v>
       </c>
       <c r="G74" t="n">
-        <v>176.3</v>
+        <v>144.8</v>
       </c>
       <c r="H74" t="n">
-        <v>85.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="I74" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>14.41</v>
+        <v>-35.09</v>
       </c>
       <c r="K74" t="n">
-        <v>-64.56999999999999</v>
+        <v>-18.85</v>
       </c>
       <c r="L74" t="n">
-        <v>66.16</v>
+        <v>39.83</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:04:19</t>
+          <t>09:10:25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.07</v>
+        <v>1.84</v>
       </c>
       <c r="F75" t="n">
-        <v>7.83</v>
+        <v>7.77</v>
       </c>
       <c r="G75" t="n">
-        <v>157.4</v>
+        <v>146.7</v>
       </c>
       <c r="H75" t="n">
-        <v>83.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-10.73</v>
+        <v>-52.82</v>
       </c>
       <c r="K75" t="n">
-        <v>-133.47</v>
+        <v>6.04</v>
       </c>
       <c r="L75" t="n">
-        <v>133.9</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:05:41</t>
+          <t>09:12:43</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.27</v>
+        <v>2.21</v>
       </c>
       <c r="F76" t="n">
-        <v>7.94</v>
+        <v>7.72</v>
       </c>
       <c r="G76" t="n">
-        <v>161.9</v>
+        <v>156.6</v>
       </c>
       <c r="H76" t="n">
-        <v>89.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>-27.11</v>
+        <v>49</v>
       </c>
       <c r="K76" t="n">
-        <v>-172.87</v>
+        <v>-12.08</v>
       </c>
       <c r="L76" t="n">
-        <v>174.98</v>
+        <v>50.47</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:09:57</t>
+          <t>09:17:17</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="F77" t="n">
-        <v>7.23</v>
+        <v>7.59</v>
       </c>
       <c r="G77" t="n">
-        <v>158.6</v>
+        <v>170.5</v>
       </c>
       <c r="H77" t="n">
-        <v>84.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="I77" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>132.57</v>
+        <v>-28.81</v>
       </c>
       <c r="K77" t="n">
-        <v>-233.67</v>
+        <v>-66.72</v>
       </c>
       <c r="L77" t="n">
-        <v>268.66</v>
+        <v>72.68000000000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:11:13</t>
+          <t>09:18:30</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="F78" t="n">
-        <v>7.97</v>
+        <v>7.72</v>
       </c>
       <c r="G78" t="n">
-        <v>166.2</v>
+        <v>162.1</v>
       </c>
       <c r="H78" t="n">
-        <v>84.8</v>
+        <v>81.2</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J78" t="n">
-        <v>-64.81999999999999</v>
+        <v>48.73</v>
       </c>
       <c r="K78" t="n">
-        <v>91.33</v>
+        <v>105.52</v>
       </c>
       <c r="L78" t="n">
-        <v>112</v>
+        <v>116.23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:12:40</t>
+          <t>09:19:50</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="F79" t="n">
-        <v>7.88</v>
+        <v>8.24</v>
       </c>
       <c r="G79" t="n">
-        <v>166.9</v>
+        <v>154.9</v>
       </c>
       <c r="H79" t="n">
-        <v>86.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>43.6</v>
+        <v>-41.7</v>
       </c>
       <c r="K79" t="n">
-        <v>69.45999999999999</v>
+        <v>54.59</v>
       </c>
       <c r="L79" t="n">
-        <v>82.01000000000001</v>
+        <v>68.69</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:17:07</t>
+          <t>09:24:39</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.95</v>
+        <v>2.18</v>
       </c>
       <c r="F80" t="n">
-        <v>7.81</v>
+        <v>7.64</v>
       </c>
       <c r="G80" t="n">
-        <v>160.9</v>
+        <v>164.1</v>
       </c>
       <c r="H80" t="n">
-        <v>82.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>128.68</v>
+        <v>48.29</v>
       </c>
       <c r="K80" t="n">
-        <v>21.03</v>
+        <v>-67.7</v>
       </c>
       <c r="L80" t="n">
-        <v>130.39</v>
+        <v>83.16</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:18:16</t>
+          <t>09:26:04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="F81" t="n">
-        <v>7.59</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G81" t="n">
-        <v>160.7</v>
+        <v>167.3</v>
       </c>
       <c r="H81" t="n">
-        <v>89.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>269.76</v>
+        <v>-35.24</v>
       </c>
       <c r="K81" t="n">
-        <v>3.88</v>
+        <v>-75.95</v>
       </c>
       <c r="L81" t="n">
-        <v>269.79</v>
+        <v>83.72</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:19:50</t>
+          <t>09:27:58</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="F82" t="n">
-        <v>7.35</v>
+        <v>7.97</v>
       </c>
       <c r="G82" t="n">
-        <v>152.9</v>
+        <v>169.6</v>
       </c>
       <c r="H82" t="n">
-        <v>87.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-111.95</v>
+        <v>-104.18</v>
       </c>
       <c r="K82" t="n">
-        <v>99.01000000000001</v>
+        <v>-10.72</v>
       </c>
       <c r="L82" t="n">
-        <v>149.45</v>
+        <v>104.73</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:24:03</t>
+          <t>09:32:14</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="F83" t="n">
-        <v>6.9</v>
+        <v>8.48</v>
       </c>
       <c r="G83" t="n">
-        <v>162.4</v>
+        <v>167.2</v>
       </c>
       <c r="H83" t="n">
-        <v>85.90000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-219.52</v>
+        <v>129.03</v>
       </c>
       <c r="K83" t="n">
-        <v>-150.57</v>
+        <v>41.11</v>
       </c>
       <c r="L83" t="n">
-        <v>266.2</v>
+        <v>135.42</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:26:22</t>
+          <t>09:33:58</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="F84" t="n">
-        <v>7.83</v>
+        <v>7.89</v>
       </c>
       <c r="G84" t="n">
-        <v>176.7</v>
+        <v>164.1</v>
       </c>
       <c r="H84" t="n">
-        <v>90</v>
+        <v>84.7</v>
       </c>
       <c r="I84" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>89.22</v>
+        <v>81.11</v>
       </c>
       <c r="K84" t="n">
-        <v>-56.83</v>
+        <v>112.31</v>
       </c>
       <c r="L84" t="n">
-        <v>105.78</v>
+        <v>138.54</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:27:08</t>
+          <t>09:34:52</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.93</v>
+        <v>2.45</v>
       </c>
       <c r="F85" t="n">
-        <v>7.26</v>
+        <v>6.98</v>
       </c>
       <c r="G85" t="n">
-        <v>173.5</v>
+        <v>153.3</v>
       </c>
       <c r="H85" t="n">
-        <v>81</v>
+        <v>89.7</v>
       </c>
       <c r="I85" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>41.79</v>
+        <v>-76.48</v>
       </c>
       <c r="K85" t="n">
-        <v>212.28</v>
+        <v>-52</v>
       </c>
       <c r="L85" t="n">
-        <v>216.35</v>
+        <v>92.48999999999999</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:33:10</t>
+          <t>09:38:50</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="F86" t="n">
-        <v>7.7</v>
+        <v>7.71</v>
       </c>
       <c r="G86" t="n">
-        <v>170.1</v>
+        <v>166.7</v>
       </c>
       <c r="H86" t="n">
-        <v>90.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I86" t="n">
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-123.71</v>
+        <v>207.58</v>
       </c>
       <c r="K86" t="n">
-        <v>-392.41</v>
+        <v>74.04000000000001</v>
       </c>
       <c r="L86" t="n">
-        <v>411.45</v>
+        <v>220.39</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:35:27</t>
+          <t>09:40:18</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.53</v>
+        <v>2.13</v>
       </c>
       <c r="F87" t="n">
-        <v>7.21</v>
+        <v>7.83</v>
       </c>
       <c r="G87" t="n">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="H87" t="n">
-        <v>85.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>204.06</v>
+        <v>42.57</v>
       </c>
       <c r="K87" t="n">
-        <v>197.62</v>
+        <v>-154.48</v>
       </c>
       <c r="L87" t="n">
-        <v>284.06</v>
+        <v>160.23</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:37:35</t>
+          <t>09:42:22</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.23</v>
+        <v>2.05</v>
       </c>
       <c r="F88" t="n">
-        <v>7.29</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G88" t="n">
-        <v>171</v>
+        <v>164.9</v>
       </c>
       <c r="H88" t="n">
-        <v>85.2</v>
+        <v>82.3</v>
       </c>
       <c r="I88" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>289.46</v>
+        <v>99.62</v>
       </c>
       <c r="K88" t="n">
-        <v>-38.84</v>
+        <v>-99.88</v>
       </c>
       <c r="L88" t="n">
-        <v>292.05</v>
+        <v>141.07</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-22.xlsx
+++ b/output/2025-08-22.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.41</v>
+        <v>-10.45</v>
       </c>
       <c r="K14" t="n">
-        <v>41.25</v>
+        <v>41.42</v>
       </c>
       <c r="L14" t="n">
-        <v>42.55</v>
+        <v>42.71</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>5.37</v>
+        <v>5.6</v>
       </c>
       <c r="K15" t="n">
-        <v>-31.78</v>
+        <v>-33.1</v>
       </c>
       <c r="L15" t="n">
-        <v>32.24</v>
+        <v>33.57</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-42.77</v>
+        <v>-42.13</v>
       </c>
       <c r="K16" t="n">
-        <v>57.12</v>
+        <v>56.26</v>
       </c>
       <c r="L16" t="n">
-        <v>71.36</v>
+        <v>70.29000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>52.85</v>
+        <v>53.82</v>
       </c>
       <c r="K17" t="n">
-        <v>12.03</v>
+        <v>12.25</v>
       </c>
       <c r="L17" t="n">
-        <v>54.2</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>18.46</v>
+        <v>18.3</v>
       </c>
       <c r="K18" t="n">
-        <v>65.25</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>67.81</v>
+        <v>67.19</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-24.59</v>
+        <v>-25.85</v>
       </c>
       <c r="K19" t="n">
-        <v>-38.53</v>
+        <v>-40.51</v>
       </c>
       <c r="L19" t="n">
-        <v>45.71</v>
+        <v>48.05</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>152.99</v>
+        <v>145.45</v>
       </c>
       <c r="K20" t="n">
-        <v>-53.2</v>
+        <v>-50.58</v>
       </c>
       <c r="L20" t="n">
-        <v>161.97</v>
+        <v>153.99</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.61</v>
+        <v>-6.47</v>
       </c>
       <c r="K21" t="n">
-        <v>-110.88</v>
+        <v>-108.62</v>
       </c>
       <c r="L21" t="n">
-        <v>111.08</v>
+        <v>108.82</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>16.89</v>
+        <v>17.94</v>
       </c>
       <c r="K22" t="n">
-        <v>59.31</v>
+        <v>63.01</v>
       </c>
       <c r="L22" t="n">
-        <v>61.67</v>
+        <v>65.52</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="K23" t="n">
-        <v>-138.87</v>
+        <v>-137.74</v>
       </c>
       <c r="L23" t="n">
-        <v>138.92</v>
+        <v>137.78</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-120.92</v>
+        <v>-120.08</v>
       </c>
       <c r="K24" t="n">
-        <v>58.34</v>
+        <v>57.93</v>
       </c>
       <c r="L24" t="n">
-        <v>134.26</v>
+        <v>133.32</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>13.02</v>
+        <v>13.3</v>
       </c>
       <c r="K25" t="n">
-        <v>106.57</v>
+        <v>108.8</v>
       </c>
       <c r="L25" t="n">
-        <v>107.36</v>
+        <v>109.61</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>54.25</v>
+        <v>55.65</v>
       </c>
       <c r="K26" t="n">
-        <v>146.72</v>
+        <v>150.5</v>
       </c>
       <c r="L26" t="n">
-        <v>156.43</v>
+        <v>160.46</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>302.73</v>
+        <v>286.07</v>
       </c>
       <c r="K27" t="n">
-        <v>142.07</v>
+        <v>134.25</v>
       </c>
       <c r="L27" t="n">
-        <v>334.41</v>
+        <v>316</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>78.23</v>
+        <v>78.89</v>
       </c>
       <c r="K28" t="n">
-        <v>150.24</v>
+        <v>151.5</v>
       </c>
       <c r="L28" t="n">
-        <v>169.39</v>
+        <v>170.81</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.859999999999999</v>
+        <v>-8.91</v>
       </c>
       <c r="K29" t="n">
-        <v>-43.81</v>
+        <v>-44.02</v>
       </c>
       <c r="L29" t="n">
-        <v>44.7</v>
+        <v>44.92</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-15.91</v>
+        <v>-15.64</v>
       </c>
       <c r="K30" t="n">
-        <v>53.32</v>
+        <v>52.41</v>
       </c>
       <c r="L30" t="n">
-        <v>55.65</v>
+        <v>54.69</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-25.52</v>
+        <v>-25.71</v>
       </c>
       <c r="K31" t="n">
-        <v>-40.69</v>
+        <v>-41.01</v>
       </c>
       <c r="L31" t="n">
-        <v>48.03</v>
+        <v>48.41</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>15.67</v>
+        <v>15.55</v>
       </c>
       <c r="K32" t="n">
-        <v>77.03</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>78.61</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>42.21</v>
+        <v>44.28</v>
       </c>
       <c r="K33" t="n">
-        <v>-19.41</v>
+        <v>-20.36</v>
       </c>
       <c r="L33" t="n">
-        <v>46.46</v>
+        <v>48.74</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-35.48</v>
+        <v>-38.85</v>
       </c>
       <c r="K34" t="n">
-        <v>13.56</v>
+        <v>14.84</v>
       </c>
       <c r="L34" t="n">
-        <v>37.98</v>
+        <v>41.59</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>60</v>
+        <v>61.56</v>
       </c>
       <c r="K35" t="n">
-        <v>56.38</v>
+        <v>57.85</v>
       </c>
       <c r="L35" t="n">
-        <v>82.33</v>
+        <v>84.47</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>93.81</v>
+        <v>94.55</v>
       </c>
       <c r="K36" t="n">
-        <v>-45.18</v>
+        <v>-45.54</v>
       </c>
       <c r="L36" t="n">
-        <v>104.12</v>
+        <v>104.94</v>
       </c>
     </row>
     <row r="37">
@@ -1612,7 +1612,7 @@
         <v>0.63</v>
       </c>
       <c r="L37" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-126.54</v>
+        <v>-124.79</v>
       </c>
       <c r="K38" t="n">
-        <v>52.75</v>
+        <v>52.03</v>
       </c>
       <c r="L38" t="n">
-        <v>137.09</v>
+        <v>135.2</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-192.3</v>
+        <v>-182.75</v>
       </c>
       <c r="K39" t="n">
-        <v>-58.42</v>
+        <v>-55.52</v>
       </c>
       <c r="L39" t="n">
-        <v>200.98</v>
+        <v>190.99</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>68.22</v>
+        <v>71.28</v>
       </c>
       <c r="K40" t="n">
-        <v>64.43000000000001</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>93.83</v>
+        <v>98.04000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-137.51</v>
+        <v>-133.28</v>
       </c>
       <c r="K41" t="n">
-        <v>231.56</v>
+        <v>224.44</v>
       </c>
       <c r="L41" t="n">
-        <v>269.31</v>
+        <v>261.04</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-210.37</v>
+        <v>-210.14</v>
       </c>
       <c r="K42" t="n">
         <v>2.19</v>
       </c>
       <c r="L42" t="n">
-        <v>210.38</v>
+        <v>210.16</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>147.15</v>
+        <v>153.06</v>
       </c>
       <c r="K43" t="n">
-        <v>40.52</v>
+        <v>42.15</v>
       </c>
       <c r="L43" t="n">
-        <v>152.62</v>
+        <v>158.75</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-18.51</v>
+        <v>-18.68</v>
       </c>
       <c r="K44" t="n">
-        <v>60.35</v>
+        <v>60.92</v>
       </c>
       <c r="L44" t="n">
-        <v>63.12</v>
+        <v>63.72</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="K45" t="n">
-        <v>43.2</v>
+        <v>44.9</v>
       </c>
       <c r="L45" t="n">
-        <v>43.2</v>
+        <v>44.9</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>32.19</v>
+        <v>31.44</v>
       </c>
       <c r="K46" t="n">
-        <v>-59.99</v>
+        <v>-58.58</v>
       </c>
       <c r="L46" t="n">
-        <v>68.08</v>
+        <v>66.48999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>33.03</v>
+        <v>32.32</v>
       </c>
       <c r="K47" t="n">
-        <v>71.95999999999999</v>
+        <v>70.42</v>
       </c>
       <c r="L47" t="n">
-        <v>79.17</v>
+        <v>77.48999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>32.22</v>
+        <v>34.59</v>
       </c>
       <c r="K48" t="n">
-        <v>27.66</v>
+        <v>29.7</v>
       </c>
       <c r="L48" t="n">
-        <v>42.47</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-79.19</v>
+        <v>-75.84</v>
       </c>
       <c r="K49" t="n">
-        <v>-94.75</v>
+        <v>-90.73999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>123.49</v>
+        <v>118.26</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-32.04</v>
+        <v>-31.01</v>
       </c>
       <c r="K50" t="n">
-        <v>119.63</v>
+        <v>115.75</v>
       </c>
       <c r="L50" t="n">
-        <v>123.84</v>
+        <v>119.83</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-110.06</v>
+        <v>-107.42</v>
       </c>
       <c r="K51" t="n">
-        <v>-45.92</v>
+        <v>-44.83</v>
       </c>
       <c r="L51" t="n">
-        <v>119.25</v>
+        <v>116.4</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-88.62</v>
+        <v>-89.17</v>
       </c>
       <c r="K52" t="n">
-        <v>-16.94</v>
+        <v>-17.05</v>
       </c>
       <c r="L52" t="n">
-        <v>90.23</v>
+        <v>90.78</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>156.23</v>
+        <v>152.14</v>
       </c>
       <c r="K53" t="n">
-        <v>-18.52</v>
+        <v>-18.04</v>
       </c>
       <c r="L53" t="n">
-        <v>157.32</v>
+        <v>153.2</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-87.98999999999999</v>
+        <v>-87.31</v>
       </c>
       <c r="K54" t="n">
-        <v>107.49</v>
+        <v>106.67</v>
       </c>
       <c r="L54" t="n">
-        <v>138.91</v>
+        <v>137.85</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>54.06</v>
+        <v>55.05</v>
       </c>
       <c r="K55" t="n">
-        <v>-103.98</v>
+        <v>-105.88</v>
       </c>
       <c r="L55" t="n">
-        <v>117.19</v>
+        <v>119.34</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>101.1</v>
+        <v>100.53</v>
       </c>
       <c r="K56" t="n">
-        <v>-26.1</v>
+        <v>-25.95</v>
       </c>
       <c r="L56" t="n">
-        <v>104.42</v>
+        <v>103.82</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>107.94</v>
+        <v>107.66</v>
       </c>
       <c r="K57" t="n">
-        <v>-172.03</v>
+        <v>-171.58</v>
       </c>
       <c r="L57" t="n">
-        <v>203.09</v>
+        <v>202.56</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>135.82</v>
+        <v>137.85</v>
       </c>
       <c r="K58" t="n">
-        <v>-92.87</v>
+        <v>-94.26000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>164.53</v>
+        <v>166.99</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>4.1</v>
+        <v>4.24</v>
       </c>
       <c r="K59" t="n">
-        <v>-43.31</v>
+        <v>-44.81</v>
       </c>
       <c r="L59" t="n">
-        <v>43.5</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.54</v>
+        <v>-5.46</v>
       </c>
       <c r="K60" t="n">
-        <v>-55.47</v>
+        <v>-54.7</v>
       </c>
       <c r="L60" t="n">
-        <v>55.74</v>
+        <v>54.97</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>21.95</v>
+        <v>22.88</v>
       </c>
       <c r="K61" t="n">
-        <v>29.37</v>
+        <v>30.62</v>
       </c>
       <c r="L61" t="n">
-        <v>36.67</v>
+        <v>38.22</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-64.28</v>
+        <v>-64.19</v>
       </c>
       <c r="K62" t="n">
-        <v>33.64</v>
+        <v>33.59</v>
       </c>
       <c r="L62" t="n">
-        <v>72.56</v>
+        <v>72.45</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-50.15</v>
+        <v>-43.22</v>
       </c>
       <c r="K63" t="n">
-        <v>37.18</v>
+        <v>32.04</v>
       </c>
       <c r="L63" t="n">
-        <v>62.43</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-45.46</v>
+        <v>-45.95</v>
       </c>
       <c r="K64" t="n">
-        <v>46.73</v>
+        <v>47.23</v>
       </c>
       <c r="L64" t="n">
-        <v>65.19</v>
+        <v>65.90000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>82.77</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>29.87</v>
+        <v>30.25</v>
       </c>
       <c r="L65" t="n">
-        <v>88</v>
+        <v>89.11</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>139.07</v>
+        <v>133.11</v>
       </c>
       <c r="K66" t="n">
-        <v>29.94</v>
+        <v>28.65</v>
       </c>
       <c r="L66" t="n">
-        <v>142.26</v>
+        <v>136.16</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-28.42</v>
+        <v>-28.15</v>
       </c>
       <c r="K67" t="n">
-        <v>109.29</v>
+        <v>108.23</v>
       </c>
       <c r="L67" t="n">
-        <v>112.92</v>
+        <v>111.83</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-78.75</v>
+        <v>-80.15000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>-78.39</v>
+        <v>-79.78</v>
       </c>
       <c r="L68" t="n">
-        <v>111.12</v>
+        <v>113.09</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>67.06</v>
+        <v>69.73</v>
       </c>
       <c r="K69" t="n">
-        <v>-67.31</v>
+        <v>-69.98999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>95.02</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-16.43</v>
+        <v>-16.16</v>
       </c>
       <c r="K70" t="n">
-        <v>-141.06</v>
+        <v>-138.7</v>
       </c>
       <c r="L70" t="n">
-        <v>142.01</v>
+        <v>139.64</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-89.51000000000001</v>
+        <v>-90.06</v>
       </c>
       <c r="K71" t="n">
-        <v>-149.66</v>
+        <v>-150.58</v>
       </c>
       <c r="L71" t="n">
-        <v>174.38</v>
+        <v>175.46</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>99.23999999999999</v>
+        <v>104.73</v>
       </c>
       <c r="K72" t="n">
-        <v>-99.31</v>
+        <v>-104.81</v>
       </c>
       <c r="L72" t="n">
-        <v>140.39</v>
+        <v>148.17</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>115.32</v>
+        <v>121.58</v>
       </c>
       <c r="K73" t="n">
-        <v>-37.62</v>
+        <v>-39.66</v>
       </c>
       <c r="L73" t="n">
-        <v>121.3</v>
+        <v>127.88</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-35.09</v>
+        <v>-35.99</v>
       </c>
       <c r="K74" t="n">
-        <v>-18.85</v>
+        <v>-19.33</v>
       </c>
       <c r="L74" t="n">
-        <v>39.83</v>
+        <v>40.85</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-52.82</v>
+        <v>-52.2</v>
       </c>
       <c r="K75" t="n">
-        <v>6.04</v>
+        <v>5.97</v>
       </c>
       <c r="L75" t="n">
-        <v>53.17</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>49</v>
+        <v>49.52</v>
       </c>
       <c r="K76" t="n">
-        <v>-12.08</v>
+        <v>-12.21</v>
       </c>
       <c r="L76" t="n">
-        <v>50.47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-28.81</v>
+        <v>-28.41</v>
       </c>
       <c r="K77" t="n">
-        <v>-66.72</v>
+        <v>-65.79000000000001</v>
       </c>
       <c r="L77" t="n">
-        <v>72.68000000000001</v>
+        <v>71.66</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>18</v>
       </c>
       <c r="J78" t="n">
-        <v>48.73</v>
+        <v>46.45</v>
       </c>
       <c r="K78" t="n">
-        <v>105.52</v>
+        <v>100.58</v>
       </c>
       <c r="L78" t="n">
-        <v>116.23</v>
+        <v>110.79</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-41.7</v>
+        <v>-41.65</v>
       </c>
       <c r="K79" t="n">
-        <v>54.59</v>
+        <v>54.52</v>
       </c>
       <c r="L79" t="n">
-        <v>68.69</v>
+        <v>68.61</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>48.29</v>
+        <v>49.03</v>
       </c>
       <c r="K80" t="n">
-        <v>-67.7</v>
+        <v>-68.73999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>83.16</v>
+        <v>84.44</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-35.24</v>
+        <v>-36.27</v>
       </c>
       <c r="K81" t="n">
-        <v>-75.95</v>
+        <v>-78.17</v>
       </c>
       <c r="L81" t="n">
-        <v>83.72</v>
+        <v>86.18000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-104.18</v>
+        <v>-102.91</v>
       </c>
       <c r="K82" t="n">
-        <v>-10.72</v>
+        <v>-10.59</v>
       </c>
       <c r="L82" t="n">
-        <v>104.73</v>
+        <v>103.46</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>129.03</v>
+        <v>127.96</v>
       </c>
       <c r="K83" t="n">
-        <v>41.11</v>
+        <v>40.77</v>
       </c>
       <c r="L83" t="n">
-        <v>135.42</v>
+        <v>134.3</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>81.11</v>
+        <v>80.17</v>
       </c>
       <c r="K84" t="n">
-        <v>112.31</v>
+        <v>111.01</v>
       </c>
       <c r="L84" t="n">
-        <v>138.54</v>
+        <v>136.93</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-76.48</v>
+        <v>-81.89</v>
       </c>
       <c r="K85" t="n">
-        <v>-52</v>
+        <v>-55.68</v>
       </c>
       <c r="L85" t="n">
-        <v>92.48999999999999</v>
+        <v>99.02</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>207.58</v>
+        <v>204.28</v>
       </c>
       <c r="K86" t="n">
-        <v>74.04000000000001</v>
+        <v>72.86</v>
       </c>
       <c r="L86" t="n">
-        <v>220.39</v>
+        <v>216.88</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>42.57</v>
+        <v>43.36</v>
       </c>
       <c r="K87" t="n">
-        <v>-154.48</v>
+        <v>-157.34</v>
       </c>
       <c r="L87" t="n">
-        <v>160.23</v>
+        <v>163.21</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>99.62</v>
+        <v>103.43</v>
       </c>
       <c r="K88" t="n">
-        <v>-99.88</v>
+        <v>-103.7</v>
       </c>
       <c r="L88" t="n">
-        <v>141.07</v>
+        <v>146.46</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-22.xlsx
+++ b/output/2025-08-22.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.45</v>
+        <v>-10.5</v>
       </c>
       <c r="K14" t="n">
-        <v>41.42</v>
+        <v>41.6</v>
       </c>
       <c r="L14" t="n">
-        <v>42.71</v>
+        <v>42.91</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>5.6</v>
+        <v>5.85</v>
       </c>
       <c r="K15" t="n">
-        <v>-33.1</v>
+        <v>-34.61</v>
       </c>
       <c r="L15" t="n">
-        <v>33.57</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-42.13</v>
+        <v>-41.39</v>
       </c>
       <c r="K16" t="n">
-        <v>56.26</v>
+        <v>55.28</v>
       </c>
       <c r="L16" t="n">
-        <v>70.29000000000001</v>
+        <v>69.06</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>53.82</v>
+        <v>54.94</v>
       </c>
       <c r="K17" t="n">
-        <v>12.25</v>
+        <v>12.51</v>
       </c>
       <c r="L17" t="n">
-        <v>55.2</v>
+        <v>56.34</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="K18" t="n">
-        <v>64.65000000000001</v>
+        <v>63.97</v>
       </c>
       <c r="L18" t="n">
-        <v>67.19</v>
+        <v>66.48</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-25.85</v>
+        <v>-27.29</v>
       </c>
       <c r="K19" t="n">
-        <v>-40.51</v>
+        <v>-42.76</v>
       </c>
       <c r="L19" t="n">
-        <v>48.05</v>
+        <v>50.73</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>145.45</v>
+        <v>136.83</v>
       </c>
       <c r="K20" t="n">
-        <v>-50.58</v>
+        <v>-47.58</v>
       </c>
       <c r="L20" t="n">
-        <v>153.99</v>
+        <v>144.87</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.47</v>
+        <v>-6.32</v>
       </c>
       <c r="K21" t="n">
-        <v>-108.62</v>
+        <v>-106.05</v>
       </c>
       <c r="L21" t="n">
-        <v>108.82</v>
+        <v>106.24</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>17.94</v>
+        <v>19.15</v>
       </c>
       <c r="K22" t="n">
-        <v>63.01</v>
+        <v>67.23999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>65.52</v>
+        <v>69.91</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="K23" t="n">
-        <v>-137.74</v>
+        <v>-136.44</v>
       </c>
       <c r="L23" t="n">
-        <v>137.78</v>
+        <v>136.49</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-120.08</v>
+        <v>-119.11</v>
       </c>
       <c r="K24" t="n">
-        <v>57.93</v>
+        <v>57.47</v>
       </c>
       <c r="L24" t="n">
-        <v>133.32</v>
+        <v>132.25</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>13.3</v>
+        <v>13.61</v>
       </c>
       <c r="K25" t="n">
-        <v>108.8</v>
+        <v>111.36</v>
       </c>
       <c r="L25" t="n">
-        <v>109.61</v>
+        <v>112.18</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>55.65</v>
+        <v>57.25</v>
       </c>
       <c r="K26" t="n">
-        <v>150.5</v>
+        <v>154.83</v>
       </c>
       <c r="L26" t="n">
-        <v>160.46</v>
+        <v>165.08</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>286.07</v>
+        <v>267.02</v>
       </c>
       <c r="K27" t="n">
-        <v>134.25</v>
+        <v>125.31</v>
       </c>
       <c r="L27" t="n">
-        <v>316</v>
+        <v>294.96</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>78.89</v>
+        <v>79.64</v>
       </c>
       <c r="K28" t="n">
-        <v>151.5</v>
+        <v>152.94</v>
       </c>
       <c r="L28" t="n">
-        <v>170.81</v>
+        <v>172.43</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.91</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>-44.02</v>
+        <v>-44.26</v>
       </c>
       <c r="L29" t="n">
-        <v>44.92</v>
+        <v>45.16</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-15.64</v>
+        <v>-15.33</v>
       </c>
       <c r="K30" t="n">
-        <v>52.41</v>
+        <v>51.37</v>
       </c>
       <c r="L30" t="n">
-        <v>54.69</v>
+        <v>53.61</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-25.71</v>
+        <v>-25.94</v>
       </c>
       <c r="K31" t="n">
-        <v>-41.01</v>
+        <v>-41.37</v>
       </c>
       <c r="L31" t="n">
-        <v>48.41</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>15.55</v>
+        <v>15.41</v>
       </c>
       <c r="K32" t="n">
-        <v>76.43000000000001</v>
+        <v>75.75</v>
       </c>
       <c r="L32" t="n">
-        <v>78</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>44.28</v>
+        <v>46.65</v>
       </c>
       <c r="K33" t="n">
-        <v>-20.36</v>
+        <v>-21.45</v>
       </c>
       <c r="L33" t="n">
-        <v>48.74</v>
+        <v>51.34</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-38.85</v>
+        <v>-42.71</v>
       </c>
       <c r="K34" t="n">
-        <v>14.84</v>
+        <v>16.32</v>
       </c>
       <c r="L34" t="n">
-        <v>41.59</v>
+        <v>45.72</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>61.56</v>
+        <v>63.34</v>
       </c>
       <c r="K35" t="n">
-        <v>57.85</v>
+        <v>59.52</v>
       </c>
       <c r="L35" t="n">
-        <v>84.47</v>
+        <v>86.92</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>94.55</v>
+        <v>95.39</v>
       </c>
       <c r="K36" t="n">
-        <v>-45.54</v>
+        <v>-45.94</v>
       </c>
       <c r="L36" t="n">
-        <v>104.94</v>
+        <v>105.88</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="K37" t="n">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="L37" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-124.79</v>
+        <v>-122.8</v>
       </c>
       <c r="K38" t="n">
-        <v>52.03</v>
+        <v>51.19</v>
       </c>
       <c r="L38" t="n">
-        <v>135.2</v>
+        <v>133.04</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-182.75</v>
+        <v>-171.82</v>
       </c>
       <c r="K39" t="n">
-        <v>-55.52</v>
+        <v>-52.2</v>
       </c>
       <c r="L39" t="n">
-        <v>190.99</v>
+        <v>179.57</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>71.28</v>
+        <v>74.77</v>
       </c>
       <c r="K40" t="n">
-        <v>67.31999999999999</v>
+        <v>70.62</v>
       </c>
       <c r="L40" t="n">
-        <v>98.04000000000001</v>
+        <v>102.85</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-133.28</v>
+        <v>-128.46</v>
       </c>
       <c r="K41" t="n">
-        <v>224.44</v>
+        <v>216.31</v>
       </c>
       <c r="L41" t="n">
-        <v>261.04</v>
+        <v>251.58</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-210.14</v>
+        <v>-209.89</v>
       </c>
       <c r="K42" t="n">
         <v>2.19</v>
       </c>
       <c r="L42" t="n">
-        <v>210.16</v>
+        <v>209.9</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>153.06</v>
+        <v>159.81</v>
       </c>
       <c r="K43" t="n">
-        <v>42.15</v>
+        <v>44.01</v>
       </c>
       <c r="L43" t="n">
-        <v>158.75</v>
+        <v>165.76</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-18.68</v>
+        <v>-18.88</v>
       </c>
       <c r="K44" t="n">
-        <v>60.92</v>
+        <v>61.57</v>
       </c>
       <c r="L44" t="n">
-        <v>63.72</v>
+        <v>64.40000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="K45" t="n">
-        <v>44.9</v>
+        <v>46.83</v>
       </c>
       <c r="L45" t="n">
-        <v>44.9</v>
+        <v>46.84</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>31.44</v>
+        <v>30.58</v>
       </c>
       <c r="K46" t="n">
-        <v>-58.58</v>
+        <v>-56.98</v>
       </c>
       <c r="L46" t="n">
-        <v>66.48999999999999</v>
+        <v>64.67</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>32.32</v>
+        <v>31.52</v>
       </c>
       <c r="K47" t="n">
-        <v>70.42</v>
+        <v>68.67</v>
       </c>
       <c r="L47" t="n">
-        <v>77.48999999999999</v>
+        <v>75.56</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>34.59</v>
+        <v>37.31</v>
       </c>
       <c r="K48" t="n">
-        <v>29.7</v>
+        <v>32.03</v>
       </c>
       <c r="L48" t="n">
-        <v>45.59</v>
+        <v>49.17</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-75.84</v>
+        <v>-72.01000000000001</v>
       </c>
       <c r="K49" t="n">
-        <v>-90.73999999999999</v>
+        <v>-86.16</v>
       </c>
       <c r="L49" t="n">
-        <v>118.26</v>
+        <v>112.29</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-31.01</v>
+        <v>-29.82</v>
       </c>
       <c r="K50" t="n">
-        <v>115.75</v>
+        <v>111.33</v>
       </c>
       <c r="L50" t="n">
-        <v>119.83</v>
+        <v>115.25</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-107.42</v>
+        <v>-104.42</v>
       </c>
       <c r="K51" t="n">
-        <v>-44.83</v>
+        <v>-43.57</v>
       </c>
       <c r="L51" t="n">
-        <v>116.4</v>
+        <v>113.14</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-89.17</v>
+        <v>-89.79000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-17.05</v>
+        <v>-17.17</v>
       </c>
       <c r="L52" t="n">
-        <v>90.78</v>
+        <v>91.42</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>152.14</v>
+        <v>147.46</v>
       </c>
       <c r="K53" t="n">
-        <v>-18.04</v>
+        <v>-17.48</v>
       </c>
       <c r="L53" t="n">
-        <v>153.2</v>
+        <v>148.5</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-87.31</v>
+        <v>-86.54000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>106.67</v>
+        <v>105.73</v>
       </c>
       <c r="L54" t="n">
-        <v>137.85</v>
+        <v>136.64</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>55.05</v>
+        <v>56.18</v>
       </c>
       <c r="K55" t="n">
-        <v>-105.88</v>
+        <v>-108.06</v>
       </c>
       <c r="L55" t="n">
-        <v>119.34</v>
+        <v>121.79</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>100.53</v>
+        <v>110.59</v>
       </c>
       <c r="K56" t="n">
-        <v>-25.95</v>
+        <v>-28.55</v>
       </c>
       <c r="L56" t="n">
-        <v>103.82</v>
+        <v>114.22</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>107.66</v>
+        <v>107.35</v>
       </c>
       <c r="K57" t="n">
-        <v>-171.58</v>
+        <v>-171.08</v>
       </c>
       <c r="L57" t="n">
-        <v>202.56</v>
+        <v>201.97</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>137.85</v>
+        <v>140.17</v>
       </c>
       <c r="K58" t="n">
-        <v>-94.26000000000001</v>
+        <v>-95.84</v>
       </c>
       <c r="L58" t="n">
-        <v>166.99</v>
+        <v>169.8</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>4.24</v>
+        <v>4.4</v>
       </c>
       <c r="K59" t="n">
-        <v>-44.81</v>
+        <v>-46.53</v>
       </c>
       <c r="L59" t="n">
-        <v>45.01</v>
+        <v>46.74</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.46</v>
+        <v>-5.37</v>
       </c>
       <c r="K60" t="n">
-        <v>-54.7</v>
+        <v>-53.82</v>
       </c>
       <c r="L60" t="n">
-        <v>54.97</v>
+        <v>54.09</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>22.88</v>
+        <v>23.94</v>
       </c>
       <c r="K61" t="n">
-        <v>30.62</v>
+        <v>32.04</v>
       </c>
       <c r="L61" t="n">
-        <v>38.22</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-64.19</v>
+        <v>-64.08</v>
       </c>
       <c r="K62" t="n">
-        <v>33.59</v>
+        <v>33.54</v>
       </c>
       <c r="L62" t="n">
-        <v>72.45</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-43.22</v>
+        <v>-44.85</v>
       </c>
       <c r="K63" t="n">
-        <v>32.04</v>
+        <v>33.25</v>
       </c>
       <c r="L63" t="n">
-        <v>53.8</v>
+        <v>55.83</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-45.95</v>
+        <v>-46.51</v>
       </c>
       <c r="K64" t="n">
-        <v>47.23</v>
+        <v>47.81</v>
       </c>
       <c r="L64" t="n">
-        <v>65.90000000000001</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>83.81999999999999</v>
+        <v>85.02</v>
       </c>
       <c r="K65" t="n">
-        <v>30.25</v>
+        <v>30.68</v>
       </c>
       <c r="L65" t="n">
-        <v>89.11</v>
+        <v>90.38</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>133.11</v>
+        <v>126.29</v>
       </c>
       <c r="K66" t="n">
-        <v>28.65</v>
+        <v>27.19</v>
       </c>
       <c r="L66" t="n">
-        <v>136.16</v>
+        <v>129.18</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-28.15</v>
+        <v>-27.84</v>
       </c>
       <c r="K67" t="n">
-        <v>108.23</v>
+        <v>107.03</v>
       </c>
       <c r="L67" t="n">
-        <v>111.83</v>
+        <v>110.59</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-80.15000000000001</v>
+        <v>-81.73999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>-79.78</v>
+        <v>-81.37</v>
       </c>
       <c r="L68" t="n">
-        <v>113.09</v>
+        <v>115.34</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>69.73</v>
+        <v>72.78</v>
       </c>
       <c r="K69" t="n">
-        <v>-69.98999999999999</v>
+        <v>-73.05</v>
       </c>
       <c r="L69" t="n">
-        <v>98.8</v>
+        <v>103.12</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-16.16</v>
+        <v>-15.85</v>
       </c>
       <c r="K70" t="n">
-        <v>-138.7</v>
+        <v>-136.01</v>
       </c>
       <c r="L70" t="n">
-        <v>139.64</v>
+        <v>136.93</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-90.06</v>
+        <v>-90.7</v>
       </c>
       <c r="K71" t="n">
-        <v>-150.58</v>
+        <v>-151.64</v>
       </c>
       <c r="L71" t="n">
-        <v>175.46</v>
+        <v>176.7</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>104.73</v>
+        <v>111.02</v>
       </c>
       <c r="K72" t="n">
-        <v>-104.81</v>
+        <v>-111.1</v>
       </c>
       <c r="L72" t="n">
-        <v>148.17</v>
+        <v>157.06</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>121.58</v>
+        <v>128.73</v>
       </c>
       <c r="K73" t="n">
-        <v>-39.66</v>
+        <v>-41.99</v>
       </c>
       <c r="L73" t="n">
-        <v>127.88</v>
+        <v>135.41</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-35.99</v>
+        <v>-37.01</v>
       </c>
       <c r="K74" t="n">
-        <v>-19.33</v>
+        <v>-19.88</v>
       </c>
       <c r="L74" t="n">
-        <v>40.85</v>
+        <v>42.01</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-52.2</v>
+        <v>-51.49</v>
       </c>
       <c r="K75" t="n">
-        <v>5.97</v>
+        <v>5.89</v>
       </c>
       <c r="L75" t="n">
-        <v>52.54</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>49.52</v>
+        <v>50.11</v>
       </c>
       <c r="K76" t="n">
-        <v>-12.21</v>
+        <v>-12.35</v>
       </c>
       <c r="L76" t="n">
-        <v>51</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-28.41</v>
+        <v>-27.95</v>
       </c>
       <c r="K77" t="n">
-        <v>-65.79000000000001</v>
+        <v>-64.73</v>
       </c>
       <c r="L77" t="n">
-        <v>71.66</v>
+        <v>70.51000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>18</v>
       </c>
       <c r="J78" t="n">
-        <v>46.45</v>
+        <v>43.85</v>
       </c>
       <c r="K78" t="n">
-        <v>100.58</v>
+        <v>94.95</v>
       </c>
       <c r="L78" t="n">
-        <v>110.79</v>
+        <v>104.58</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-41.65</v>
+        <v>-41.59</v>
       </c>
       <c r="K79" t="n">
-        <v>54.52</v>
+        <v>54.45</v>
       </c>
       <c r="L79" t="n">
-        <v>68.61</v>
+        <v>68.52</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>49.03</v>
+        <v>49.88</v>
       </c>
       <c r="K80" t="n">
-        <v>-68.73999999999999</v>
+        <v>-69.93000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>84.44</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-36.27</v>
+        <v>-37.45</v>
       </c>
       <c r="K81" t="n">
-        <v>-78.17</v>
+        <v>-80.72</v>
       </c>
       <c r="L81" t="n">
-        <v>86.18000000000001</v>
+        <v>88.98</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-102.91</v>
+        <v>-101.47</v>
       </c>
       <c r="K82" t="n">
-        <v>-10.59</v>
+        <v>-10.44</v>
       </c>
       <c r="L82" t="n">
-        <v>103.46</v>
+        <v>102.01</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>127.96</v>
+        <v>126.75</v>
       </c>
       <c r="K83" t="n">
-        <v>40.77</v>
+        <v>40.38</v>
       </c>
       <c r="L83" t="n">
-        <v>134.3</v>
+        <v>133.03</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>80.17</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>111.01</v>
+        <v>109.52</v>
       </c>
       <c r="L84" t="n">
-        <v>136.93</v>
+        <v>135.09</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-81.89</v>
+        <v>-88.06</v>
       </c>
       <c r="K85" t="n">
-        <v>-55.68</v>
+        <v>-59.88</v>
       </c>
       <c r="L85" t="n">
-        <v>99.02</v>
+        <v>106.49</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>204.28</v>
+        <v>200.51</v>
       </c>
       <c r="K86" t="n">
-        <v>72.86</v>
+        <v>71.52</v>
       </c>
       <c r="L86" t="n">
-        <v>216.88</v>
+        <v>212.88</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>43.36</v>
+        <v>44.27</v>
       </c>
       <c r="K87" t="n">
-        <v>-157.34</v>
+        <v>-160.61</v>
       </c>
       <c r="L87" t="n">
-        <v>163.21</v>
+        <v>166.6</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>103.43</v>
+        <v>107.78</v>
       </c>
       <c r="K88" t="n">
-        <v>-103.7</v>
+        <v>-108.06</v>
       </c>
       <c r="L88" t="n">
-        <v>146.46</v>
+        <v>152.63</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-22.xlsx
+++ b/output/2025-08-22.xlsx
@@ -628,25 +628,25 @@
         <v>1.52</v>
       </c>
       <c r="F14" t="n">
-        <v>8.18</v>
+        <v>2.98</v>
       </c>
       <c r="G14" t="n">
-        <v>162.3</v>
+        <v>175.5</v>
       </c>
       <c r="H14" t="n">
-        <v>82.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.5</v>
+        <v>-11.2</v>
       </c>
       <c r="K14" t="n">
-        <v>41.6</v>
+        <v>43.76</v>
       </c>
       <c r="L14" t="n">
-        <v>42.91</v>
+        <v>45.17</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>1.74</v>
       </c>
       <c r="F15" t="n">
-        <v>7.19</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>164.9</v>
+        <v>155.9</v>
       </c>
       <c r="H15" t="n">
-        <v>76.7</v>
+        <v>88.3</v>
       </c>
       <c r="I15" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>5.85</v>
+        <v>9.23</v>
       </c>
       <c r="K15" t="n">
-        <v>-34.61</v>
+        <v>-52.58</v>
       </c>
       <c r="L15" t="n">
-        <v>35.1</v>
+        <v>53.38</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>3.03</v>
       </c>
       <c r="F16" t="n">
-        <v>7.46</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>161.1</v>
+        <v>161.2</v>
       </c>
       <c r="H16" t="n">
-        <v>87.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>-41.39</v>
+        <v>-50.94</v>
       </c>
       <c r="K16" t="n">
-        <v>55.28</v>
+        <v>67.56</v>
       </c>
       <c r="L16" t="n">
-        <v>69.06</v>
+        <v>84.61</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>1.71</v>
       </c>
       <c r="F17" t="n">
-        <v>7.86</v>
+        <v>7.17</v>
       </c>
       <c r="G17" t="n">
-        <v>171.9</v>
+        <v>169.2</v>
       </c>
       <c r="H17" t="n">
-        <v>86.40000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>54.94</v>
+        <v>70.09</v>
       </c>
       <c r="K17" t="n">
-        <v>12.51</v>
+        <v>14.31</v>
       </c>
       <c r="L17" t="n">
-        <v>56.34</v>
+        <v>71.53</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>1.46</v>
       </c>
       <c r="F18" t="n">
-        <v>7.78</v>
+        <v>1.76</v>
       </c>
       <c r="G18" t="n">
-        <v>133.9</v>
+        <v>167.6</v>
       </c>
       <c r="H18" t="n">
-        <v>79.3</v>
+        <v>72.8</v>
       </c>
       <c r="I18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>18.1</v>
+        <v>17.44</v>
       </c>
       <c r="K18" t="n">
-        <v>63.97</v>
+        <v>61.39</v>
       </c>
       <c r="L18" t="n">
-        <v>66.48</v>
+        <v>63.82</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>1.73</v>
       </c>
       <c r="F19" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>160.1</v>
+        <v>164</v>
       </c>
       <c r="H19" t="n">
-        <v>84</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-27.29</v>
+        <v>-35.47</v>
       </c>
       <c r="K19" t="n">
-        <v>-42.76</v>
+        <v>-58.77</v>
       </c>
       <c r="L19" t="n">
-        <v>50.73</v>
+        <v>68.64</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>1.48</v>
       </c>
       <c r="F20" t="n">
-        <v>7.58</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>159.9</v>
+        <v>163.5</v>
       </c>
       <c r="H20" t="n">
-        <v>94.2</v>
+        <v>85.8</v>
       </c>
       <c r="I20" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>136.83</v>
+        <v>169.64</v>
       </c>
       <c r="K20" t="n">
-        <v>-47.58</v>
+        <v>-62.17</v>
       </c>
       <c r="L20" t="n">
-        <v>144.87</v>
+        <v>180.67</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>1.47</v>
       </c>
       <c r="F21" t="n">
-        <v>7.95</v>
+        <v>3.32</v>
       </c>
       <c r="G21" t="n">
-        <v>149.9</v>
+        <v>171.1</v>
       </c>
       <c r="H21" t="n">
-        <v>88.40000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.32</v>
+        <v>-6.65</v>
       </c>
       <c r="K21" t="n">
-        <v>-106.05</v>
+        <v>-110.84</v>
       </c>
       <c r="L21" t="n">
-        <v>106.24</v>
+        <v>111.04</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>1.56</v>
       </c>
       <c r="F22" t="n">
-        <v>7.92</v>
+        <v>2.91</v>
       </c>
       <c r="G22" t="n">
-        <v>153.6</v>
+        <v>170.4</v>
       </c>
       <c r="H22" t="n">
-        <v>82.09999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="I22" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>19.15</v>
+        <v>21.34</v>
       </c>
       <c r="K22" t="n">
-        <v>67.23999999999999</v>
+        <v>66.28</v>
       </c>
       <c r="L22" t="n">
-        <v>69.91</v>
+        <v>69.63</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>1.73</v>
       </c>
       <c r="F23" t="n">
-        <v>7.7</v>
+        <v>6.77</v>
       </c>
       <c r="G23" t="n">
-        <v>168.5</v>
+        <v>166</v>
       </c>
       <c r="H23" t="n">
-        <v>88.7</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="I23" t="n">
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>3.62</v>
+        <v>7.8</v>
       </c>
       <c r="K23" t="n">
-        <v>-136.44</v>
+        <v>-173.95</v>
       </c>
       <c r="L23" t="n">
-        <v>136.49</v>
+        <v>174.13</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>2.03</v>
       </c>
       <c r="F24" t="n">
-        <v>7.78</v>
+        <v>5.56</v>
       </c>
       <c r="G24" t="n">
-        <v>155.9</v>
+        <v>167.7</v>
       </c>
       <c r="H24" t="n">
-        <v>83.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="I24" t="n">
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-119.11</v>
+        <v>-135.79</v>
       </c>
       <c r="K24" t="n">
-        <v>57.47</v>
+        <v>51.06</v>
       </c>
       <c r="L24" t="n">
-        <v>132.25</v>
+        <v>145.07</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>2.23</v>
       </c>
       <c r="F25" t="n">
-        <v>7.29</v>
+        <v>7.67</v>
       </c>
       <c r="G25" t="n">
-        <v>178.4</v>
+        <v>157.9</v>
       </c>
       <c r="H25" t="n">
-        <v>80.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>13.61</v>
+        <v>31.72</v>
       </c>
       <c r="K25" t="n">
-        <v>111.36</v>
+        <v>126.83</v>
       </c>
       <c r="L25" t="n">
-        <v>112.18</v>
+        <v>130.74</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>2.08</v>
       </c>
       <c r="F26" t="n">
-        <v>7.89</v>
+        <v>7.51</v>
       </c>
       <c r="G26" t="n">
-        <v>162</v>
+        <v>169.8</v>
       </c>
       <c r="H26" t="n">
-        <v>86.5</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>57.25</v>
+        <v>95.89</v>
       </c>
       <c r="K26" t="n">
-        <v>154.83</v>
+        <v>177.61</v>
       </c>
       <c r="L26" t="n">
-        <v>165.08</v>
+        <v>201.84</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>1.46</v>
       </c>
       <c r="F27" t="n">
-        <v>7.55</v>
+        <v>5.96</v>
       </c>
       <c r="G27" t="n">
-        <v>160</v>
+        <v>163.1</v>
       </c>
       <c r="H27" t="n">
-        <v>86.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>267.02</v>
+        <v>320.2</v>
       </c>
       <c r="K27" t="n">
-        <v>125.31</v>
+        <v>131.6</v>
       </c>
       <c r="L27" t="n">
-        <v>294.96</v>
+        <v>346.19</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>2.05</v>
       </c>
       <c r="F28" t="n">
-        <v>7.55</v>
+        <v>5.4</v>
       </c>
       <c r="G28" t="n">
-        <v>160.3</v>
+        <v>162.9</v>
       </c>
       <c r="H28" t="n">
-        <v>83.09999999999999</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>79.64</v>
+        <v>115.5</v>
       </c>
       <c r="K28" t="n">
-        <v>152.94</v>
+        <v>158.75</v>
       </c>
       <c r="L28" t="n">
-        <v>172.43</v>
+        <v>196.32</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>1.28</v>
       </c>
       <c r="F29" t="n">
-        <v>7.79</v>
+        <v>7.7</v>
       </c>
       <c r="G29" t="n">
-        <v>155.1</v>
+        <v>167.9</v>
       </c>
       <c r="H29" t="n">
-        <v>88.40000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.949999999999999</v>
+        <v>-12.69</v>
       </c>
       <c r="K29" t="n">
-        <v>-44.26</v>
+        <v>-63.01</v>
       </c>
       <c r="L29" t="n">
-        <v>45.16</v>
+        <v>64.27</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>1.82</v>
       </c>
       <c r="F30" t="n">
-        <v>7.48</v>
+        <v>5.74</v>
       </c>
       <c r="G30" t="n">
-        <v>167.2</v>
+        <v>161.6</v>
       </c>
       <c r="H30" t="n">
-        <v>85</v>
+        <v>89.5</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-15.33</v>
+        <v>-18.65</v>
       </c>
       <c r="K30" t="n">
-        <v>51.37</v>
+        <v>62.74</v>
       </c>
       <c r="L30" t="n">
-        <v>53.61</v>
+        <v>65.45</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>1.98</v>
       </c>
       <c r="F31" t="n">
-        <v>7.6</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>157.8</v>
+        <v>164.1</v>
       </c>
       <c r="H31" t="n">
-        <v>85</v>
+        <v>84.8</v>
       </c>
       <c r="I31" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-25.94</v>
+        <v>-31.4</v>
       </c>
       <c r="K31" t="n">
-        <v>-41.37</v>
+        <v>-50.78</v>
       </c>
       <c r="L31" t="n">
-        <v>48.83</v>
+        <v>59.7</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>1.97</v>
       </c>
       <c r="F32" t="n">
-        <v>7.18</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>159.3</v>
+        <v>155.5</v>
       </c>
       <c r="H32" t="n">
-        <v>92</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>15.41</v>
+        <v>19.06</v>
       </c>
       <c r="K32" t="n">
-        <v>75.75</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>77.3</v>
+        <v>90.5</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>1.81</v>
       </c>
       <c r="F33" t="n">
-        <v>8.27</v>
+        <v>6.84</v>
       </c>
       <c r="G33" t="n">
-        <v>170</v>
+        <v>177.4</v>
       </c>
       <c r="H33" t="n">
-        <v>87.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>46.65</v>
+        <v>60.88</v>
       </c>
       <c r="K33" t="n">
-        <v>-21.45</v>
+        <v>-30.58</v>
       </c>
       <c r="L33" t="n">
-        <v>51.34</v>
+        <v>68.12</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>1.81</v>
       </c>
       <c r="F34" t="n">
-        <v>7.75</v>
+        <v>6</v>
       </c>
       <c r="G34" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H34" t="n">
-        <v>85.40000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-42.71</v>
+        <v>-57.66</v>
       </c>
       <c r="K34" t="n">
-        <v>16.32</v>
+        <v>17.47</v>
       </c>
       <c r="L34" t="n">
-        <v>45.72</v>
+        <v>60.25</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>1.62</v>
       </c>
       <c r="F35" t="n">
-        <v>7.7</v>
+        <v>5.2</v>
       </c>
       <c r="G35" t="n">
-        <v>165.7</v>
+        <v>166.1</v>
       </c>
       <c r="H35" t="n">
-        <v>82.3</v>
+        <v>88.7</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>63.34</v>
+        <v>75.3</v>
       </c>
       <c r="K35" t="n">
-        <v>59.52</v>
+        <v>62.47</v>
       </c>
       <c r="L35" t="n">
-        <v>86.92</v>
+        <v>97.84</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>2.32</v>
       </c>
       <c r="F36" t="n">
-        <v>7.7</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>157.1</v>
+        <v>165.9</v>
       </c>
       <c r="H36" t="n">
-        <v>86.7</v>
+        <v>84.5</v>
       </c>
       <c r="I36" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>95.39</v>
+        <v>106.71</v>
       </c>
       <c r="K36" t="n">
-        <v>-45.94</v>
+        <v>-59.72</v>
       </c>
       <c r="L36" t="n">
-        <v>105.88</v>
+        <v>122.28</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>1.96</v>
       </c>
       <c r="F37" t="n">
-        <v>7.44</v>
+        <v>3.16</v>
       </c>
       <c r="G37" t="n">
-        <v>148</v>
+        <v>160.7</v>
       </c>
       <c r="H37" t="n">
-        <v>89.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>1.72</v>
+        <v>4.45</v>
       </c>
       <c r="K37" t="n">
-        <v>0.64</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>1.84</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>1.87</v>
       </c>
       <c r="F38" t="n">
-        <v>7.36</v>
+        <v>6.9</v>
       </c>
       <c r="G38" t="n">
-        <v>182.9</v>
+        <v>159.3</v>
       </c>
       <c r="H38" t="n">
-        <v>86.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-122.8</v>
+        <v>-163.83</v>
       </c>
       <c r="K38" t="n">
-        <v>51.19</v>
+        <v>58.14</v>
       </c>
       <c r="L38" t="n">
-        <v>133.04</v>
+        <v>173.84</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>1.48</v>
       </c>
       <c r="F39" t="n">
-        <v>7.12</v>
+        <v>2.5</v>
       </c>
       <c r="G39" t="n">
-        <v>172.6</v>
+        <v>154.4</v>
       </c>
       <c r="H39" t="n">
-        <v>88.7</v>
+        <v>92.2</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-171.82</v>
+        <v>-172.51</v>
       </c>
       <c r="K39" t="n">
-        <v>-52.2</v>
+        <v>-59.32</v>
       </c>
       <c r="L39" t="n">
-        <v>179.57</v>
+        <v>182.43</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>2.01</v>
       </c>
       <c r="F40" t="n">
-        <v>7.21</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>144.1</v>
+        <v>156.1</v>
       </c>
       <c r="H40" t="n">
-        <v>90.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>74.77</v>
+        <v>117.73</v>
       </c>
       <c r="K40" t="n">
-        <v>70.62</v>
+        <v>72.95</v>
       </c>
       <c r="L40" t="n">
-        <v>102.85</v>
+        <v>138.5</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>1.93</v>
       </c>
       <c r="F41" t="n">
-        <v>6.93</v>
+        <v>5.6</v>
       </c>
       <c r="G41" t="n">
-        <v>151.9</v>
+        <v>150.7</v>
       </c>
       <c r="H41" t="n">
-        <v>96.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="I41" t="n">
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-128.46</v>
+        <v>-133.97</v>
       </c>
       <c r="K41" t="n">
-        <v>216.31</v>
+        <v>224.79</v>
       </c>
       <c r="L41" t="n">
-        <v>251.58</v>
+        <v>261.68</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>2.54</v>
       </c>
       <c r="F42" t="n">
-        <v>7.91</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>147.4</v>
+        <v>170.3</v>
       </c>
       <c r="H42" t="n">
-        <v>88.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-209.89</v>
+        <v>-248.21</v>
       </c>
       <c r="K42" t="n">
-        <v>2.19</v>
+        <v>-50.78</v>
       </c>
       <c r="L42" t="n">
-        <v>209.9</v>
+        <v>253.35</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>2.01</v>
       </c>
       <c r="F43" t="n">
-        <v>7.18</v>
+        <v>6.47</v>
       </c>
       <c r="G43" t="n">
-        <v>159.5</v>
+        <v>155.6</v>
       </c>
       <c r="H43" t="n">
-        <v>80.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>159.81</v>
+        <v>201.69</v>
       </c>
       <c r="K43" t="n">
-        <v>44.01</v>
+        <v>1.09</v>
       </c>
       <c r="L43" t="n">
-        <v>165.76</v>
+        <v>201.7</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>2.88</v>
       </c>
       <c r="F44" t="n">
-        <v>7.73</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>158.1</v>
+        <v>166.6</v>
       </c>
       <c r="H44" t="n">
-        <v>86.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="I44" t="n">
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-18.88</v>
+        <v>-21.95</v>
       </c>
       <c r="K44" t="n">
-        <v>61.57</v>
+        <v>70.62</v>
       </c>
       <c r="L44" t="n">
-        <v>64.40000000000001</v>
+        <v>73.95</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>2.14</v>
       </c>
       <c r="F45" t="n">
-        <v>7.38</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>151.8</v>
+        <v>159.7</v>
       </c>
       <c r="H45" t="n">
-        <v>90.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>0.37</v>
+        <v>0.63</v>
       </c>
       <c r="K45" t="n">
-        <v>46.83</v>
+        <v>57.14</v>
       </c>
       <c r="L45" t="n">
-        <v>46.84</v>
+        <v>57.15</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>2.04</v>
       </c>
       <c r="F46" t="n">
-        <v>7.98</v>
+        <v>8.26</v>
       </c>
       <c r="G46" t="n">
-        <v>160.7</v>
+        <v>171.6</v>
       </c>
       <c r="H46" t="n">
-        <v>87.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>30.58</v>
+        <v>36.14</v>
       </c>
       <c r="K46" t="n">
-        <v>-56.98</v>
+        <v>-67.94</v>
       </c>
       <c r="L46" t="n">
-        <v>64.67</v>
+        <v>76.95</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>1.75</v>
       </c>
       <c r="F47" t="n">
-        <v>6.98</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>159.9</v>
+        <v>151.7</v>
       </c>
       <c r="H47" t="n">
-        <v>85.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>31.52</v>
+        <v>45.93</v>
       </c>
       <c r="K47" t="n">
-        <v>68.67</v>
+        <v>97.08</v>
       </c>
       <c r="L47" t="n">
-        <v>75.56</v>
+        <v>107.4</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>1.85</v>
       </c>
       <c r="F48" t="n">
-        <v>7.99</v>
+        <v>7.38</v>
       </c>
       <c r="G48" t="n">
-        <v>149.1</v>
+        <v>171.9</v>
       </c>
       <c r="H48" t="n">
-        <v>87.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>37.31</v>
+        <v>50.46</v>
       </c>
       <c r="K48" t="n">
-        <v>32.03</v>
+        <v>39.89</v>
       </c>
       <c r="L48" t="n">
-        <v>49.17</v>
+        <v>64.31999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>2.85</v>
       </c>
       <c r="F49" t="n">
-        <v>7.06</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>176.4</v>
+        <v>153.2</v>
       </c>
       <c r="H49" t="n">
-        <v>90.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I49" t="n">
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-72.01000000000001</v>
+        <v>-79.03</v>
       </c>
       <c r="K49" t="n">
-        <v>-86.16</v>
+        <v>-97.93000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>112.29</v>
+        <v>125.84</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>1.64</v>
       </c>
       <c r="F50" t="n">
-        <v>7.75</v>
+        <v>5.45</v>
       </c>
       <c r="G50" t="n">
-        <v>168.8</v>
+        <v>167</v>
       </c>
       <c r="H50" t="n">
-        <v>85.2</v>
+        <v>90.3</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-29.82</v>
+        <v>-36.9</v>
       </c>
       <c r="K50" t="n">
-        <v>111.33</v>
+        <v>137.52</v>
       </c>
       <c r="L50" t="n">
-        <v>115.25</v>
+        <v>142.38</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>2.07</v>
       </c>
       <c r="F51" t="n">
-        <v>7.42</v>
+        <v>8.4</v>
       </c>
       <c r="G51" t="n">
-        <v>178</v>
+        <v>160.5</v>
       </c>
       <c r="H51" t="n">
-        <v>85.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I51" t="n">
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-104.42</v>
+        <v>-127.48</v>
       </c>
       <c r="K51" t="n">
-        <v>-43.57</v>
+        <v>-60.03</v>
       </c>
       <c r="L51" t="n">
-        <v>113.14</v>
+        <v>140.91</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>1.8</v>
       </c>
       <c r="F52" t="n">
-        <v>7.26</v>
+        <v>5.25</v>
       </c>
       <c r="G52" t="n">
-        <v>162.4</v>
+        <v>157.1</v>
       </c>
       <c r="H52" t="n">
-        <v>83.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>-89.79000000000001</v>
+        <v>-107.6</v>
       </c>
       <c r="K52" t="n">
-        <v>-17.17</v>
+        <v>-26.99</v>
       </c>
       <c r="L52" t="n">
-        <v>91.42</v>
+        <v>110.93</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>1.97</v>
       </c>
       <c r="F53" t="n">
-        <v>7.08</v>
+        <v>5.81</v>
       </c>
       <c r="G53" t="n">
-        <v>159.4</v>
+        <v>153.7</v>
       </c>
       <c r="H53" t="n">
-        <v>86.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I53" t="n">
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>147.46</v>
+        <v>167.35</v>
       </c>
       <c r="K53" t="n">
-        <v>-17.48</v>
+        <v>-29.37</v>
       </c>
       <c r="L53" t="n">
-        <v>148.5</v>
+        <v>169.91</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>1.59</v>
       </c>
       <c r="F54" t="n">
-        <v>7.48</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>173.5</v>
+        <v>161.7</v>
       </c>
       <c r="H54" t="n">
-        <v>91.90000000000001</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>-86.54000000000001</v>
+        <v>-117.15</v>
       </c>
       <c r="K54" t="n">
-        <v>105.73</v>
+        <v>137.05</v>
       </c>
       <c r="L54" t="n">
-        <v>136.64</v>
+        <v>180.3</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>2.33</v>
       </c>
       <c r="F55" t="n">
-        <v>7.22</v>
+        <v>3.28</v>
       </c>
       <c r="G55" t="n">
-        <v>154.8</v>
+        <v>156.3</v>
       </c>
       <c r="H55" t="n">
-        <v>86.8</v>
+        <v>83.3</v>
       </c>
       <c r="I55" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J55" t="n">
-        <v>56.18</v>
+        <v>57.06</v>
       </c>
       <c r="K55" t="n">
-        <v>-108.06</v>
+        <v>-112.81</v>
       </c>
       <c r="L55" t="n">
-        <v>121.79</v>
+        <v>126.42</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>2.4</v>
       </c>
       <c r="F56" t="n">
-        <v>6.99</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>158.4</v>
+        <v>151.9</v>
       </c>
       <c r="H56" t="n">
-        <v>89.09999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>110.59</v>
+        <v>156.55</v>
       </c>
       <c r="K56" t="n">
-        <v>-28.55</v>
+        <v>-114.85</v>
       </c>
       <c r="L56" t="n">
-        <v>114.22</v>
+        <v>194.16</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>2.12</v>
       </c>
       <c r="F57" t="n">
-        <v>7.75</v>
+        <v>5.66</v>
       </c>
       <c r="G57" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="H57" t="n">
-        <v>75.09999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="I57" t="n">
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>107.35</v>
+        <v>118.11</v>
       </c>
       <c r="K57" t="n">
-        <v>-171.08</v>
+        <v>-211.87</v>
       </c>
       <c r="L57" t="n">
-        <v>201.97</v>
+        <v>242.56</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>1.88</v>
       </c>
       <c r="F58" t="n">
-        <v>8.32</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>154.7</v>
+        <v>178.5</v>
       </c>
       <c r="H58" t="n">
-        <v>89.7</v>
+        <v>83.3</v>
       </c>
       <c r="I58" t="n">
         <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>140.17</v>
+        <v>165.73</v>
       </c>
       <c r="K58" t="n">
-        <v>-95.84</v>
+        <v>-159.21</v>
       </c>
       <c r="L58" t="n">
-        <v>169.8</v>
+        <v>229.81</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>2.3</v>
       </c>
       <c r="F59" t="n">
-        <v>7.62</v>
+        <v>8.42</v>
       </c>
       <c r="G59" t="n">
-        <v>172.2</v>
+        <v>164.4</v>
       </c>
       <c r="H59" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>4.4</v>
+        <v>5.65</v>
       </c>
       <c r="K59" t="n">
-        <v>-46.53</v>
+        <v>-56.2</v>
       </c>
       <c r="L59" t="n">
-        <v>46.74</v>
+        <v>56.49</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>2.02</v>
       </c>
       <c r="F60" t="n">
-        <v>7.05</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G60" t="n">
-        <v>147.7</v>
+        <v>153</v>
       </c>
       <c r="H60" t="n">
-        <v>88.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="I60" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.37</v>
+        <v>-6.78</v>
       </c>
       <c r="K60" t="n">
-        <v>-53.82</v>
+        <v>-70.08</v>
       </c>
       <c r="L60" t="n">
-        <v>54.09</v>
+        <v>70.41</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>1.78</v>
       </c>
       <c r="F61" t="n">
-        <v>8.01</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>157.3</v>
+        <v>172.2</v>
       </c>
       <c r="H61" t="n">
-        <v>76.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>23.94</v>
+        <v>32.16</v>
       </c>
       <c r="K61" t="n">
-        <v>32.04</v>
+        <v>42.42</v>
       </c>
       <c r="L61" t="n">
-        <v>40</v>
+        <v>53.23</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>1.77</v>
       </c>
       <c r="F62" t="n">
-        <v>7.34</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>162.9</v>
+        <v>158.9</v>
       </c>
       <c r="H62" t="n">
-        <v>88.8</v>
+        <v>87.3</v>
       </c>
       <c r="I62" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-64.08</v>
+        <v>-82.44</v>
       </c>
       <c r="K62" t="n">
-        <v>33.54</v>
+        <v>42.01</v>
       </c>
       <c r="L62" t="n">
-        <v>72.33</v>
+        <v>92.52</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>1.65</v>
       </c>
       <c r="F63" t="n">
-        <v>6.82</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>158.1</v>
+        <v>148.3</v>
       </c>
       <c r="H63" t="n">
-        <v>88.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="I63" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-44.85</v>
+        <v>-62.58</v>
       </c>
       <c r="K63" t="n">
-        <v>33.25</v>
+        <v>45.8</v>
       </c>
       <c r="L63" t="n">
-        <v>55.83</v>
+        <v>77.55</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>1.88</v>
       </c>
       <c r="F64" t="n">
-        <v>7.54</v>
+        <v>4.31</v>
       </c>
       <c r="G64" t="n">
-        <v>158.6</v>
+        <v>162.9</v>
       </c>
       <c r="H64" t="n">
-        <v>81.40000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="I64" t="n">
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-46.51</v>
+        <v>-51.12</v>
       </c>
       <c r="K64" t="n">
-        <v>47.81</v>
+        <v>51.32</v>
       </c>
       <c r="L64" t="n">
-        <v>66.7</v>
+        <v>72.44</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>2.27</v>
       </c>
       <c r="F65" t="n">
-        <v>7.37</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="G65" t="n">
-        <v>166.3</v>
+        <v>159.5</v>
       </c>
       <c r="H65" t="n">
-        <v>84.40000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>85.02</v>
+        <v>115.14</v>
       </c>
       <c r="K65" t="n">
-        <v>30.68</v>
+        <v>31.47</v>
       </c>
       <c r="L65" t="n">
-        <v>90.38</v>
+        <v>119.36</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>1.89</v>
       </c>
       <c r="F66" t="n">
-        <v>7.47</v>
+        <v>3.76</v>
       </c>
       <c r="G66" t="n">
-        <v>161.6</v>
+        <v>161.3</v>
       </c>
       <c r="H66" t="n">
-        <v>80.3</v>
+        <v>86.7</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>126.29</v>
+        <v>143.11</v>
       </c>
       <c r="K66" t="n">
-        <v>27.19</v>
+        <v>26.58</v>
       </c>
       <c r="L66" t="n">
-        <v>129.18</v>
+        <v>145.56</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>1.81</v>
       </c>
       <c r="F67" t="n">
-        <v>7.32</v>
+        <v>6.13</v>
       </c>
       <c r="G67" t="n">
-        <v>162.7</v>
+        <v>158.3</v>
       </c>
       <c r="H67" t="n">
-        <v>90.2</v>
+        <v>87.3</v>
       </c>
       <c r="I67" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-27.84</v>
+        <v>-29.41</v>
       </c>
       <c r="K67" t="n">
-        <v>107.03</v>
+        <v>117.16</v>
       </c>
       <c r="L67" t="n">
-        <v>110.59</v>
+        <v>120.8</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>2.23</v>
       </c>
       <c r="F68" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="G68" t="n">
-        <v>164.4</v>
+        <v>152</v>
       </c>
       <c r="H68" t="n">
-        <v>78.7</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-81.73999999999999</v>
+        <v>-78.52</v>
       </c>
       <c r="K68" t="n">
-        <v>-81.37</v>
+        <v>-105.75</v>
       </c>
       <c r="L68" t="n">
-        <v>115.34</v>
+        <v>131.72</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>1.87</v>
       </c>
       <c r="F69" t="n">
-        <v>7.47</v>
+        <v>3.42</v>
       </c>
       <c r="G69" t="n">
-        <v>164.7</v>
+        <v>161.4</v>
       </c>
       <c r="H69" t="n">
-        <v>89.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="I69" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>72.78</v>
+        <v>73.47</v>
       </c>
       <c r="K69" t="n">
-        <v>-73.05</v>
+        <v>-83.66</v>
       </c>
       <c r="L69" t="n">
-        <v>103.12</v>
+        <v>111.34</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>1.92</v>
       </c>
       <c r="F70" t="n">
-        <v>7.7</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>149.9</v>
+        <v>166</v>
       </c>
       <c r="H70" t="n">
-        <v>93.8</v>
+        <v>80.8</v>
       </c>
       <c r="I70" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-15.85</v>
+        <v>-18.86</v>
       </c>
       <c r="K70" t="n">
-        <v>-136.01</v>
+        <v>-188.5</v>
       </c>
       <c r="L70" t="n">
-        <v>136.93</v>
+        <v>189.44</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>1.61</v>
       </c>
       <c r="F71" t="n">
-        <v>7.72</v>
+        <v>3.56</v>
       </c>
       <c r="G71" t="n">
-        <v>153.9</v>
+        <v>166.4</v>
       </c>
       <c r="H71" t="n">
-        <v>91</v>
+        <v>82.8</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-90.7</v>
+        <v>-93.25</v>
       </c>
       <c r="K71" t="n">
-        <v>-151.64</v>
+        <v>-189.42</v>
       </c>
       <c r="L71" t="n">
-        <v>176.7</v>
+        <v>211.13</v>
       </c>
     </row>
     <row r="72">
@@ -3064,25 +3064,25 @@
         <v>2.14</v>
       </c>
       <c r="F72" t="n">
-        <v>7.51</v>
+        <v>7.95</v>
       </c>
       <c r="G72" t="n">
-        <v>166.7</v>
+        <v>162.1</v>
       </c>
       <c r="H72" t="n">
-        <v>85.59999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="I72" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>111.02</v>
+        <v>127.77</v>
       </c>
       <c r="K72" t="n">
-        <v>-111.1</v>
+        <v>-162.74</v>
       </c>
       <c r="L72" t="n">
-        <v>157.06</v>
+        <v>206.9</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>1.41</v>
       </c>
       <c r="F73" t="n">
-        <v>7.47</v>
+        <v>1.76</v>
       </c>
       <c r="G73" t="n">
-        <v>160</v>
+        <v>161.4</v>
       </c>
       <c r="H73" t="n">
-        <v>82</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>128.73</v>
+        <v>144.11</v>
       </c>
       <c r="K73" t="n">
-        <v>-41.99</v>
+        <v>-76.72</v>
       </c>
       <c r="L73" t="n">
-        <v>135.41</v>
+        <v>163.26</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>1.95</v>
       </c>
       <c r="F74" t="n">
-        <v>8.02</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>144.8</v>
+        <v>172.4</v>
       </c>
       <c r="H74" t="n">
-        <v>91.7</v>
+        <v>78.3</v>
       </c>
       <c r="I74" t="n">
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-37.01</v>
+        <v>-47.69</v>
       </c>
       <c r="K74" t="n">
-        <v>-19.88</v>
+        <v>-26.26</v>
       </c>
       <c r="L74" t="n">
-        <v>42.01</v>
+        <v>54.44</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>1.84</v>
       </c>
       <c r="F75" t="n">
-        <v>7.77</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>146.7</v>
+        <v>167.4</v>
       </c>
       <c r="H75" t="n">
-        <v>87.5</v>
+        <v>79.2</v>
       </c>
       <c r="I75" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-51.49</v>
+        <v>-69.11</v>
       </c>
       <c r="K75" t="n">
-        <v>5.89</v>
+        <v>7.34</v>
       </c>
       <c r="L75" t="n">
-        <v>51.83</v>
+        <v>69.48999999999999</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>2.21</v>
       </c>
       <c r="F76" t="n">
-        <v>7.72</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G76" t="n">
-        <v>156.6</v>
+        <v>166.3</v>
       </c>
       <c r="H76" t="n">
-        <v>88</v>
+        <v>84.2</v>
       </c>
       <c r="I76" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>50.11</v>
+        <v>61.03</v>
       </c>
       <c r="K76" t="n">
-        <v>-12.35</v>
+        <v>-15.78</v>
       </c>
       <c r="L76" t="n">
-        <v>51.6</v>
+        <v>63.04</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>1.92</v>
       </c>
       <c r="F77" t="n">
-        <v>7.59</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G77" t="n">
-        <v>170.5</v>
+        <v>163.7</v>
       </c>
       <c r="H77" t="n">
-        <v>84</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>-27.95</v>
+        <v>-37.56</v>
       </c>
       <c r="K77" t="n">
-        <v>-64.73</v>
+        <v>-89.8</v>
       </c>
       <c r="L77" t="n">
-        <v>70.51000000000001</v>
+        <v>97.34</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>2.07</v>
       </c>
       <c r="F78" t="n">
-        <v>7.72</v>
+        <v>5.18</v>
       </c>
       <c r="G78" t="n">
-        <v>162.1</v>
+        <v>166.3</v>
       </c>
       <c r="H78" t="n">
-        <v>81.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>43.85</v>
+        <v>46.33</v>
       </c>
       <c r="K78" t="n">
-        <v>94.95</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="L78" t="n">
-        <v>104.58</v>
+        <v>109.14</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>2.07</v>
       </c>
       <c r="F79" t="n">
-        <v>8.24</v>
+        <v>7.08</v>
       </c>
       <c r="G79" t="n">
-        <v>154.9</v>
+        <v>176.7</v>
       </c>
       <c r="H79" t="n">
-        <v>94.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="I79" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-41.59</v>
+        <v>-47.83</v>
       </c>
       <c r="K79" t="n">
-        <v>54.45</v>
+        <v>60.24</v>
       </c>
       <c r="L79" t="n">
-        <v>68.52</v>
+        <v>76.92</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>2.18</v>
       </c>
       <c r="F80" t="n">
-        <v>7.64</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>164.1</v>
+        <v>164.9</v>
       </c>
       <c r="H80" t="n">
-        <v>86.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="I80" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>49.88</v>
+        <v>65.73</v>
       </c>
       <c r="K80" t="n">
-        <v>-69.93000000000001</v>
+        <v>-97.52</v>
       </c>
       <c r="L80" t="n">
-        <v>85.90000000000001</v>
+        <v>117.6</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>2.26</v>
       </c>
       <c r="F81" t="n">
-        <v>8.210000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="G81" t="n">
-        <v>167.3</v>
+        <v>159.7</v>
       </c>
       <c r="H81" t="n">
-        <v>85.7</v>
+        <v>86</v>
       </c>
       <c r="I81" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>-37.45</v>
+        <v>150.52</v>
       </c>
       <c r="K81" t="n">
-        <v>-80.72</v>
+        <v>7.22</v>
       </c>
       <c r="L81" t="n">
-        <v>88.98</v>
+        <v>150.69</v>
       </c>
     </row>
     <row r="82">
@@ -3481,28 +3481,28 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.28</v>
+        <v>1.99</v>
       </c>
       <c r="F82" t="n">
-        <v>7.97</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G82" t="n">
-        <v>169.6</v>
+        <v>158</v>
       </c>
       <c r="H82" t="n">
-        <v>84.90000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-101.47</v>
+        <v>101.56</v>
       </c>
       <c r="K82" t="n">
-        <v>-10.44</v>
+        <v>-89.67</v>
       </c>
       <c r="L82" t="n">
-        <v>102.01</v>
+        <v>135.49</v>
       </c>
     </row>
     <row r="83">
@@ -3523,10 +3523,10 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.81</v>
+        <v>3.28</v>
       </c>
       <c r="F83" t="n">
-        <v>8.48</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G83" t="n">
         <v>167.2</v>
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>126.75</v>
+        <v>-85.48999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>40.38</v>
+        <v>150.45</v>
       </c>
       <c r="L83" t="n">
-        <v>133.03</v>
+        <v>173.05</v>
       </c>
     </row>
     <row r="84">
@@ -3565,10 +3565,10 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="F84" t="n">
-        <v>7.89</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G84" t="n">
         <v>164.1</v>
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>79.09999999999999</v>
+        <v>-59.67</v>
       </c>
       <c r="K84" t="n">
-        <v>109.52</v>
+        <v>122.45</v>
       </c>
       <c r="L84" t="n">
-        <v>135.09</v>
+        <v>136.22</v>
       </c>
     </row>
     <row r="85">
@@ -3607,10 +3607,10 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="F85" t="n">
-        <v>6.98</v>
+        <v>7.13</v>
       </c>
       <c r="G85" t="n">
         <v>153.3</v>
@@ -3622,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-88.06</v>
+        <v>18.1</v>
       </c>
       <c r="K85" t="n">
-        <v>-59.88</v>
+        <v>-134.48</v>
       </c>
       <c r="L85" t="n">
-        <v>106.49</v>
+        <v>135.69</v>
       </c>
     </row>
     <row r="86">
@@ -3649,10 +3649,10 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="F86" t="n">
-        <v>7.71</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G86" t="n">
         <v>166.7</v>
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>200.51</v>
+        <v>-242.23</v>
       </c>
       <c r="K86" t="n">
-        <v>71.52</v>
+        <v>174.3</v>
       </c>
       <c r="L86" t="n">
-        <v>212.88</v>
+        <v>298.42</v>
       </c>
     </row>
     <row r="87">
@@ -3691,10 +3691,10 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="F87" t="n">
-        <v>7.83</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G87" t="n">
         <v>147</v>
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>44.27</v>
+        <v>299.65</v>
       </c>
       <c r="K87" t="n">
-        <v>-160.61</v>
+        <v>-13.36</v>
       </c>
       <c r="L87" t="n">
-        <v>166.6</v>
+        <v>299.95</v>
       </c>
     </row>
     <row r="88">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="F88" t="n">
-        <v>8.130000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="G88" t="n">
-        <v>164.9</v>
+        <v>152.9</v>
       </c>
       <c r="H88" t="n">
-        <v>82.3</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="I88" t="n">
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>107.78</v>
+        <v>221.8</v>
       </c>
       <c r="K88" t="n">
-        <v>-108.06</v>
+        <v>-220.48</v>
       </c>
       <c r="L88" t="n">
-        <v>152.63</v>
+        <v>312.74</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-22.xlsx
+++ b/output/2025-08-22.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-11.2</v>
+        <v>-11.63</v>
       </c>
       <c r="K14" t="n">
-        <v>43.76</v>
+        <v>45.44</v>
       </c>
       <c r="L14" t="n">
-        <v>45.17</v>
+        <v>46.9</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>9.23</v>
+        <v>9.91</v>
       </c>
       <c r="K15" t="n">
-        <v>-52.58</v>
+        <v>-56.47</v>
       </c>
       <c r="L15" t="n">
-        <v>53.38</v>
+        <v>57.34</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>18</v>
       </c>
       <c r="J16" t="n">
-        <v>-50.94</v>
+        <v>-56.4</v>
       </c>
       <c r="K16" t="n">
-        <v>67.56</v>
+        <v>74.8</v>
       </c>
       <c r="L16" t="n">
-        <v>84.61</v>
+        <v>93.68000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -808,13 +808,13 @@
         <v>21</v>
       </c>
       <c r="J18" t="n">
-        <v>17.44</v>
+        <v>18.42</v>
       </c>
       <c r="K18" t="n">
-        <v>61.39</v>
+        <v>64.86</v>
       </c>
       <c r="L18" t="n">
-        <v>63.82</v>
+        <v>67.43000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-35.47</v>
+        <v>-36.83</v>
       </c>
       <c r="K19" t="n">
-        <v>-58.77</v>
+        <v>-61.03</v>
       </c>
       <c r="L19" t="n">
-        <v>68.64</v>
+        <v>71.28</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>169.64</v>
+        <v>172.96</v>
       </c>
       <c r="K20" t="n">
-        <v>-62.17</v>
+        <v>-63.38</v>
       </c>
       <c r="L20" t="n">
-        <v>180.67</v>
+        <v>184.21</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.65</v>
+        <v>-7.03</v>
       </c>
       <c r="K21" t="n">
-        <v>-110.84</v>
+        <v>-117.11</v>
       </c>
       <c r="L21" t="n">
-        <v>111.04</v>
+        <v>117.33</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>21.34</v>
+        <v>21.76</v>
       </c>
       <c r="K22" t="n">
-        <v>66.28</v>
+        <v>67.58</v>
       </c>
       <c r="L22" t="n">
-        <v>69.63</v>
+        <v>70.98999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>7.8</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>-173.95</v>
+        <v>-192.59</v>
       </c>
       <c r="L23" t="n">
-        <v>174.13</v>
+        <v>192.78</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-135.79</v>
+        <v>-143.48</v>
       </c>
       <c r="K24" t="n">
-        <v>51.06</v>
+        <v>53.95</v>
       </c>
       <c r="L24" t="n">
-        <v>145.07</v>
+        <v>153.28</v>
       </c>
     </row>
     <row r="25">
@@ -1144,13 +1144,13 @@
         <v>18</v>
       </c>
       <c r="J26" t="n">
-        <v>95.89</v>
+        <v>106.16</v>
       </c>
       <c r="K26" t="n">
-        <v>177.61</v>
+        <v>196.64</v>
       </c>
       <c r="L26" t="n">
-        <v>201.84</v>
+        <v>223.47</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>21</v>
       </c>
       <c r="J27" t="n">
-        <v>320.2</v>
+        <v>338.33</v>
       </c>
       <c r="K27" t="n">
-        <v>131.6</v>
+        <v>139.05</v>
       </c>
       <c r="L27" t="n">
-        <v>346.19</v>
+        <v>365.79</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>115.5</v>
+        <v>124.06</v>
       </c>
       <c r="K28" t="n">
-        <v>158.75</v>
+        <v>170.51</v>
       </c>
       <c r="L28" t="n">
-        <v>196.32</v>
+        <v>210.87</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-12.69</v>
+        <v>-13.41</v>
       </c>
       <c r="K29" t="n">
-        <v>-63.01</v>
+        <v>-66.58</v>
       </c>
       <c r="L29" t="n">
-        <v>64.27</v>
+        <v>67.91</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>-18.65</v>
+        <v>-20.35</v>
       </c>
       <c r="K30" t="n">
-        <v>62.74</v>
+        <v>68.44</v>
       </c>
       <c r="L30" t="n">
-        <v>65.45</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-31.4</v>
+        <v>-32.01</v>
       </c>
       <c r="K31" t="n">
-        <v>-50.78</v>
+        <v>-51.77</v>
       </c>
       <c r="L31" t="n">
-        <v>59.7</v>
+        <v>60.87</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>19.06</v>
+        <v>19.44</v>
       </c>
       <c r="K32" t="n">
-        <v>88.45999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="L32" t="n">
-        <v>90.5</v>
+        <v>92.27</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>60.88</v>
+        <v>63.22</v>
       </c>
       <c r="K33" t="n">
-        <v>-30.58</v>
+        <v>-31.75</v>
       </c>
       <c r="L33" t="n">
-        <v>68.12</v>
+        <v>70.73999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>19</v>
       </c>
       <c r="J34" t="n">
-        <v>-57.66</v>
+        <v>-62.91</v>
       </c>
       <c r="K34" t="n">
-        <v>17.47</v>
+        <v>19.06</v>
       </c>
       <c r="L34" t="n">
-        <v>60.25</v>
+        <v>65.73</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>22</v>
       </c>
       <c r="J35" t="n">
-        <v>75.3</v>
+        <v>78.2</v>
       </c>
       <c r="K35" t="n">
-        <v>62.47</v>
+        <v>64.87</v>
       </c>
       <c r="L35" t="n">
-        <v>97.84</v>
+        <v>101.6</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>22</v>
       </c>
       <c r="J36" t="n">
-        <v>106.71</v>
+        <v>110.81</v>
       </c>
       <c r="K36" t="n">
-        <v>-59.72</v>
+        <v>-62.02</v>
       </c>
       <c r="L36" t="n">
-        <v>122.28</v>
+        <v>126.99</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>4.45</v>
+        <v>4.78</v>
       </c>
       <c r="K37" t="n">
-        <v>-9.390000000000001</v>
+        <v>-10.09</v>
       </c>
       <c r="L37" t="n">
-        <v>10.39</v>
+        <v>11.16</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>-163.83</v>
+        <v>-178.72</v>
       </c>
       <c r="K38" t="n">
-        <v>58.14</v>
+        <v>63.42</v>
       </c>
       <c r="L38" t="n">
-        <v>173.84</v>
+        <v>189.64</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-172.51</v>
+        <v>-179.15</v>
       </c>
       <c r="K39" t="n">
-        <v>-59.32</v>
+        <v>-61.61</v>
       </c>
       <c r="L39" t="n">
-        <v>182.43</v>
+        <v>189.44</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>117.73</v>
+        <v>126.45</v>
       </c>
       <c r="K40" t="n">
-        <v>72.95</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>138.5</v>
+        <v>148.76</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-133.97</v>
+        <v>-143.9</v>
       </c>
       <c r="K41" t="n">
-        <v>224.79</v>
+        <v>241.44</v>
       </c>
       <c r="L41" t="n">
-        <v>261.68</v>
+        <v>281.07</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-248.21</v>
+        <v>-270.78</v>
       </c>
       <c r="K42" t="n">
-        <v>-50.78</v>
+        <v>-55.4</v>
       </c>
       <c r="L42" t="n">
-        <v>253.35</v>
+        <v>276.39</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>201.69</v>
+        <v>216.63</v>
       </c>
       <c r="K43" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="L43" t="n">
-        <v>201.7</v>
+        <v>216.64</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-21.95</v>
+        <v>-23.95</v>
       </c>
       <c r="K44" t="n">
-        <v>70.62</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>73.95</v>
+        <v>80.67</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>20</v>
       </c>
       <c r="J45" t="n">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="K45" t="n">
-        <v>57.14</v>
+        <v>61.37</v>
       </c>
       <c r="L45" t="n">
-        <v>57.15</v>
+        <v>61.38</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>20</v>
       </c>
       <c r="J46" t="n">
-        <v>36.14</v>
+        <v>38.82</v>
       </c>
       <c r="K46" t="n">
-        <v>-67.94</v>
+        <v>-72.97</v>
       </c>
       <c r="L46" t="n">
-        <v>76.95</v>
+        <v>82.65000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>45.93</v>
+        <v>50.11</v>
       </c>
       <c r="K47" t="n">
-        <v>97.08</v>
+        <v>105.91</v>
       </c>
       <c r="L47" t="n">
-        <v>107.4</v>
+        <v>117.16</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>50.46</v>
+        <v>53.31</v>
       </c>
       <c r="K48" t="n">
-        <v>39.89</v>
+        <v>42.15</v>
       </c>
       <c r="L48" t="n">
-        <v>64.31999999999999</v>
+        <v>67.95999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-79.03</v>
+        <v>-84.89</v>
       </c>
       <c r="K49" t="n">
-        <v>-97.93000000000001</v>
+        <v>-105.18</v>
       </c>
       <c r="L49" t="n">
-        <v>125.84</v>
+        <v>135.16</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-36.9</v>
+        <v>-39.63</v>
       </c>
       <c r="K50" t="n">
-        <v>137.52</v>
+        <v>147.71</v>
       </c>
       <c r="L50" t="n">
-        <v>142.38</v>
+        <v>152.93</v>
       </c>
     </row>
     <row r="51">
@@ -2236,13 +2236,13 @@
         <v>20</v>
       </c>
       <c r="J52" t="n">
-        <v>-107.6</v>
+        <v>-115.57</v>
       </c>
       <c r="K52" t="n">
-        <v>-26.99</v>
+        <v>-28.99</v>
       </c>
       <c r="L52" t="n">
-        <v>110.93</v>
+        <v>119.15</v>
       </c>
     </row>
     <row r="53">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>-117.15</v>
+        <v>-123.78</v>
       </c>
       <c r="K54" t="n">
-        <v>137.05</v>
+        <v>144.81</v>
       </c>
       <c r="L54" t="n">
-        <v>180.3</v>
+        <v>190.51</v>
       </c>
     </row>
     <row r="55">
@@ -2404,13 +2404,13 @@
         <v>19</v>
       </c>
       <c r="J56" t="n">
-        <v>156.55</v>
+        <v>170.78</v>
       </c>
       <c r="K56" t="n">
-        <v>-114.85</v>
+        <v>-125.29</v>
       </c>
       <c r="L56" t="n">
-        <v>194.16</v>
+        <v>211.81</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>118.11</v>
+        <v>126.86</v>
       </c>
       <c r="K57" t="n">
-        <v>-211.87</v>
+        <v>-227.56</v>
       </c>
       <c r="L57" t="n">
-        <v>242.56</v>
+        <v>260.53</v>
       </c>
     </row>
     <row r="58">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>5.65</v>
+        <v>5.76</v>
       </c>
       <c r="K59" t="n">
-        <v>-56.2</v>
+        <v>-57.31</v>
       </c>
       <c r="L59" t="n">
-        <v>56.49</v>
+        <v>57.59</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>-6.78</v>
+        <v>-7.16</v>
       </c>
       <c r="K60" t="n">
-        <v>-70.08</v>
+        <v>-74.05</v>
       </c>
       <c r="L60" t="n">
-        <v>70.41</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>21</v>
       </c>
       <c r="J61" t="n">
-        <v>32.16</v>
+        <v>33.98</v>
       </c>
       <c r="K61" t="n">
-        <v>42.42</v>
+        <v>44.82</v>
       </c>
       <c r="L61" t="n">
-        <v>53.23</v>
+        <v>56.24</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-82.44</v>
+        <v>-89.93000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>42.01</v>
+        <v>45.83</v>
       </c>
       <c r="L62" t="n">
-        <v>92.52</v>
+        <v>100.94</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>-62.58</v>
+        <v>-67.20999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>45.8</v>
+        <v>49.19</v>
       </c>
       <c r="L63" t="n">
-        <v>77.55</v>
+        <v>83.29000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-51.12</v>
+        <v>-55.77</v>
       </c>
       <c r="K64" t="n">
-        <v>51.32</v>
+        <v>55.99</v>
       </c>
       <c r="L64" t="n">
-        <v>72.44</v>
+        <v>79.02</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>21</v>
       </c>
       <c r="J65" t="n">
-        <v>115.14</v>
+        <v>121.65</v>
       </c>
       <c r="K65" t="n">
-        <v>31.47</v>
+        <v>33.25</v>
       </c>
       <c r="L65" t="n">
-        <v>119.36</v>
+        <v>126.12</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>19</v>
       </c>
       <c r="J66" t="n">
-        <v>143.11</v>
+        <v>156.12</v>
       </c>
       <c r="K66" t="n">
-        <v>26.58</v>
+        <v>29</v>
       </c>
       <c r="L66" t="n">
-        <v>145.56</v>
+        <v>158.79</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-29.41</v>
+        <v>-31.07</v>
       </c>
       <c r="K67" t="n">
-        <v>117.16</v>
+        <v>123.79</v>
       </c>
       <c r="L67" t="n">
-        <v>120.8</v>
+        <v>127.63</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>21</v>
       </c>
       <c r="J68" t="n">
-        <v>-78.52</v>
+        <v>-82.97</v>
       </c>
       <c r="K68" t="n">
-        <v>-105.75</v>
+        <v>-111.74</v>
       </c>
       <c r="L68" t="n">
-        <v>131.72</v>
+        <v>139.18</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>73.47</v>
+        <v>74.91</v>
       </c>
       <c r="K69" t="n">
-        <v>-83.66</v>
+        <v>-85.3</v>
       </c>
       <c r="L69" t="n">
-        <v>111.34</v>
+        <v>113.52</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>21</v>
       </c>
       <c r="J70" t="n">
-        <v>-18.86</v>
+        <v>-19.92</v>
       </c>
       <c r="K70" t="n">
-        <v>-188.5</v>
+        <v>-199.17</v>
       </c>
       <c r="L70" t="n">
-        <v>189.44</v>
+        <v>200.16</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-93.25</v>
+        <v>-101.73</v>
       </c>
       <c r="K71" t="n">
-        <v>-189.42</v>
+        <v>-206.64</v>
       </c>
       <c r="L71" t="n">
-        <v>211.13</v>
+        <v>230.32</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>21</v>
       </c>
       <c r="J72" t="n">
-        <v>127.77</v>
+        <v>135</v>
       </c>
       <c r="K72" t="n">
-        <v>-162.74</v>
+        <v>-171.95</v>
       </c>
       <c r="L72" t="n">
-        <v>206.9</v>
+        <v>218.62</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>18</v>
       </c>
       <c r="J73" t="n">
-        <v>144.11</v>
+        <v>159.55</v>
       </c>
       <c r="K73" t="n">
-        <v>-76.72</v>
+        <v>-84.94</v>
       </c>
       <c r="L73" t="n">
-        <v>163.26</v>
+        <v>180.75</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-47.69</v>
+        <v>-49.52</v>
       </c>
       <c r="K74" t="n">
-        <v>-26.26</v>
+        <v>-27.27</v>
       </c>
       <c r="L74" t="n">
-        <v>54.44</v>
+        <v>56.53</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>18</v>
       </c>
       <c r="J75" t="n">
-        <v>-69.11</v>
+        <v>-76.51000000000001</v>
       </c>
       <c r="K75" t="n">
-        <v>7.34</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>69.48999999999999</v>
+        <v>76.94</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>20</v>
       </c>
       <c r="J76" t="n">
-        <v>61.03</v>
+        <v>65.55</v>
       </c>
       <c r="K76" t="n">
-        <v>-15.78</v>
+        <v>-16.94</v>
       </c>
       <c r="L76" t="n">
-        <v>63.04</v>
+        <v>67.70999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>20</v>
       </c>
       <c r="J77" t="n">
-        <v>-37.56</v>
+        <v>-40.34</v>
       </c>
       <c r="K77" t="n">
-        <v>-89.8</v>
+        <v>-96.45999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>97.34</v>
+        <v>104.55</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>46.33</v>
+        <v>50.55</v>
       </c>
       <c r="K78" t="n">
-        <v>98.81999999999999</v>
+        <v>107.81</v>
       </c>
       <c r="L78" t="n">
-        <v>109.14</v>
+        <v>119.07</v>
       </c>
     </row>
     <row r="79">
@@ -3412,13 +3412,13 @@
         <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>65.73</v>
+        <v>69.45</v>
       </c>
       <c r="K80" t="n">
-        <v>-97.52</v>
+        <v>-103.04</v>
       </c>
       <c r="L80" t="n">
-        <v>117.6</v>
+        <v>124.26</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>18</v>
       </c>
       <c r="J81" t="n">
-        <v>150.52</v>
+        <v>166.64</v>
       </c>
       <c r="K81" t="n">
-        <v>7.22</v>
+        <v>7.99</v>
       </c>
       <c r="L81" t="n">
-        <v>150.69</v>
+        <v>166.83</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>101.56</v>
+        <v>105.47</v>
       </c>
       <c r="K82" t="n">
-        <v>-89.67</v>
+        <v>-93.12</v>
       </c>
       <c r="L82" t="n">
-        <v>135.49</v>
+        <v>140.7</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-85.48999999999999</v>
+        <v>-91.83</v>
       </c>
       <c r="K83" t="n">
-        <v>150.45</v>
+        <v>161.6</v>
       </c>
       <c r="L83" t="n">
-        <v>173.05</v>
+        <v>185.87</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-59.67</v>
+        <v>-63.05</v>
       </c>
       <c r="K84" t="n">
-        <v>122.45</v>
+        <v>129.38</v>
       </c>
       <c r="L84" t="n">
-        <v>136.22</v>
+        <v>143.93</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>18.1</v>
+        <v>20.04</v>
       </c>
       <c r="K85" t="n">
-        <v>-134.48</v>
+        <v>-148.88</v>
       </c>
       <c r="L85" t="n">
-        <v>135.69</v>
+        <v>150.23</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-242.23</v>
+        <v>-260.17</v>
       </c>
       <c r="K86" t="n">
-        <v>174.3</v>
+        <v>187.21</v>
       </c>
       <c r="L86" t="n">
-        <v>298.42</v>
+        <v>320.53</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>299.65</v>
+        <v>305.53</v>
       </c>
       <c r="K87" t="n">
-        <v>-13.36</v>
+        <v>-13.63</v>
       </c>
       <c r="L87" t="n">
-        <v>299.95</v>
+        <v>305.83</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>221.8</v>
+        <v>230.34</v>
       </c>
       <c r="K88" t="n">
-        <v>-220.48</v>
+        <v>-228.96</v>
       </c>
       <c r="L88" t="n">
-        <v>312.74</v>
+        <v>324.77</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-22.xlsx
+++ b/output/2025-08-22.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="F14" t="n">
-        <v>2.98</v>
+        <v>2.53</v>
       </c>
       <c r="G14" t="n">
-        <v>175.5</v>
+        <v>174.5</v>
       </c>
       <c r="H14" t="n">
-        <v>87.09999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J14" t="n">
-        <v>-11.63</v>
+        <v>24.33</v>
       </c>
       <c r="K14" t="n">
-        <v>45.44</v>
+        <v>-12.69</v>
       </c>
       <c r="L14" t="n">
-        <v>46.9</v>
+        <v>27.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:02:45</t>
+          <t>06:01:32</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="F15" t="n">
-        <v>8.619999999999999</v>
+        <v>7.02</v>
       </c>
       <c r="G15" t="n">
-        <v>155.9</v>
+        <v>164</v>
       </c>
       <c r="H15" t="n">
-        <v>88.3</v>
+        <v>74.5</v>
       </c>
       <c r="I15" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>9.91</v>
+        <v>24.98</v>
       </c>
       <c r="K15" t="n">
-        <v>-56.47</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>57.34</v>
+        <v>26.24</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:03:24</t>
+          <t>06:03:38</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.03</v>
+        <v>1.85</v>
       </c>
       <c r="F16" t="n">
-        <v>8.619999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="G16" t="n">
-        <v>161.2</v>
+        <v>167.6</v>
       </c>
       <c r="H16" t="n">
-        <v>86.40000000000001</v>
+        <v>56.7</v>
       </c>
       <c r="I16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>-56.4</v>
+        <v>-28.05</v>
       </c>
       <c r="K16" t="n">
-        <v>74.8</v>
+        <v>20.83</v>
       </c>
       <c r="L16" t="n">
-        <v>93.68000000000001</v>
+        <v>34.93</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:07:18</t>
+          <t>06:08:14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="F17" t="n">
-        <v>7.17</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>169.2</v>
+        <v>171.2</v>
       </c>
       <c r="H17" t="n">
-        <v>91.90000000000001</v>
+        <v>40.3</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>70.09</v>
+        <v>-16.16</v>
       </c>
       <c r="K17" t="n">
-        <v>14.31</v>
+        <v>-46.21</v>
       </c>
       <c r="L17" t="n">
-        <v>71.53</v>
+        <v>48.95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:10:00</t>
+          <t>06:09:44</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="F18" t="n">
-        <v>1.76</v>
+        <v>4.1</v>
       </c>
       <c r="G18" t="n">
-        <v>167.6</v>
+        <v>156</v>
       </c>
       <c r="H18" t="n">
-        <v>72.8</v>
+        <v>56.1</v>
       </c>
       <c r="I18" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>18.42</v>
+        <v>-14.78</v>
       </c>
       <c r="K18" t="n">
-        <v>64.86</v>
+        <v>-42.22</v>
       </c>
       <c r="L18" t="n">
-        <v>67.43000000000001</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:11:16</t>
+          <t>06:11:47</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="F19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>164</v>
+        <v>154.5</v>
       </c>
       <c r="H19" t="n">
-        <v>85.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-36.83</v>
+        <v>-27.99</v>
       </c>
       <c r="K19" t="n">
-        <v>-61.03</v>
+        <v>13.19</v>
       </c>
       <c r="L19" t="n">
-        <v>71.28</v>
+        <v>30.94</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:17:12</t>
+          <t>06:16:35</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.48</v>
+        <v>1.84</v>
       </c>
       <c r="F20" t="n">
-        <v>8.619999999999999</v>
+        <v>6.03</v>
       </c>
       <c r="G20" t="n">
-        <v>163.5</v>
+        <v>165.6</v>
       </c>
       <c r="H20" t="n">
-        <v>85.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>172.96</v>
+        <v>75.63</v>
       </c>
       <c r="K20" t="n">
-        <v>-63.38</v>
+        <v>35.4</v>
       </c>
       <c r="L20" t="n">
-        <v>184.21</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:19:28</t>
+          <t>06:18:54</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="F21" t="n">
-        <v>3.32</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>171.1</v>
+        <v>166.5</v>
       </c>
       <c r="H21" t="n">
-        <v>80.90000000000001</v>
+        <v>38.3</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-7.03</v>
+        <v>-44.21</v>
       </c>
       <c r="K21" t="n">
-        <v>-117.11</v>
+        <v>15.32</v>
       </c>
       <c r="L21" t="n">
-        <v>117.33</v>
+        <v>46.79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:20:49</t>
+          <t>06:21:00</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="F22" t="n">
-        <v>2.91</v>
+        <v>7.32</v>
       </c>
       <c r="G22" t="n">
-        <v>170.4</v>
+        <v>159.7</v>
       </c>
       <c r="H22" t="n">
-        <v>82.7</v>
+        <v>100</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J22" t="n">
-        <v>21.76</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>67.58</v>
+        <v>-51.74</v>
       </c>
       <c r="L22" t="n">
-        <v>70.98999999999999</v>
+        <v>82.94</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:26:38</t>
+          <t>06:25:32</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="F23" t="n">
-        <v>6.77</v>
+        <v>5.42</v>
       </c>
       <c r="G23" t="n">
-        <v>166</v>
+        <v>164.5</v>
       </c>
       <c r="H23" t="n">
-        <v>90.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="I23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J23" t="n">
-        <v>8.640000000000001</v>
+        <v>49.41</v>
       </c>
       <c r="K23" t="n">
-        <v>-192.59</v>
+        <v>-98.2</v>
       </c>
       <c r="L23" t="n">
-        <v>192.78</v>
+        <v>109.93</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:28:26</t>
+          <t>06:27:06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.03</v>
+        <v>1.63</v>
       </c>
       <c r="F24" t="n">
-        <v>5.56</v>
+        <v>5.8</v>
       </c>
       <c r="G24" t="n">
-        <v>167.7</v>
+        <v>161</v>
       </c>
       <c r="H24" t="n">
-        <v>83.8</v>
+        <v>100</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>-143.48</v>
+        <v>97.59</v>
       </c>
       <c r="K24" t="n">
-        <v>53.95</v>
+        <v>54.16</v>
       </c>
       <c r="L24" t="n">
-        <v>153.28</v>
+        <v>111.61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:30:03</t>
+          <t>06:29:10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.23</v>
+        <v>1.64</v>
       </c>
       <c r="F25" t="n">
-        <v>7.67</v>
+        <v>7.02</v>
       </c>
       <c r="G25" t="n">
-        <v>157.9</v>
+        <v>151.4</v>
       </c>
       <c r="H25" t="n">
-        <v>95.09999999999999</v>
+        <v>55.6</v>
       </c>
       <c r="I25" t="n">
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>31.72</v>
+        <v>99.02</v>
       </c>
       <c r="K25" t="n">
-        <v>126.83</v>
+        <v>-90.52</v>
       </c>
       <c r="L25" t="n">
-        <v>130.74</v>
+        <v>134.16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:33:48</t>
+          <t>06:32:38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="F26" t="n">
-        <v>7.51</v>
+        <v>4.9</v>
       </c>
       <c r="G26" t="n">
-        <v>169.8</v>
+        <v>159.8</v>
       </c>
       <c r="H26" t="n">
-        <v>86.90000000000001</v>
+        <v>48.1</v>
       </c>
       <c r="I26" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>106.16</v>
+        <v>156.94</v>
       </c>
       <c r="K26" t="n">
-        <v>196.64</v>
+        <v>75.98</v>
       </c>
       <c r="L26" t="n">
-        <v>223.47</v>
+        <v>174.36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:35:08</t>
+          <t>06:33:36</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="F27" t="n">
-        <v>5.96</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>163.1</v>
+        <v>167.6</v>
       </c>
       <c r="H27" t="n">
-        <v>85.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J27" t="n">
-        <v>338.33</v>
+        <v>161.1</v>
       </c>
       <c r="K27" t="n">
-        <v>139.05</v>
+        <v>-69.3</v>
       </c>
       <c r="L27" t="n">
-        <v>365.79</v>
+        <v>175.37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:36:58</t>
+          <t>06:34:35</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="F28" t="n">
-        <v>5.4</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G28" t="n">
-        <v>162.9</v>
+        <v>165.1</v>
       </c>
       <c r="H28" t="n">
-        <v>86.09999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>124.06</v>
+        <v>-163.39</v>
       </c>
       <c r="K28" t="n">
-        <v>170.51</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>210.87</v>
+        <v>182.74</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:49:57</t>
+          <t>06:44:30</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.28</v>
+        <v>3.01</v>
       </c>
       <c r="F29" t="n">
-        <v>7.7</v>
+        <v>7.09</v>
       </c>
       <c r="G29" t="n">
-        <v>167.9</v>
+        <v>167.7</v>
       </c>
       <c r="H29" t="n">
-        <v>83.40000000000001</v>
+        <v>75.5</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>-13.41</v>
+        <v>38.09</v>
       </c>
       <c r="K29" t="n">
-        <v>-66.58</v>
+        <v>-30.31</v>
       </c>
       <c r="L29" t="n">
-        <v>67.91</v>
+        <v>48.68</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:52:13</t>
+          <t>06:46:37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="F30" t="n">
-        <v>5.74</v>
+        <v>7.64</v>
       </c>
       <c r="G30" t="n">
-        <v>161.6</v>
+        <v>159.9</v>
       </c>
       <c r="H30" t="n">
-        <v>89.5</v>
+        <v>59.8</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>-20.35</v>
+        <v>33.31</v>
       </c>
       <c r="K30" t="n">
-        <v>68.44</v>
+        <v>0.73</v>
       </c>
       <c r="L30" t="n">
-        <v>71.40000000000001</v>
+        <v>33.32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:52:57</t>
+          <t>06:48:53</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="F31" t="n">
-        <v>8.130000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G31" t="n">
-        <v>164.1</v>
+        <v>167.5</v>
       </c>
       <c r="H31" t="n">
-        <v>84.8</v>
+        <v>45.3</v>
       </c>
       <c r="I31" t="n">
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>-32.01</v>
+        <v>-37.31</v>
       </c>
       <c r="K31" t="n">
-        <v>-51.77</v>
+        <v>0.12</v>
       </c>
       <c r="L31" t="n">
-        <v>60.87</v>
+        <v>37.31</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:57:05</t>
+          <t>06:52:38</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="F32" t="n">
-        <v>8.619999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>155.5</v>
+        <v>160.3</v>
       </c>
       <c r="H32" t="n">
-        <v>85.59999999999999</v>
+        <v>59</v>
       </c>
       <c r="I32" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J32" t="n">
-        <v>19.44</v>
+        <v>15.15</v>
       </c>
       <c r="K32" t="n">
-        <v>90.2</v>
+        <v>-56.8</v>
       </c>
       <c r="L32" t="n">
-        <v>92.27</v>
+        <v>58.79</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:58:23</t>
+          <t>06:54:23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="F33" t="n">
-        <v>6.84</v>
+        <v>2.53</v>
       </c>
       <c r="G33" t="n">
-        <v>177.4</v>
+        <v>157.3</v>
       </c>
       <c r="H33" t="n">
-        <v>90.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>63.22</v>
+        <v>0.79</v>
       </c>
       <c r="K33" t="n">
-        <v>-31.75</v>
+        <v>41.11</v>
       </c>
       <c r="L33" t="n">
-        <v>70.73999999999999</v>
+        <v>41.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:00:37</t>
+          <t>06:56:11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="F34" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="G34" t="n">
-        <v>167</v>
+        <v>175.9</v>
       </c>
       <c r="H34" t="n">
-        <v>87.40000000000001</v>
+        <v>41</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>-62.91</v>
+        <v>13.32</v>
       </c>
       <c r="K34" t="n">
-        <v>19.06</v>
+        <v>-55.28</v>
       </c>
       <c r="L34" t="n">
-        <v>65.73</v>
+        <v>56.86</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:06:02</t>
+          <t>07:01:34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="F35" t="n">
-        <v>5.2</v>
+        <v>6.68</v>
       </c>
       <c r="G35" t="n">
-        <v>166.1</v>
+        <v>155.9</v>
       </c>
       <c r="H35" t="n">
-        <v>88.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>78.2</v>
+        <v>-70.17</v>
       </c>
       <c r="K35" t="n">
-        <v>64.87</v>
+        <v>22.1</v>
       </c>
       <c r="L35" t="n">
-        <v>101.6</v>
+        <v>73.56999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:06:32</t>
+          <t>07:02:38</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.32</v>
+        <v>1.55</v>
       </c>
       <c r="F36" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>165.9</v>
+        <v>159.8</v>
       </c>
       <c r="H36" t="n">
-        <v>84.5</v>
+        <v>78.7</v>
       </c>
       <c r="I36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>110.81</v>
+        <v>61.34</v>
       </c>
       <c r="K36" t="n">
-        <v>-62.02</v>
+        <v>-49.29</v>
       </c>
       <c r="L36" t="n">
-        <v>126.99</v>
+        <v>78.69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:08:52</t>
+          <t>07:05:00</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.96</v>
+        <v>1.46</v>
       </c>
       <c r="F37" t="n">
-        <v>3.16</v>
+        <v>1.76</v>
       </c>
       <c r="G37" t="n">
-        <v>160.7</v>
+        <v>159.6</v>
       </c>
       <c r="H37" t="n">
-        <v>79.90000000000001</v>
+        <v>29.3</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>4.78</v>
+        <v>-77.29000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>-10.09</v>
+        <v>35.28</v>
       </c>
       <c r="L37" t="n">
-        <v>11.16</v>
+        <v>84.95999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:14:13</t>
+          <t>07:08:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="F38" t="n">
-        <v>6.9</v>
+        <v>6.25</v>
       </c>
       <c r="G38" t="n">
-        <v>159.3</v>
+        <v>165.4</v>
       </c>
       <c r="H38" t="n">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>-178.72</v>
+        <v>-67.5</v>
       </c>
       <c r="K38" t="n">
-        <v>63.42</v>
+        <v>-120.65</v>
       </c>
       <c r="L38" t="n">
-        <v>189.64</v>
+        <v>138.25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:15:19</t>
+          <t>07:09:40</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.48</v>
+        <v>2.11</v>
       </c>
       <c r="F39" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="G39" t="n">
-        <v>154.4</v>
+        <v>161.7</v>
       </c>
       <c r="H39" t="n">
-        <v>92.2</v>
+        <v>46.9</v>
       </c>
       <c r="I39" t="n">
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-179.15</v>
+        <v>-33.68</v>
       </c>
       <c r="K39" t="n">
-        <v>-61.61</v>
+        <v>131.7</v>
       </c>
       <c r="L39" t="n">
-        <v>189.44</v>
+        <v>135.94</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:17:15</t>
+          <t>07:10:32</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.01</v>
+        <v>1.72</v>
       </c>
       <c r="F40" t="n">
-        <v>8.619999999999999</v>
+        <v>7.92</v>
       </c>
       <c r="G40" t="n">
-        <v>156.1</v>
+        <v>146.8</v>
       </c>
       <c r="H40" t="n">
-        <v>78</v>
+        <v>50.2</v>
       </c>
       <c r="I40" t="n">
         <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>126.45</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>78.34999999999999</v>
+        <v>93.53</v>
       </c>
       <c r="L40" t="n">
-        <v>148.76</v>
+        <v>123.96</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:22:20</t>
+          <t>07:13:44</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="F41" t="n">
-        <v>5.6</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>150.7</v>
+        <v>183.7</v>
       </c>
       <c r="H41" t="n">
-        <v>81.90000000000001</v>
+        <v>66</v>
       </c>
       <c r="I41" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-143.9</v>
+        <v>-105.04</v>
       </c>
       <c r="K41" t="n">
-        <v>241.44</v>
+        <v>-101.94</v>
       </c>
       <c r="L41" t="n">
-        <v>281.07</v>
+        <v>146.37</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:23:54</t>
+          <t>07:16:11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.54</v>
+        <v>1.6</v>
       </c>
       <c r="F42" t="n">
-        <v>8.619999999999999</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>170.3</v>
+        <v>162.6</v>
       </c>
       <c r="H42" t="n">
-        <v>79.59999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J42" t="n">
-        <v>-270.78</v>
+        <v>171.47</v>
       </c>
       <c r="K42" t="n">
-        <v>-55.4</v>
+        <v>47.42</v>
       </c>
       <c r="L42" t="n">
-        <v>276.39</v>
+        <v>177.91</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:24:32</t>
+          <t>07:17:07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.01</v>
+        <v>1.81</v>
       </c>
       <c r="F43" t="n">
-        <v>6.47</v>
+        <v>5.17</v>
       </c>
       <c r="G43" t="n">
-        <v>155.6</v>
+        <v>171.5</v>
       </c>
       <c r="H43" t="n">
-        <v>85.59999999999999</v>
+        <v>47.3</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>216.63</v>
+        <v>-10.52</v>
       </c>
       <c r="K43" t="n">
-        <v>1.17</v>
+        <v>-179.44</v>
       </c>
       <c r="L43" t="n">
-        <v>216.64</v>
+        <v>179.75</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:36:20</t>
+          <t>07:25:54</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="F44" t="n">
-        <v>8.619999999999999</v>
+        <v>7.44</v>
       </c>
       <c r="G44" t="n">
-        <v>166.6</v>
+        <v>159.2</v>
       </c>
       <c r="H44" t="n">
-        <v>84.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>-23.95</v>
+        <v>-27.42</v>
       </c>
       <c r="K44" t="n">
-        <v>77.04000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="L44" t="n">
-        <v>80.67</v>
+        <v>27.43</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:37:07</t>
+          <t>07:27:43</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="F45" t="n">
-        <v>8.619999999999999</v>
+        <v>6.13</v>
       </c>
       <c r="G45" t="n">
-        <v>159.7</v>
+        <v>158.5</v>
       </c>
       <c r="H45" t="n">
-        <v>81.8</v>
+        <v>83.2</v>
       </c>
       <c r="I45" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J45" t="n">
-        <v>0.68</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="K45" t="n">
-        <v>61.37</v>
+        <v>-38.19</v>
       </c>
       <c r="L45" t="n">
-        <v>61.38</v>
+        <v>39.05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:38:48</t>
+          <t>07:28:50</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.04</v>
+        <v>2.09</v>
       </c>
       <c r="F46" t="n">
-        <v>8.26</v>
+        <v>7.13</v>
       </c>
       <c r="G46" t="n">
-        <v>171.6</v>
+        <v>175.4</v>
       </c>
       <c r="H46" t="n">
-        <v>86.3</v>
+        <v>28.5</v>
       </c>
       <c r="I46" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J46" t="n">
-        <v>38.82</v>
+        <v>-13</v>
       </c>
       <c r="K46" t="n">
-        <v>-72.97</v>
+        <v>35.43</v>
       </c>
       <c r="L46" t="n">
-        <v>82.65000000000001</v>
+        <v>37.74</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:42:57</t>
+          <t>07:33:10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.75</v>
+        <v>2.28</v>
       </c>
       <c r="F47" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>151.7</v>
+        <v>177.9</v>
       </c>
       <c r="H47" t="n">
-        <v>85.90000000000001</v>
+        <v>30.6</v>
       </c>
       <c r="I47" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J47" t="n">
-        <v>50.11</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>105.91</v>
+        <v>-30.98</v>
       </c>
       <c r="L47" t="n">
-        <v>117.16</v>
+        <v>32.03</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:44:31</t>
+          <t>07:35:24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="F48" t="n">
-        <v>7.38</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>171.9</v>
+        <v>160.1</v>
       </c>
       <c r="H48" t="n">
-        <v>80.40000000000001</v>
+        <v>33.4</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>53.31</v>
+        <v>-5.85</v>
       </c>
       <c r="K48" t="n">
-        <v>42.15</v>
+        <v>-50.06</v>
       </c>
       <c r="L48" t="n">
-        <v>67.95999999999999</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:46:14</t>
+          <t>07:37:46</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.85</v>
+        <v>1.68</v>
       </c>
       <c r="F49" t="n">
-        <v>8.619999999999999</v>
+        <v>6.68</v>
       </c>
       <c r="G49" t="n">
-        <v>153.2</v>
+        <v>156.8</v>
       </c>
       <c r="H49" t="n">
-        <v>94.09999999999999</v>
+        <v>50.9</v>
       </c>
       <c r="I49" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>-84.89</v>
+        <v>55.34</v>
       </c>
       <c r="K49" t="n">
-        <v>-105.18</v>
+        <v>8.48</v>
       </c>
       <c r="L49" t="n">
-        <v>135.16</v>
+        <v>55.99</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:49:56</t>
+          <t>07:41:29</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="F50" t="n">
-        <v>5.45</v>
+        <v>4.77</v>
       </c>
       <c r="G50" t="n">
-        <v>167</v>
+        <v>154.7</v>
       </c>
       <c r="H50" t="n">
-        <v>90.3</v>
+        <v>77.7</v>
       </c>
       <c r="I50" t="n">
         <v>20</v>
       </c>
       <c r="J50" t="n">
-        <v>-39.63</v>
+        <v>-55.64</v>
       </c>
       <c r="K50" t="n">
-        <v>147.71</v>
+        <v>-19.26</v>
       </c>
       <c r="L50" t="n">
-        <v>152.93</v>
+        <v>58.88</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:51:43</t>
+          <t>07:42:37</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="F51" t="n">
-        <v>8.4</v>
+        <v>6.33</v>
       </c>
       <c r="G51" t="n">
-        <v>160.5</v>
+        <v>168.5</v>
       </c>
       <c r="H51" t="n">
-        <v>94.90000000000001</v>
+        <v>50.6</v>
       </c>
       <c r="I51" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J51" t="n">
-        <v>-127.48</v>
+        <v>-73.36</v>
       </c>
       <c r="K51" t="n">
-        <v>-60.03</v>
+        <v>52.04</v>
       </c>
       <c r="L51" t="n">
-        <v>140.91</v>
+        <v>89.94</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:53:59</t>
+          <t>07:43:45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="F52" t="n">
-        <v>5.25</v>
+        <v>6.87</v>
       </c>
       <c r="G52" t="n">
-        <v>157.1</v>
+        <v>162</v>
       </c>
       <c r="H52" t="n">
-        <v>87.09999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-115.57</v>
+        <v>-13.35</v>
       </c>
       <c r="K52" t="n">
-        <v>-28.99</v>
+        <v>-81.05</v>
       </c>
       <c r="L52" t="n">
-        <v>119.15</v>
+        <v>82.14</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:59:04</t>
+          <t>07:48:33</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.97</v>
+        <v>1.58</v>
       </c>
       <c r="F53" t="n">
-        <v>5.81</v>
+        <v>5.29</v>
       </c>
       <c r="G53" t="n">
-        <v>153.7</v>
+        <v>148</v>
       </c>
       <c r="H53" t="n">
-        <v>85.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="I53" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>167.35</v>
+        <v>138.15</v>
       </c>
       <c r="K53" t="n">
-        <v>-29.37</v>
+        <v>28.03</v>
       </c>
       <c r="L53" t="n">
-        <v>169.91</v>
+        <v>140.97</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:00:10</t>
+          <t>07:50:51</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="F54" t="n">
-        <v>8.619999999999999</v>
+        <v>6.36</v>
       </c>
       <c r="G54" t="n">
-        <v>161.7</v>
+        <v>163.4</v>
       </c>
       <c r="H54" t="n">
-        <v>92.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I54" t="n">
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>-123.78</v>
+        <v>48.65</v>
       </c>
       <c r="K54" t="n">
-        <v>144.81</v>
+        <v>-113.23</v>
       </c>
       <c r="L54" t="n">
-        <v>190.51</v>
+        <v>123.23</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:01:50</t>
+          <t>07:52:02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.33</v>
+        <v>1.88</v>
       </c>
       <c r="F55" t="n">
-        <v>3.28</v>
+        <v>4.41</v>
       </c>
       <c r="G55" t="n">
-        <v>156.3</v>
+        <v>164.1</v>
       </c>
       <c r="H55" t="n">
-        <v>83.3</v>
+        <v>80.5</v>
       </c>
       <c r="I55" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J55" t="n">
-        <v>57.06</v>
+        <v>93.67</v>
       </c>
       <c r="K55" t="n">
-        <v>-112.81</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>126.42</v>
+        <v>124.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:07:07</t>
+          <t>07:56:37</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="F56" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>151.9</v>
+        <v>172</v>
       </c>
       <c r="H56" t="n">
-        <v>85.09999999999999</v>
+        <v>33.6</v>
       </c>
       <c r="I56" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J56" t="n">
-        <v>170.78</v>
+        <v>177.3</v>
       </c>
       <c r="K56" t="n">
-        <v>-125.29</v>
+        <v>-89.66</v>
       </c>
       <c r="L56" t="n">
-        <v>211.81</v>
+        <v>198.68</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:10:00</t>
+          <t>07:59:21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.12</v>
+        <v>1.82</v>
       </c>
       <c r="F57" t="n">
-        <v>5.66</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>167</v>
+        <v>156.7</v>
       </c>
       <c r="H57" t="n">
-        <v>87.40000000000001</v>
+        <v>44.9</v>
       </c>
       <c r="I57" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>126.86</v>
+        <v>127.84</v>
       </c>
       <c r="K57" t="n">
-        <v>-227.56</v>
+        <v>114.58</v>
       </c>
       <c r="L57" t="n">
-        <v>260.53</v>
+        <v>171.67</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:10:50</t>
+          <t>08:01:34</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="F58" t="n">
-        <v>8.619999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="G58" t="n">
-        <v>178.5</v>
+        <v>163</v>
       </c>
       <c r="H58" t="n">
-        <v>83.3</v>
+        <v>53.7</v>
       </c>
       <c r="I58" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J58" t="n">
-        <v>165.73</v>
+        <v>12.27</v>
       </c>
       <c r="K58" t="n">
-        <v>-159.21</v>
+        <v>-135.54</v>
       </c>
       <c r="L58" t="n">
-        <v>229.81</v>
+        <v>136.09</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:22:02</t>
+          <t>08:11:16</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="F59" t="n">
-        <v>8.42</v>
+        <v>8.34</v>
       </c>
       <c r="G59" t="n">
-        <v>164.4</v>
+        <v>154.9</v>
       </c>
       <c r="H59" t="n">
-        <v>92</v>
+        <v>80.3</v>
       </c>
       <c r="I59" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>5.76</v>
+        <v>18.31</v>
       </c>
       <c r="K59" t="n">
-        <v>-57.31</v>
+        <v>-25.36</v>
       </c>
       <c r="L59" t="n">
-        <v>57.59</v>
+        <v>31.28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:24:29</t>
+          <t>08:13:00</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="F60" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G60" t="n">
-        <v>153</v>
+        <v>161.8</v>
       </c>
       <c r="H60" t="n">
-        <v>79.7</v>
+        <v>60.3</v>
       </c>
       <c r="I60" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.16</v>
+        <v>38.41</v>
       </c>
       <c r="K60" t="n">
-        <v>-74.05</v>
+        <v>17.94</v>
       </c>
       <c r="L60" t="n">
-        <v>74.40000000000001</v>
+        <v>42.4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:26:33</t>
+          <t>08:13:31</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="F61" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>172.2</v>
+        <v>157.1</v>
       </c>
       <c r="H61" t="n">
-        <v>84.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="I61" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J61" t="n">
-        <v>33.98</v>
+        <v>28.58</v>
       </c>
       <c r="K61" t="n">
-        <v>44.82</v>
+        <v>-18.82</v>
       </c>
       <c r="L61" t="n">
-        <v>56.24</v>
+        <v>34.22</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:30:58</t>
+          <t>08:19:38</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.77</v>
+        <v>2.21</v>
       </c>
       <c r="F62" t="n">
-        <v>8.199999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>158.9</v>
+        <v>169.7</v>
       </c>
       <c r="H62" t="n">
-        <v>87.3</v>
+        <v>60.1</v>
       </c>
       <c r="I62" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J62" t="n">
-        <v>-89.93000000000001</v>
+        <v>-51.85</v>
       </c>
       <c r="K62" t="n">
-        <v>45.83</v>
+        <v>7.52</v>
       </c>
       <c r="L62" t="n">
-        <v>100.94</v>
+        <v>52.39</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:31:39</t>
+          <t>08:20:44</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="F63" t="n">
-        <v>8.220000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>148.3</v>
+        <v>148.2</v>
       </c>
       <c r="H63" t="n">
-        <v>85</v>
+        <v>78.8</v>
       </c>
       <c r="I63" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J63" t="n">
-        <v>-67.20999999999999</v>
+        <v>67</v>
       </c>
       <c r="K63" t="n">
-        <v>49.19</v>
+        <v>-38.99</v>
       </c>
       <c r="L63" t="n">
-        <v>83.29000000000001</v>
+        <v>77.52</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:33:43</t>
+          <t>08:23:11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="F64" t="n">
-        <v>4.31</v>
+        <v>6.86</v>
       </c>
       <c r="G64" t="n">
-        <v>162.9</v>
+        <v>159.9</v>
       </c>
       <c r="H64" t="n">
-        <v>85.2</v>
+        <v>46.7</v>
       </c>
       <c r="I64" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J64" t="n">
-        <v>-55.77</v>
+        <v>49.38</v>
       </c>
       <c r="K64" t="n">
-        <v>55.99</v>
+        <v>-8.19</v>
       </c>
       <c r="L64" t="n">
-        <v>79.02</v>
+        <v>50.05</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:37:38</t>
+          <t>08:27:43</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.27</v>
+        <v>1.94</v>
       </c>
       <c r="F65" t="n">
-        <v>8.470000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="G65" t="n">
-        <v>159.5</v>
+        <v>170.3</v>
       </c>
       <c r="H65" t="n">
-        <v>89.09999999999999</v>
+        <v>36.6</v>
       </c>
       <c r="I65" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>121.65</v>
+        <v>-2.03</v>
       </c>
       <c r="K65" t="n">
-        <v>33.25</v>
+        <v>-65.11</v>
       </c>
       <c r="L65" t="n">
-        <v>126.12</v>
+        <v>65.14</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:39:24</t>
+          <t>08:29:21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="F66" t="n">
-        <v>3.76</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G66" t="n">
-        <v>161.3</v>
+        <v>164.5</v>
       </c>
       <c r="H66" t="n">
-        <v>86.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>156.12</v>
+        <v>60.1</v>
       </c>
       <c r="K66" t="n">
-        <v>29</v>
+        <v>-70.84</v>
       </c>
       <c r="L66" t="n">
-        <v>158.79</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:40:05</t>
+          <t>08:30:32</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="F67" t="n">
-        <v>6.13</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G67" t="n">
-        <v>158.3</v>
+        <v>160.5</v>
       </c>
       <c r="H67" t="n">
-        <v>87.3</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="I67" t="n">
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-31.07</v>
+        <v>12.61</v>
       </c>
       <c r="K67" t="n">
-        <v>123.79</v>
+        <v>-98.61</v>
       </c>
       <c r="L67" t="n">
-        <v>127.63</v>
+        <v>99.41</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:44:55</t>
+          <t>08:34:08</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.23</v>
+        <v>1.5</v>
       </c>
       <c r="F68" t="n">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="G68" t="n">
-        <v>152</v>
+        <v>164.4</v>
       </c>
       <c r="H68" t="n">
-        <v>88.09999999999999</v>
+        <v>48.8</v>
       </c>
       <c r="I68" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J68" t="n">
-        <v>-82.97</v>
+        <v>-4.52</v>
       </c>
       <c r="K68" t="n">
-        <v>-111.74</v>
+        <v>-119.49</v>
       </c>
       <c r="L68" t="n">
-        <v>139.18</v>
+        <v>119.57</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:46:48</t>
+          <t>08:36:06</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.87</v>
+        <v>2.11</v>
       </c>
       <c r="F69" t="n">
-        <v>3.42</v>
+        <v>4.77</v>
       </c>
       <c r="G69" t="n">
-        <v>161.4</v>
+        <v>174.4</v>
       </c>
       <c r="H69" t="n">
-        <v>88.3</v>
+        <v>85</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J69" t="n">
-        <v>74.91</v>
+        <v>31.09</v>
       </c>
       <c r="K69" t="n">
-        <v>-85.3</v>
+        <v>154.4</v>
       </c>
       <c r="L69" t="n">
-        <v>113.52</v>
+        <v>157.49</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:48:41</t>
+          <t>08:38:26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="F70" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>166</v>
+        <v>149.4</v>
       </c>
       <c r="H70" t="n">
-        <v>80.8</v>
+        <v>38.9</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-19.92</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>-199.17</v>
+        <v>-95.63</v>
       </c>
       <c r="L70" t="n">
-        <v>200.16</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:53:54</t>
+          <t>08:43:16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="F71" t="n">
-        <v>3.56</v>
+        <v>8.31</v>
       </c>
       <c r="G71" t="n">
-        <v>166.4</v>
+        <v>154.8</v>
       </c>
       <c r="H71" t="n">
-        <v>82.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J71" t="n">
-        <v>-101.73</v>
+        <v>-159.92</v>
       </c>
       <c r="K71" t="n">
-        <v>-206.64</v>
+        <v>-6.67</v>
       </c>
       <c r="L71" t="n">
-        <v>230.32</v>
+        <v>160.06</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:55:49</t>
+          <t>08:44:43</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="F72" t="n">
-        <v>7.95</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G72" t="n">
-        <v>162.1</v>
+        <v>161.8</v>
       </c>
       <c r="H72" t="n">
-        <v>89.3</v>
+        <v>63.5</v>
       </c>
       <c r="I72" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J72" t="n">
-        <v>135</v>
+        <v>-43.2</v>
       </c>
       <c r="K72" t="n">
-        <v>-171.95</v>
+        <v>122.67</v>
       </c>
       <c r="L72" t="n">
-        <v>218.62</v>
+        <v>130.05</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:57:47</t>
+          <t>08:46:35</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.41</v>
+        <v>1.83</v>
       </c>
       <c r="F73" t="n">
-        <v>1.76</v>
+        <v>7.74</v>
       </c>
       <c r="G73" t="n">
-        <v>161.4</v>
+        <v>164.5</v>
       </c>
       <c r="H73" t="n">
-        <v>85.90000000000001</v>
+        <v>53.2</v>
       </c>
       <c r="I73" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="J73" t="n">
-        <v>159.55</v>
+        <v>39.59</v>
       </c>
       <c r="K73" t="n">
-        <v>-84.94</v>
+        <v>-219.71</v>
       </c>
       <c r="L73" t="n">
-        <v>180.75</v>
+        <v>223.25</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:07:44</t>
+          <t>08:59:02</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="F74" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>172.4</v>
+        <v>155.5</v>
       </c>
       <c r="H74" t="n">
-        <v>78.3</v>
+        <v>32.5</v>
       </c>
       <c r="I74" t="n">
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-49.52</v>
+        <v>22.76</v>
       </c>
       <c r="K74" t="n">
-        <v>-27.27</v>
+        <v>18.02</v>
       </c>
       <c r="L74" t="n">
-        <v>56.53</v>
+        <v>29.03</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:10:25</t>
+          <t>09:00:21</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.84</v>
+        <v>2.01</v>
       </c>
       <c r="F75" t="n">
-        <v>8.619999999999999</v>
+        <v>6.95</v>
       </c>
       <c r="G75" t="n">
-        <v>167.4</v>
+        <v>158.4</v>
       </c>
       <c r="H75" t="n">
-        <v>79.2</v>
+        <v>75.5</v>
       </c>
       <c r="I75" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-76.51000000000001</v>
+        <v>13.72</v>
       </c>
       <c r="K75" t="n">
-        <v>8.130000000000001</v>
+        <v>22.15</v>
       </c>
       <c r="L75" t="n">
-        <v>76.94</v>
+        <v>26.05</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:12:43</t>
+          <t>09:01:40</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.21</v>
+        <v>2.01</v>
       </c>
       <c r="F76" t="n">
-        <v>8.619999999999999</v>
+        <v>5.75</v>
       </c>
       <c r="G76" t="n">
-        <v>166.3</v>
+        <v>171</v>
       </c>
       <c r="H76" t="n">
-        <v>84.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J76" t="n">
-        <v>65.55</v>
+        <v>-39.47</v>
       </c>
       <c r="K76" t="n">
-        <v>-16.94</v>
+        <v>10.18</v>
       </c>
       <c r="L76" t="n">
-        <v>67.70999999999999</v>
+        <v>40.76</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:17:17</t>
+          <t>09:06:02</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="F77" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G77" t="n">
-        <v>163.7</v>
+        <v>157.4</v>
       </c>
       <c r="H77" t="n">
-        <v>91.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="I77" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J77" t="n">
-        <v>-40.34</v>
+        <v>-34.92</v>
       </c>
       <c r="K77" t="n">
-        <v>-96.45999999999999</v>
+        <v>50.86</v>
       </c>
       <c r="L77" t="n">
-        <v>104.55</v>
+        <v>61.7</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:18:30</t>
+          <t>09:08:05</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.07</v>
+        <v>2.56</v>
       </c>
       <c r="F78" t="n">
-        <v>5.18</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G78" t="n">
-        <v>166.3</v>
+        <v>161.2</v>
       </c>
       <c r="H78" t="n">
-        <v>86.90000000000001</v>
+        <v>18.6</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J78" t="n">
-        <v>50.55</v>
+        <v>37.97</v>
       </c>
       <c r="K78" t="n">
-        <v>107.81</v>
+        <v>14.32</v>
       </c>
       <c r="L78" t="n">
-        <v>119.07</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:19:50</t>
+          <t>09:09:26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.07</v>
+        <v>2.46</v>
       </c>
       <c r="F79" t="n">
-        <v>7.08</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G79" t="n">
-        <v>176.7</v>
+        <v>162.5</v>
       </c>
       <c r="H79" t="n">
-        <v>83.3</v>
+        <v>45.8</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J79" t="n">
-        <v>-47.83</v>
+        <v>-49.14</v>
       </c>
       <c r="K79" t="n">
-        <v>60.24</v>
+        <v>-19.33</v>
       </c>
       <c r="L79" t="n">
-        <v>76.92</v>
+        <v>52.81</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:24:39</t>
+          <t>09:14:21</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.18</v>
+        <v>2.43</v>
       </c>
       <c r="F80" t="n">
-        <v>8.619999999999999</v>
+        <v>7.26</v>
       </c>
       <c r="G80" t="n">
-        <v>164.9</v>
+        <v>165.1</v>
       </c>
       <c r="H80" t="n">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="I80" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>69.45</v>
+        <v>79.44</v>
       </c>
       <c r="K80" t="n">
-        <v>-103.04</v>
+        <v>36.62</v>
       </c>
       <c r="L80" t="n">
-        <v>124.26</v>
+        <v>87.48</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:26:04</t>
+          <t>09:16:33</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.26</v>
+        <v>2.13</v>
       </c>
       <c r="F81" t="n">
-        <v>8.4</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>159.7</v>
+        <v>164</v>
       </c>
       <c r="H81" t="n">
-        <v>86</v>
+        <v>57.5</v>
       </c>
       <c r="I81" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>166.64</v>
+        <v>-18.64</v>
       </c>
       <c r="K81" t="n">
-        <v>7.99</v>
+        <v>-82.98</v>
       </c>
       <c r="L81" t="n">
-        <v>166.83</v>
+        <v>85.05</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:27:58</t>
+          <t>09:18:05</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.99</v>
+        <v>1.55</v>
       </c>
       <c r="F82" t="n">
-        <v>8.619999999999999</v>
+        <v>3.78</v>
       </c>
       <c r="G82" t="n">
-        <v>158</v>
+        <v>163.4</v>
       </c>
       <c r="H82" t="n">
-        <v>86.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>105.47</v>
+        <v>-10.52</v>
       </c>
       <c r="K82" t="n">
-        <v>-93.12</v>
+        <v>-66</v>
       </c>
       <c r="L82" t="n">
-        <v>140.7</v>
+        <v>66.84</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:32:14</t>
+          <t>09:22:15</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="F83" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G83" t="n">
-        <v>167.2</v>
+        <v>162.7</v>
       </c>
       <c r="H83" t="n">
-        <v>91.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="I83" t="n">
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-91.83</v>
+        <v>166.5</v>
       </c>
       <c r="K83" t="n">
-        <v>161.6</v>
+        <v>119.35</v>
       </c>
       <c r="L83" t="n">
-        <v>185.87</v>
+        <v>204.86</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:33:58</t>
+          <t>09:24:01</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="F84" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G84" t="n">
-        <v>164.1</v>
+        <v>148.5</v>
       </c>
       <c r="H84" t="n">
-        <v>84.7</v>
+        <v>54.9</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>-63.05</v>
+        <v>-71.84999999999999</v>
       </c>
       <c r="K84" t="n">
-        <v>129.38</v>
+        <v>-95.98</v>
       </c>
       <c r="L84" t="n">
-        <v>143.93</v>
+        <v>119.9</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:34:52</t>
+          <t>09:24:52</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.39</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
-        <v>7.13</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G85" t="n">
-        <v>153.3</v>
+        <v>166.8</v>
       </c>
       <c r="H85" t="n">
-        <v>89.7</v>
+        <v>100</v>
       </c>
       <c r="I85" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J85" t="n">
-        <v>20.04</v>
+        <v>128.36</v>
       </c>
       <c r="K85" t="n">
-        <v>-148.88</v>
+        <v>-12.42</v>
       </c>
       <c r="L85" t="n">
-        <v>150.23</v>
+        <v>128.96</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:38:50</t>
+          <t>09:30:35</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.05</v>
+        <v>2.46</v>
       </c>
       <c r="F86" t="n">
-        <v>8.619999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G86" t="n">
-        <v>166.7</v>
+        <v>166.4</v>
       </c>
       <c r="H86" t="n">
-        <v>85.09999999999999</v>
+        <v>46.9</v>
       </c>
       <c r="I86" t="n">
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>-260.17</v>
+        <v>-70.48</v>
       </c>
       <c r="K86" t="n">
-        <v>187.21</v>
+        <v>164.89</v>
       </c>
       <c r="L86" t="n">
-        <v>320.53</v>
+        <v>179.32</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:40:18</t>
+          <t>09:32:59</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="F87" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>147</v>
+        <v>172.5</v>
       </c>
       <c r="H87" t="n">
-        <v>90.40000000000001</v>
+        <v>61.5</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J87" t="n">
-        <v>305.53</v>
+        <v>58.34</v>
       </c>
       <c r="K87" t="n">
-        <v>-13.63</v>
+        <v>-122.32</v>
       </c>
       <c r="L87" t="n">
-        <v>305.83</v>
+        <v>135.52</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:42:22</t>
+          <t>09:35:10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="F88" t="n">
-        <v>8.4</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G88" t="n">
         <v>152.9</v>
       </c>
       <c r="H88" t="n">
-        <v>85.90000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>230.34</v>
+        <v>-71.11</v>
       </c>
       <c r="K88" t="n">
-        <v>-228.96</v>
+        <v>-142.56</v>
       </c>
       <c r="L88" t="n">
-        <v>324.77</v>
+        <v>159.31</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-22.xlsx
+++ b/output/2025-08-22.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.54</v>
+        <v>1.96</v>
       </c>
       <c r="F14" t="n">
-        <v>2.53</v>
+        <v>7.54</v>
       </c>
       <c r="G14" t="n">
-        <v>174.5</v>
+        <v>163.3</v>
       </c>
       <c r="H14" t="n">
-        <v>66.2</v>
+        <v>36.8</v>
       </c>
       <c r="I14" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J14" t="n">
-        <v>24.33</v>
+        <v>-34.14</v>
       </c>
       <c r="K14" t="n">
-        <v>-12.69</v>
+        <v>-18.68</v>
       </c>
       <c r="L14" t="n">
-        <v>27.44</v>
+        <v>38.91</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:01:32</t>
+          <t>06:02:10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="F15" t="n">
-        <v>7.02</v>
+        <v>1.66</v>
       </c>
       <c r="G15" t="n">
-        <v>164</v>
+        <v>158.7</v>
       </c>
       <c r="H15" t="n">
-        <v>74.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>24.98</v>
+        <v>-25.35</v>
       </c>
       <c r="K15" t="n">
-        <v>-8.039999999999999</v>
+        <v>31.34</v>
       </c>
       <c r="L15" t="n">
-        <v>26.24</v>
+        <v>40.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:03:38</t>
+          <t>06:03:49</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="F16" t="n">
-        <v>8.52</v>
+        <v>7.09</v>
       </c>
       <c r="G16" t="n">
-        <v>167.6</v>
+        <v>150.2</v>
       </c>
       <c r="H16" t="n">
-        <v>56.7</v>
+        <v>78.5</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J16" t="n">
-        <v>-28.05</v>
+        <v>-3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>20.83</v>
+        <v>29.57</v>
       </c>
       <c r="L16" t="n">
-        <v>34.93</v>
+        <v>29.81</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:08:14</t>
+          <t>06:08:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="F17" t="n">
-        <v>8.619999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="G17" t="n">
-        <v>171.2</v>
+        <v>168</v>
       </c>
       <c r="H17" t="n">
-        <v>40.3</v>
+        <v>60.6</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-16.16</v>
+        <v>-35.51</v>
       </c>
       <c r="K17" t="n">
-        <v>-46.21</v>
+        <v>54.86</v>
       </c>
       <c r="L17" t="n">
-        <v>48.95</v>
+        <v>65.34999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:09:44</t>
+          <t>06:09:45</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.61</v>
+        <v>1.9</v>
       </c>
       <c r="F18" t="n">
-        <v>4.1</v>
+        <v>8</v>
       </c>
       <c r="G18" t="n">
-        <v>156</v>
+        <v>167.1</v>
       </c>
       <c r="H18" t="n">
-        <v>56.1</v>
+        <v>71.5</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-14.78</v>
+        <v>44.28</v>
       </c>
       <c r="K18" t="n">
-        <v>-42.22</v>
+        <v>-25.01</v>
       </c>
       <c r="L18" t="n">
-        <v>44.73</v>
+        <v>50.85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:11:47</t>
+          <t>06:11:59</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="F19" t="n">
-        <v>8.619999999999999</v>
+        <v>5.09</v>
       </c>
       <c r="G19" t="n">
-        <v>154.5</v>
+        <v>155.8</v>
       </c>
       <c r="H19" t="n">
-        <v>73.7</v>
+        <v>61.9</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J19" t="n">
-        <v>-27.99</v>
+        <v>22.94</v>
       </c>
       <c r="K19" t="n">
-        <v>13.19</v>
+        <v>-49.42</v>
       </c>
       <c r="L19" t="n">
-        <v>30.94</v>
+        <v>54.49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:16:35</t>
+          <t>06:16:23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="F20" t="n">
-        <v>6.03</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>165.6</v>
+        <v>163.3</v>
       </c>
       <c r="H20" t="n">
-        <v>65.09999999999999</v>
+        <v>58.3</v>
       </c>
       <c r="I20" t="n">
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>75.63</v>
+        <v>79.48999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>35.4</v>
+        <v>33.08</v>
       </c>
       <c r="L20" t="n">
-        <v>83.5</v>
+        <v>86.09999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:18:54</t>
+          <t>06:18:28</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.39</v>
+        <v>1.94</v>
       </c>
       <c r="F21" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>166.5</v>
+        <v>161</v>
       </c>
       <c r="H21" t="n">
-        <v>38.3</v>
+        <v>53.6</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-44.21</v>
+        <v>-26.62</v>
       </c>
       <c r="K21" t="n">
-        <v>15.32</v>
+        <v>-79.75</v>
       </c>
       <c r="L21" t="n">
-        <v>46.79</v>
+        <v>84.08</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:21:00</t>
+          <t>06:19:56</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.33</v>
+        <v>1.77</v>
       </c>
       <c r="F22" t="n">
-        <v>7.32</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G22" t="n">
         <v>159.7</v>
       </c>
       <c r="H22" t="n">
-        <v>100</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>64.81999999999999</v>
+        <v>-42.44</v>
       </c>
       <c r="K22" t="n">
-        <v>-51.74</v>
+        <v>36.97</v>
       </c>
       <c r="L22" t="n">
-        <v>82.94</v>
+        <v>56.28</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>06:25:32</t>
+          <t>06:23:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="F23" t="n">
-        <v>5.42</v>
+        <v>8.56</v>
       </c>
       <c r="G23" t="n">
-        <v>164.5</v>
+        <v>161.9</v>
       </c>
       <c r="H23" t="n">
-        <v>81.7</v>
+        <v>61.8</v>
       </c>
       <c r="I23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>49.41</v>
+        <v>-66.67</v>
       </c>
       <c r="K23" t="n">
-        <v>-98.2</v>
+        <v>-112.16</v>
       </c>
       <c r="L23" t="n">
-        <v>109.93</v>
+        <v>130.48</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>06:27:06</t>
+          <t>06:25:00</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="F24" t="n">
-        <v>5.8</v>
+        <v>5.81</v>
       </c>
       <c r="G24" t="n">
-        <v>161</v>
+        <v>161.1</v>
       </c>
       <c r="H24" t="n">
-        <v>100</v>
+        <v>75.8</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J24" t="n">
-        <v>97.59</v>
+        <v>34.49</v>
       </c>
       <c r="K24" t="n">
-        <v>54.16</v>
+        <v>115.65</v>
       </c>
       <c r="L24" t="n">
-        <v>111.61</v>
+        <v>120.68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>06:29:10</t>
+          <t>06:26:52</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.64</v>
+        <v>1.98</v>
       </c>
       <c r="F25" t="n">
-        <v>7.02</v>
+        <v>5.13</v>
       </c>
       <c r="G25" t="n">
-        <v>151.4</v>
+        <v>170.6</v>
       </c>
       <c r="H25" t="n">
-        <v>55.6</v>
+        <v>63</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>99.02</v>
+        <v>113.63</v>
       </c>
       <c r="K25" t="n">
-        <v>-90.52</v>
+        <v>-65.16</v>
       </c>
       <c r="L25" t="n">
-        <v>134.16</v>
+        <v>130.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>06:32:38</t>
+          <t>06:31:57</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.38</v>
+        <v>2.07</v>
       </c>
       <c r="F26" t="n">
-        <v>4.9</v>
+        <v>6.58</v>
       </c>
       <c r="G26" t="n">
-        <v>159.8</v>
+        <v>166.8</v>
       </c>
       <c r="H26" t="n">
-        <v>48.1</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J26" t="n">
-        <v>156.94</v>
+        <v>2.67</v>
       </c>
       <c r="K26" t="n">
-        <v>75.98</v>
+        <v>-76.79000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>174.36</v>
+        <v>76.84</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>06:33:36</t>
+          <t>06:34:16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.41</v>
+        <v>3.42</v>
       </c>
       <c r="F27" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>167.6</v>
+        <v>175.4</v>
       </c>
       <c r="H27" t="n">
-        <v>78</v>
+        <v>40.6</v>
       </c>
       <c r="I27" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>161.1</v>
+        <v>-81.75</v>
       </c>
       <c r="K27" t="n">
-        <v>-69.3</v>
+        <v>-217.2</v>
       </c>
       <c r="L27" t="n">
-        <v>175.37</v>
+        <v>232.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>06:34:35</t>
+          <t>06:35:28</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="F28" t="n">
-        <v>8.619999999999999</v>
+        <v>7.98</v>
       </c>
       <c r="G28" t="n">
-        <v>165.1</v>
+        <v>160.8</v>
       </c>
       <c r="H28" t="n">
-        <v>65.3</v>
+        <v>99</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-163.39</v>
+        <v>145.62</v>
       </c>
       <c r="K28" t="n">
-        <v>81.84999999999999</v>
+        <v>57</v>
       </c>
       <c r="L28" t="n">
-        <v>182.74</v>
+        <v>156.38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>06:44:30</t>
+          <t>06:47:26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.01</v>
+        <v>1.62</v>
       </c>
       <c r="F29" t="n">
-        <v>7.09</v>
+        <v>3.17</v>
       </c>
       <c r="G29" t="n">
-        <v>167.7</v>
+        <v>161.9</v>
       </c>
       <c r="H29" t="n">
-        <v>75.5</v>
+        <v>32.7</v>
       </c>
       <c r="I29" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>38.09</v>
+        <v>-29.06</v>
       </c>
       <c r="K29" t="n">
-        <v>-30.31</v>
+        <v>7.7</v>
       </c>
       <c r="L29" t="n">
-        <v>48.68</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>06:46:37</t>
+          <t>06:49:44</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.2</v>
+        <v>1.78</v>
       </c>
       <c r="F30" t="n">
-        <v>7.64</v>
+        <v>5.15</v>
       </c>
       <c r="G30" t="n">
-        <v>159.9</v>
+        <v>153.2</v>
       </c>
       <c r="H30" t="n">
-        <v>59.8</v>
+        <v>19.9</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>33.31</v>
+        <v>16.61</v>
       </c>
       <c r="K30" t="n">
-        <v>0.73</v>
+        <v>-34.9</v>
       </c>
       <c r="L30" t="n">
-        <v>33.32</v>
+        <v>38.65</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>06:48:53</t>
+          <t>06:51:54</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.01</v>
+        <v>1.48</v>
       </c>
       <c r="F31" t="n">
-        <v>8.619999999999999</v>
+        <v>3.22</v>
       </c>
       <c r="G31" t="n">
-        <v>167.5</v>
+        <v>161.2</v>
       </c>
       <c r="H31" t="n">
-        <v>45.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J31" t="n">
-        <v>-37.31</v>
+        <v>-24.84</v>
       </c>
       <c r="K31" t="n">
-        <v>0.12</v>
+        <v>-21.65</v>
       </c>
       <c r="L31" t="n">
-        <v>37.31</v>
+        <v>32.95</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>06:52:38</t>
+          <t>06:56:21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.07</v>
+        <v>2.24</v>
       </c>
       <c r="F32" t="n">
-        <v>8.529999999999999</v>
+        <v>6.53</v>
       </c>
       <c r="G32" t="n">
-        <v>160.3</v>
+        <v>148.9</v>
       </c>
       <c r="H32" t="n">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="I32" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>15.15</v>
+        <v>-52.94</v>
       </c>
       <c r="K32" t="n">
-        <v>-56.8</v>
+        <v>-48.46</v>
       </c>
       <c r="L32" t="n">
-        <v>58.79</v>
+        <v>71.77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>06:54:23</t>
+          <t>06:57:14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="F33" t="n">
-        <v>2.53</v>
+        <v>7.77</v>
       </c>
       <c r="G33" t="n">
-        <v>157.3</v>
+        <v>165.4</v>
       </c>
       <c r="H33" t="n">
-        <v>65.59999999999999</v>
+        <v>34.7</v>
       </c>
       <c r="I33" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J33" t="n">
-        <v>0.79</v>
+        <v>-30.17</v>
       </c>
       <c r="K33" t="n">
-        <v>41.11</v>
+        <v>-24.25</v>
       </c>
       <c r="L33" t="n">
-        <v>41.12</v>
+        <v>38.71</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>06:56:11</t>
+          <t>06:59:32</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
       <c r="F34" t="n">
-        <v>7.6</v>
+        <v>6.87</v>
       </c>
       <c r="G34" t="n">
-        <v>175.9</v>
+        <v>157.5</v>
       </c>
       <c r="H34" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>13.32</v>
+        <v>-48.96</v>
       </c>
       <c r="K34" t="n">
-        <v>-55.28</v>
+        <v>13.24</v>
       </c>
       <c r="L34" t="n">
-        <v>56.86</v>
+        <v>50.72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:01:34</t>
+          <t>07:04:14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="F35" t="n">
-        <v>6.68</v>
+        <v>6.36</v>
       </c>
       <c r="G35" t="n">
-        <v>155.9</v>
+        <v>167.1</v>
       </c>
       <c r="H35" t="n">
-        <v>74.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J35" t="n">
-        <v>-70.17</v>
+        <v>26.86</v>
       </c>
       <c r="K35" t="n">
-        <v>22.1</v>
+        <v>-88.86</v>
       </c>
       <c r="L35" t="n">
-        <v>73.56999999999999</v>
+        <v>92.83</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:02:38</t>
+          <t>07:06:38</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="F36" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>159.8</v>
+        <v>188.5</v>
       </c>
       <c r="H36" t="n">
-        <v>78.7</v>
+        <v>55.7</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J36" t="n">
-        <v>61.34</v>
+        <v>-28.33</v>
       </c>
       <c r="K36" t="n">
-        <v>-49.29</v>
+        <v>-81.91</v>
       </c>
       <c r="L36" t="n">
-        <v>78.69</v>
+        <v>86.67</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:05:00</t>
+          <t>07:08:09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.46</v>
+        <v>1.76</v>
       </c>
       <c r="F37" t="n">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="G37" t="n">
-        <v>159.6</v>
+        <v>171.2</v>
       </c>
       <c r="H37" t="n">
-        <v>29.3</v>
+        <v>51.6</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J37" t="n">
-        <v>-77.29000000000001</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>35.28</v>
+        <v>1.6</v>
       </c>
       <c r="L37" t="n">
-        <v>84.95999999999999</v>
+        <v>98.94</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:08:13</t>
+          <t>07:13:38</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="F38" t="n">
-        <v>6.25</v>
+        <v>4.29</v>
       </c>
       <c r="G38" t="n">
-        <v>165.4</v>
+        <v>163.7</v>
       </c>
       <c r="H38" t="n">
-        <v>100</v>
+        <v>60.7</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-67.5</v>
+        <v>-4.63</v>
       </c>
       <c r="K38" t="n">
-        <v>-120.65</v>
+        <v>141.4</v>
       </c>
       <c r="L38" t="n">
-        <v>138.25</v>
+        <v>141.48</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:09:40</t>
+          <t>07:15:05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="F39" t="n">
-        <v>4.33</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>161.7</v>
+        <v>157.7</v>
       </c>
       <c r="H39" t="n">
-        <v>46.9</v>
+        <v>56.5</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>-33.68</v>
+        <v>149.74</v>
       </c>
       <c r="K39" t="n">
-        <v>131.7</v>
+        <v>-18.3</v>
       </c>
       <c r="L39" t="n">
-        <v>135.94</v>
+        <v>150.86</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:10:32</t>
+          <t>07:16:26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="F40" t="n">
-        <v>7.92</v>
+        <v>7.17</v>
       </c>
       <c r="G40" t="n">
-        <v>146.8</v>
+        <v>150.6</v>
       </c>
       <c r="H40" t="n">
-        <v>50.2</v>
+        <v>57.7</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>81.34999999999999</v>
+        <v>-125.78</v>
       </c>
       <c r="K40" t="n">
-        <v>93.53</v>
+        <v>-33.29</v>
       </c>
       <c r="L40" t="n">
-        <v>123.96</v>
+        <v>130.11</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:13:44</t>
+          <t>07:19:49</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="F41" t="n">
-        <v>8.619999999999999</v>
+        <v>6.61</v>
       </c>
       <c r="G41" t="n">
-        <v>183.7</v>
+        <v>169.9</v>
       </c>
       <c r="H41" t="n">
-        <v>66</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J41" t="n">
-        <v>-105.04</v>
+        <v>-134.18</v>
       </c>
       <c r="K41" t="n">
-        <v>-101.94</v>
+        <v>-66.20999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>146.37</v>
+        <v>149.63</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:16:11</t>
+          <t>07:21:58</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="F42" t="n">
-        <v>8.210000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>162.6</v>
+        <v>156.5</v>
       </c>
       <c r="H42" t="n">
-        <v>96.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="I42" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>171.47</v>
+        <v>54.99</v>
       </c>
       <c r="K42" t="n">
-        <v>47.42</v>
+        <v>184.29</v>
       </c>
       <c r="L42" t="n">
-        <v>177.91</v>
+        <v>192.32</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:17:07</t>
+          <t>07:23:01</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.81</v>
+        <v>2.28</v>
       </c>
       <c r="F43" t="n">
-        <v>5.17</v>
+        <v>7.88</v>
       </c>
       <c r="G43" t="n">
-        <v>171.5</v>
+        <v>153.6</v>
       </c>
       <c r="H43" t="n">
-        <v>47.3</v>
+        <v>48.4</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J43" t="n">
-        <v>-10.52</v>
+        <v>-261.14</v>
       </c>
       <c r="K43" t="n">
-        <v>-179.44</v>
+        <v>153.47</v>
       </c>
       <c r="L43" t="n">
-        <v>179.75</v>
+        <v>302.9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>07:25:54</t>
+          <t>07:35:34</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.05</v>
+        <v>2.26</v>
       </c>
       <c r="F44" t="n">
-        <v>7.44</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>159.2</v>
+        <v>159.1</v>
       </c>
       <c r="H44" t="n">
-        <v>81.2</v>
+        <v>50.7</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J44" t="n">
-        <v>-27.42</v>
+        <v>-29.67</v>
       </c>
       <c r="K44" t="n">
-        <v>0.63</v>
+        <v>-19.4</v>
       </c>
       <c r="L44" t="n">
-        <v>27.43</v>
+        <v>35.45</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>07:27:43</t>
+          <t>07:36:59</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="F45" t="n">
-        <v>6.13</v>
+        <v>7.38</v>
       </c>
       <c r="G45" t="n">
-        <v>158.5</v>
+        <v>166</v>
       </c>
       <c r="H45" t="n">
-        <v>83.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J45" t="n">
-        <v>8.140000000000001</v>
+        <v>-23.72</v>
       </c>
       <c r="K45" t="n">
-        <v>-38.19</v>
+        <v>28.56</v>
       </c>
       <c r="L45" t="n">
-        <v>39.05</v>
+        <v>37.12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>07:28:50</t>
+          <t>07:38:42</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.09</v>
+        <v>1.74</v>
       </c>
       <c r="F46" t="n">
-        <v>7.13</v>
+        <v>2.36</v>
       </c>
       <c r="G46" t="n">
-        <v>175.4</v>
+        <v>162.2</v>
       </c>
       <c r="H46" t="n">
-        <v>28.5</v>
+        <v>35.4</v>
       </c>
       <c r="I46" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J46" t="n">
-        <v>-13</v>
+        <v>-27.15</v>
       </c>
       <c r="K46" t="n">
-        <v>35.43</v>
+        <v>-23.78</v>
       </c>
       <c r="L46" t="n">
-        <v>37.74</v>
+        <v>36.09</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>07:33:10</t>
+          <t>07:42:20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.28</v>
+        <v>1.74</v>
       </c>
       <c r="F47" t="n">
-        <v>8.619999999999999</v>
+        <v>3.72</v>
       </c>
       <c r="G47" t="n">
-        <v>177.9</v>
+        <v>141.2</v>
       </c>
       <c r="H47" t="n">
-        <v>30.6</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J47" t="n">
-        <v>-8.130000000000001</v>
+        <v>-42.95</v>
       </c>
       <c r="K47" t="n">
-        <v>-30.98</v>
+        <v>22.11</v>
       </c>
       <c r="L47" t="n">
-        <v>32.03</v>
+        <v>48.3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>07:35:24</t>
+          <t>07:44:11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="F48" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G48" t="n">
-        <v>160.1</v>
+        <v>152.8</v>
       </c>
       <c r="H48" t="n">
-        <v>33.4</v>
+        <v>64.3</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-5.85</v>
+        <v>15.4</v>
       </c>
       <c r="K48" t="n">
-        <v>-50.06</v>
+        <v>52.94</v>
       </c>
       <c r="L48" t="n">
-        <v>50.4</v>
+        <v>55.14</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>07:37:46</t>
+          <t>07:46:26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="F49" t="n">
-        <v>6.68</v>
+        <v>7.32</v>
       </c>
       <c r="G49" t="n">
-        <v>156.8</v>
+        <v>150.8</v>
       </c>
       <c r="H49" t="n">
-        <v>50.9</v>
+        <v>33.5</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J49" t="n">
-        <v>55.34</v>
+        <v>12.91</v>
       </c>
       <c r="K49" t="n">
-        <v>8.48</v>
+        <v>50.07</v>
       </c>
       <c r="L49" t="n">
-        <v>55.99</v>
+        <v>51.71</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>07:41:29</t>
+          <t>07:52:31</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.65</v>
+        <v>2.49</v>
       </c>
       <c r="F50" t="n">
-        <v>4.77</v>
+        <v>7.55</v>
       </c>
       <c r="G50" t="n">
-        <v>154.7</v>
+        <v>162.2</v>
       </c>
       <c r="H50" t="n">
-        <v>77.7</v>
+        <v>82.2</v>
       </c>
       <c r="I50" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-55.64</v>
+        <v>56.94</v>
       </c>
       <c r="K50" t="n">
-        <v>-19.26</v>
+        <v>-59.53</v>
       </c>
       <c r="L50" t="n">
-        <v>58.88</v>
+        <v>82.38</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>07:42:37</t>
+          <t>07:53:33</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.08</v>
+        <v>1.68</v>
       </c>
       <c r="F51" t="n">
-        <v>6.33</v>
+        <v>6.23</v>
       </c>
       <c r="G51" t="n">
-        <v>168.5</v>
+        <v>164.8</v>
       </c>
       <c r="H51" t="n">
-        <v>50.6</v>
+        <v>53.1</v>
       </c>
       <c r="I51" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J51" t="n">
-        <v>-73.36</v>
+        <v>-62.61</v>
       </c>
       <c r="K51" t="n">
-        <v>52.04</v>
+        <v>24.37</v>
       </c>
       <c r="L51" t="n">
-        <v>89.94</v>
+        <v>67.18000000000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>07:43:45</t>
+          <t>07:55:24</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="F52" t="n">
-        <v>6.87</v>
+        <v>6.91</v>
       </c>
       <c r="G52" t="n">
-        <v>162</v>
+        <v>143.1</v>
       </c>
       <c r="H52" t="n">
-        <v>92.09999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>-13.35</v>
+        <v>-11.8</v>
       </c>
       <c r="K52" t="n">
-        <v>-81.05</v>
+        <v>-70.75</v>
       </c>
       <c r="L52" t="n">
-        <v>82.14</v>
+        <v>71.72</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>07:48:33</t>
+          <t>08:01:35</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="F53" t="n">
-        <v>5.29</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>148</v>
+        <v>163.5</v>
       </c>
       <c r="H53" t="n">
-        <v>72</v>
+        <v>63.7</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J53" t="n">
-        <v>138.15</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>28.03</v>
+        <v>-52.14</v>
       </c>
       <c r="L53" t="n">
-        <v>140.97</v>
+        <v>99.75</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>07:50:51</t>
+          <t>08:03:19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="F54" t="n">
-        <v>6.36</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G54" t="n">
-        <v>163.4</v>
+        <v>143.1</v>
       </c>
       <c r="H54" t="n">
-        <v>89.59999999999999</v>
+        <v>37.1</v>
       </c>
       <c r="I54" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>48.65</v>
+        <v>124.26</v>
       </c>
       <c r="K54" t="n">
-        <v>-113.23</v>
+        <v>4.31</v>
       </c>
       <c r="L54" t="n">
-        <v>123.23</v>
+        <v>124.33</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>07:52:02</t>
+          <t>08:05:37</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.88</v>
+        <v>2.47</v>
       </c>
       <c r="F55" t="n">
-        <v>4.41</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>164.1</v>
+        <v>169.6</v>
       </c>
       <c r="H55" t="n">
-        <v>80.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>93.67</v>
+        <v>126.79</v>
       </c>
       <c r="K55" t="n">
-        <v>82.76000000000001</v>
+        <v>12.14</v>
       </c>
       <c r="L55" t="n">
-        <v>124.99</v>
+        <v>127.37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>07:56:37</t>
+          <t>08:09:01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="F56" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>172</v>
+        <v>159.3</v>
       </c>
       <c r="H56" t="n">
-        <v>33.6</v>
+        <v>70.2</v>
       </c>
       <c r="I56" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J56" t="n">
-        <v>177.3</v>
+        <v>130.56</v>
       </c>
       <c r="K56" t="n">
-        <v>-89.66</v>
+        <v>140.28</v>
       </c>
       <c r="L56" t="n">
-        <v>198.68</v>
+        <v>191.63</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>07:59:21</t>
+          <t>08:10:38</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.82</v>
+        <v>2.46</v>
       </c>
       <c r="F57" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G57" t="n">
-        <v>156.7</v>
+        <v>161.7</v>
       </c>
       <c r="H57" t="n">
-        <v>44.9</v>
+        <v>53.1</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>127.84</v>
+        <v>-172.09</v>
       </c>
       <c r="K57" t="n">
-        <v>114.58</v>
+        <v>-8.34</v>
       </c>
       <c r="L57" t="n">
-        <v>171.67</v>
+        <v>172.29</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:01:34</t>
+          <t>08:12:44</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="F58" t="n">
-        <v>8.52</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>163</v>
+        <v>169.7</v>
       </c>
       <c r="H58" t="n">
-        <v>53.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J58" t="n">
-        <v>12.27</v>
+        <v>129.18</v>
       </c>
       <c r="K58" t="n">
-        <v>-135.54</v>
+        <v>-94.58</v>
       </c>
       <c r="L58" t="n">
-        <v>136.09</v>
+        <v>160.1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:11:16</t>
+          <t>08:21:43</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.39</v>
+        <v>1.58</v>
       </c>
       <c r="F59" t="n">
-        <v>8.34</v>
+        <v>5.66</v>
       </c>
       <c r="G59" t="n">
-        <v>154.9</v>
+        <v>160</v>
       </c>
       <c r="H59" t="n">
-        <v>80.3</v>
+        <v>51</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>18.31</v>
+        <v>-32.57</v>
       </c>
       <c r="K59" t="n">
-        <v>-25.36</v>
+        <v>-1.71</v>
       </c>
       <c r="L59" t="n">
-        <v>31.28</v>
+        <v>32.62</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:13:00</t>
+          <t>08:24:05</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.95</v>
+        <v>2.33</v>
       </c>
       <c r="F60" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G60" t="n">
-        <v>161.8</v>
+        <v>160.1</v>
       </c>
       <c r="H60" t="n">
-        <v>60.3</v>
+        <v>73.5</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>38.41</v>
+        <v>2.04</v>
       </c>
       <c r="K60" t="n">
-        <v>17.94</v>
+        <v>-46.27</v>
       </c>
       <c r="L60" t="n">
-        <v>42.4</v>
+        <v>46.32</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:13:31</t>
+          <t>08:25:13</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.07</v>
+        <v>2.23</v>
       </c>
       <c r="F61" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>157.1</v>
+        <v>169.1</v>
       </c>
       <c r="H61" t="n">
-        <v>66.2</v>
+        <v>31</v>
       </c>
       <c r="I61" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="J61" t="n">
-        <v>28.58</v>
+        <v>-30.24</v>
       </c>
       <c r="K61" t="n">
-        <v>-18.82</v>
+        <v>17.28</v>
       </c>
       <c r="L61" t="n">
-        <v>34.22</v>
+        <v>34.83</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>08:19:38</t>
+          <t>08:29:36</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.21</v>
+        <v>1.57</v>
       </c>
       <c r="F62" t="n">
-        <v>8.619999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>169.7</v>
+        <v>170</v>
       </c>
       <c r="H62" t="n">
-        <v>60.1</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>-51.85</v>
+        <v>-17.03</v>
       </c>
       <c r="K62" t="n">
-        <v>7.52</v>
+        <v>-46.39</v>
       </c>
       <c r="L62" t="n">
-        <v>52.39</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>08:20:44</t>
+          <t>08:31:54</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.08</v>
+        <v>1.93</v>
       </c>
       <c r="F63" t="n">
-        <v>8.619999999999999</v>
+        <v>7.12</v>
       </c>
       <c r="G63" t="n">
-        <v>148.2</v>
+        <v>155.7</v>
       </c>
       <c r="H63" t="n">
-        <v>78.8</v>
+        <v>56.7</v>
       </c>
       <c r="I63" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>67</v>
+        <v>44.48</v>
       </c>
       <c r="K63" t="n">
-        <v>-38.99</v>
+        <v>33.06</v>
       </c>
       <c r="L63" t="n">
-        <v>77.52</v>
+        <v>55.42</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>08:23:11</t>
+          <t>08:33:44</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.73</v>
+        <v>2.17</v>
       </c>
       <c r="F64" t="n">
-        <v>6.86</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G64" t="n">
-        <v>159.9</v>
+        <v>158.8</v>
       </c>
       <c r="H64" t="n">
-        <v>46.7</v>
+        <v>64.3</v>
       </c>
       <c r="I64" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J64" t="n">
-        <v>49.38</v>
+        <v>39.26</v>
       </c>
       <c r="K64" t="n">
-        <v>-8.19</v>
+        <v>-60.64</v>
       </c>
       <c r="L64" t="n">
-        <v>50.05</v>
+        <v>72.23999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>08:27:43</t>
+          <t>08:37:45</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.94</v>
+        <v>3.16</v>
       </c>
       <c r="F65" t="n">
-        <v>6.7</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G65" t="n">
-        <v>170.3</v>
+        <v>157.2</v>
       </c>
       <c r="H65" t="n">
-        <v>36.6</v>
+        <v>37.5</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.03</v>
+        <v>24.47</v>
       </c>
       <c r="K65" t="n">
-        <v>-65.11</v>
+        <v>-82.62</v>
       </c>
       <c r="L65" t="n">
-        <v>65.14</v>
+        <v>86.17</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>08:29:21</t>
+          <t>08:39:37</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.99</v>
+        <v>1.79</v>
       </c>
       <c r="F66" t="n">
-        <v>8.619999999999999</v>
+        <v>4.11</v>
       </c>
       <c r="G66" t="n">
-        <v>164.5</v>
+        <v>160.6</v>
       </c>
       <c r="H66" t="n">
-        <v>68.09999999999999</v>
+        <v>52.4</v>
       </c>
       <c r="I66" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>60.1</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>-70.84</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>92.90000000000001</v>
+        <v>85.68000000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>08:30:32</t>
+          <t>08:41:53</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="F67" t="n">
-        <v>8.460000000000001</v>
+        <v>6.51</v>
       </c>
       <c r="G67" t="n">
-        <v>160.5</v>
+        <v>149.3</v>
       </c>
       <c r="H67" t="n">
-        <v>88.09999999999999</v>
+        <v>63.6</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J67" t="n">
-        <v>12.61</v>
+        <v>-62.26</v>
       </c>
       <c r="K67" t="n">
-        <v>-98.61</v>
+        <v>65.13</v>
       </c>
       <c r="L67" t="n">
-        <v>99.41</v>
+        <v>90.11</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>08:34:08</t>
+          <t>08:45:51</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="F68" t="n">
-        <v>3.12</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G68" t="n">
-        <v>164.4</v>
+        <v>155.7</v>
       </c>
       <c r="H68" t="n">
-        <v>48.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>-4.52</v>
+        <v>86.26000000000001</v>
       </c>
       <c r="K68" t="n">
-        <v>-119.49</v>
+        <v>150.41</v>
       </c>
       <c r="L68" t="n">
-        <v>119.57</v>
+        <v>173.39</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>08:36:06</t>
+          <t>08:46:37</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="F69" t="n">
-        <v>4.77</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G69" t="n">
-        <v>174.4</v>
+        <v>173</v>
       </c>
       <c r="H69" t="n">
-        <v>85</v>
+        <v>68.8</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J69" t="n">
-        <v>31.09</v>
+        <v>-184.24</v>
       </c>
       <c r="K69" t="n">
-        <v>154.4</v>
+        <v>-79.51000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>157.49</v>
+        <v>200.67</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>08:38:26</t>
+          <t>08:48:57</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.95</v>
+        <v>1.58</v>
       </c>
       <c r="F70" t="n">
-        <v>8.619999999999999</v>
+        <v>2.89</v>
       </c>
       <c r="G70" t="n">
-        <v>149.4</v>
+        <v>155</v>
       </c>
       <c r="H70" t="n">
-        <v>38.9</v>
+        <v>53.2</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J70" t="n">
-        <v>98.09999999999999</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>-95.63</v>
+        <v>72.47</v>
       </c>
       <c r="L70" t="n">
-        <v>137</v>
+        <v>111.29</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>08:43:16</t>
+          <t>08:53:39</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.98</v>
+        <v>1.53</v>
       </c>
       <c r="F71" t="n">
-        <v>8.31</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>154.8</v>
+        <v>157.1</v>
       </c>
       <c r="H71" t="n">
-        <v>77.40000000000001</v>
+        <v>55.9</v>
       </c>
       <c r="I71" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-159.92</v>
+        <v>36.8</v>
       </c>
       <c r="K71" t="n">
-        <v>-6.67</v>
+        <v>166.44</v>
       </c>
       <c r="L71" t="n">
-        <v>160.06</v>
+        <v>170.46</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>08:44:43</t>
+          <t>08:54:55</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="F72" t="n">
-        <v>8.619999999999999</v>
+        <v>5.25</v>
       </c>
       <c r="G72" t="n">
-        <v>161.8</v>
+        <v>174</v>
       </c>
       <c r="H72" t="n">
-        <v>63.5</v>
+        <v>58.5</v>
       </c>
       <c r="I72" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J72" t="n">
-        <v>-43.2</v>
+        <v>133.02</v>
       </c>
       <c r="K72" t="n">
-        <v>122.67</v>
+        <v>-124.82</v>
       </c>
       <c r="L72" t="n">
-        <v>130.05</v>
+        <v>182.41</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>08:46:35</t>
+          <t>08:55:32</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="F73" t="n">
-        <v>7.74</v>
+        <v>6.58</v>
       </c>
       <c r="G73" t="n">
-        <v>164.5</v>
+        <v>171.6</v>
       </c>
       <c r="H73" t="n">
-        <v>53.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J73" t="n">
-        <v>39.59</v>
+        <v>-121.09</v>
       </c>
       <c r="K73" t="n">
-        <v>-219.71</v>
+        <v>-95.77</v>
       </c>
       <c r="L73" t="n">
-        <v>223.25</v>
+        <v>154.38</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>08:59:02</t>
+          <t>09:06:10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2</v>
+        <v>2.53</v>
       </c>
       <c r="F74" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G74" t="n">
-        <v>155.5</v>
+        <v>172.2</v>
       </c>
       <c r="H74" t="n">
-        <v>32.5</v>
+        <v>100</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J74" t="n">
-        <v>22.76</v>
+        <v>-41.84</v>
       </c>
       <c r="K74" t="n">
-        <v>18.02</v>
+        <v>-6.24</v>
       </c>
       <c r="L74" t="n">
-        <v>29.03</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:00:21</t>
+          <t>09:08:07</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
       <c r="F75" t="n">
-        <v>6.95</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G75" t="n">
-        <v>158.4</v>
+        <v>147.2</v>
       </c>
       <c r="H75" t="n">
-        <v>75.5</v>
+        <v>71.3</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>13.72</v>
+        <v>22.01</v>
       </c>
       <c r="K75" t="n">
-        <v>22.15</v>
+        <v>-35.99</v>
       </c>
       <c r="L75" t="n">
-        <v>26.05</v>
+        <v>42.18</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:01:40</t>
+          <t>09:09:49</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.01</v>
+        <v>1.87</v>
       </c>
       <c r="F76" t="n">
-        <v>5.75</v>
+        <v>6.26</v>
       </c>
       <c r="G76" t="n">
-        <v>171</v>
+        <v>159.2</v>
       </c>
       <c r="H76" t="n">
-        <v>78.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="J76" t="n">
-        <v>-39.47</v>
+        <v>-15.56</v>
       </c>
       <c r="K76" t="n">
-        <v>10.18</v>
+        <v>36.5</v>
       </c>
       <c r="L76" t="n">
-        <v>40.76</v>
+        <v>39.68</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:06:02</t>
+          <t>09:14:25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="F77" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G77" t="n">
-        <v>157.4</v>
+        <v>159.2</v>
       </c>
       <c r="H77" t="n">
-        <v>80.3</v>
+        <v>81.2</v>
       </c>
       <c r="I77" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J77" t="n">
-        <v>-34.92</v>
+        <v>-52.36</v>
       </c>
       <c r="K77" t="n">
-        <v>50.86</v>
+        <v>8.82</v>
       </c>
       <c r="L77" t="n">
-        <v>61.7</v>
+        <v>53.09</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:08:05</t>
+          <t>09:15:20</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.56</v>
+        <v>2.26</v>
       </c>
       <c r="F78" t="n">
-        <v>8.619999999999999</v>
+        <v>7.37</v>
       </c>
       <c r="G78" t="n">
-        <v>161.2</v>
+        <v>171.6</v>
       </c>
       <c r="H78" t="n">
-        <v>18.6</v>
+        <v>26</v>
       </c>
       <c r="I78" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J78" t="n">
-        <v>37.97</v>
+        <v>17.23</v>
       </c>
       <c r="K78" t="n">
-        <v>14.32</v>
+        <v>35.63</v>
       </c>
       <c r="L78" t="n">
-        <v>40.58</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:09:26</t>
+          <t>09:16:25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.46</v>
+        <v>2.23</v>
       </c>
       <c r="F79" t="n">
-        <v>8.619999999999999</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="G79" t="n">
-        <v>162.5</v>
+        <v>158.8</v>
       </c>
       <c r="H79" t="n">
-        <v>45.8</v>
+        <v>46.1</v>
       </c>
       <c r="I79" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J79" t="n">
-        <v>-49.14</v>
+        <v>-23.32</v>
       </c>
       <c r="K79" t="n">
-        <v>-19.33</v>
+        <v>51.19</v>
       </c>
       <c r="L79" t="n">
-        <v>52.81</v>
+        <v>56.26</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:14:21</t>
+          <t>09:21:53</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.43</v>
+        <v>2.16</v>
       </c>
       <c r="F80" t="n">
-        <v>7.26</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>165.1</v>
+        <v>170.1</v>
       </c>
       <c r="H80" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>79.44</v>
+        <v>-36.06</v>
       </c>
       <c r="K80" t="n">
-        <v>36.62</v>
+        <v>119.61</v>
       </c>
       <c r="L80" t="n">
-        <v>87.48</v>
+        <v>124.93</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:16:33</t>
+          <t>09:24:05</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.13</v>
+        <v>2.06</v>
       </c>
       <c r="F81" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G81" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="H81" t="n">
-        <v>57.5</v>
+        <v>55</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-18.64</v>
+        <v>113.77</v>
       </c>
       <c r="K81" t="n">
-        <v>-82.98</v>
+        <v>2.56</v>
       </c>
       <c r="L81" t="n">
-        <v>85.05</v>
+        <v>113.8</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:18:05</t>
+          <t>09:25:13</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.55</v>
+        <v>2.15</v>
       </c>
       <c r="F82" t="n">
-        <v>3.78</v>
+        <v>6.64</v>
       </c>
       <c r="G82" t="n">
-        <v>163.4</v>
+        <v>162.5</v>
       </c>
       <c r="H82" t="n">
-        <v>67.90000000000001</v>
+        <v>59.7</v>
       </c>
       <c r="I82" t="n">
         <v>23</v>
       </c>
       <c r="J82" t="n">
-        <v>-10.52</v>
+        <v>-80.91</v>
       </c>
       <c r="K82" t="n">
-        <v>-66</v>
+        <v>32.09</v>
       </c>
       <c r="L82" t="n">
-        <v>66.84</v>
+        <v>87.04000000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>09:22:15</t>
+          <t>09:30:39</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>3.3</v>
+        <v>1.66</v>
       </c>
       <c r="F83" t="n">
-        <v>8.619999999999999</v>
+        <v>7.79</v>
       </c>
       <c r="G83" t="n">
-        <v>162.7</v>
+        <v>156.4</v>
       </c>
       <c r="H83" t="n">
-        <v>80.3</v>
+        <v>55</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J83" t="n">
-        <v>166.5</v>
+        <v>-165.83</v>
       </c>
       <c r="K83" t="n">
-        <v>119.35</v>
+        <v>-41.23</v>
       </c>
       <c r="L83" t="n">
-        <v>204.86</v>
+        <v>170.88</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>09:24:01</t>
+          <t>09:32:24</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.07</v>
+        <v>2.26</v>
       </c>
       <c r="F84" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G84" t="n">
-        <v>148.5</v>
+        <v>155.9</v>
       </c>
       <c r="H84" t="n">
-        <v>54.9</v>
+        <v>77.7</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="J84" t="n">
-        <v>-71.84999999999999</v>
+        <v>-2.06</v>
       </c>
       <c r="K84" t="n">
-        <v>-95.98</v>
+        <v>171.22</v>
       </c>
       <c r="L84" t="n">
-        <v>119.9</v>
+        <v>171.24</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>09:24:52</t>
+          <t>09:33:13</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3613,28 +3613,28 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G85" t="n">
-        <v>166.8</v>
+        <v>155.2</v>
       </c>
       <c r="H85" t="n">
-        <v>100</v>
+        <v>50.5</v>
       </c>
       <c r="I85" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J85" t="n">
-        <v>128.36</v>
+        <v>109.09</v>
       </c>
       <c r="K85" t="n">
-        <v>-12.42</v>
+        <v>-71.83</v>
       </c>
       <c r="L85" t="n">
-        <v>128.96</v>
+        <v>130.62</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>09:30:35</t>
+          <t>09:39:12</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.46</v>
+        <v>2.71</v>
       </c>
       <c r="F86" t="n">
-        <v>8.609999999999999</v>
+        <v>7.85</v>
       </c>
       <c r="G86" t="n">
-        <v>166.4</v>
+        <v>159</v>
       </c>
       <c r="H86" t="n">
-        <v>46.9</v>
+        <v>83.7</v>
       </c>
       <c r="I86" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>-70.48</v>
+        <v>-151.89</v>
       </c>
       <c r="K86" t="n">
-        <v>164.89</v>
+        <v>-61.47</v>
       </c>
       <c r="L86" t="n">
-        <v>179.32</v>
+        <v>163.86</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>09:32:59</t>
+          <t>09:40:08</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.27</v>
+        <v>1.9</v>
       </c>
       <c r="F87" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>172.5</v>
+        <v>159.5</v>
       </c>
       <c r="H87" t="n">
-        <v>61.5</v>
+        <v>55.4</v>
       </c>
       <c r="I87" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>58.34</v>
+        <v>200.23</v>
       </c>
       <c r="K87" t="n">
-        <v>-122.32</v>
+        <v>-11.25</v>
       </c>
       <c r="L87" t="n">
-        <v>135.52</v>
+        <v>200.54</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>09:35:10</t>
+          <t>09:41:36</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="F88" t="n">
-        <v>8.619999999999999</v>
+        <v>7.61</v>
       </c>
       <c r="G88" t="n">
-        <v>152.9</v>
+        <v>151.9</v>
       </c>
       <c r="H88" t="n">
-        <v>67.5</v>
+        <v>79.8</v>
       </c>
       <c r="I88" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="J88" t="n">
-        <v>-71.11</v>
+        <v>-180.09</v>
       </c>
       <c r="K88" t="n">
-        <v>-142.56</v>
+        <v>-77.45999999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>159.31</v>
+        <v>196.04</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-22.xlsx
+++ b/output/2025-08-22.xlsx
@@ -640,13 +640,13 @@
         <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-10.5</v>
+        <v>-11.33</v>
       </c>
       <c r="K14" t="n">
-        <v>41.6</v>
+        <v>44.87</v>
       </c>
       <c r="L14" t="n">
-        <v>42.91</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>5.85</v>
+        <v>6.59</v>
       </c>
       <c r="K15" t="n">
-        <v>-34.61</v>
+        <v>-38.98</v>
       </c>
       <c r="L15" t="n">
-        <v>35.1</v>
+        <v>39.54</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-41.39</v>
+        <v>-44.87</v>
       </c>
       <c r="K16" t="n">
-        <v>55.28</v>
+        <v>59.93</v>
       </c>
       <c r="L16" t="n">
-        <v>69.06</v>
+        <v>74.87</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>23</v>
       </c>
       <c r="J17" t="n">
-        <v>54.94</v>
+        <v>61.12</v>
       </c>
       <c r="K17" t="n">
-        <v>12.51</v>
+        <v>13.92</v>
       </c>
       <c r="L17" t="n">
-        <v>56.34</v>
+        <v>62.69</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>20</v>
       </c>
       <c r="J18" t="n">
-        <v>18.1</v>
+        <v>19.17</v>
       </c>
       <c r="K18" t="n">
-        <v>63.97</v>
+        <v>67.73</v>
       </c>
       <c r="L18" t="n">
-        <v>66.48</v>
+        <v>70.39</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>21</v>
       </c>
       <c r="J19" t="n">
-        <v>-27.29</v>
+        <v>-31.62</v>
       </c>
       <c r="K19" t="n">
-        <v>-42.76</v>
+        <v>-49.56</v>
       </c>
       <c r="L19" t="n">
-        <v>50.73</v>
+        <v>58.79</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>18</v>
       </c>
       <c r="J20" t="n">
-        <v>136.83</v>
+        <v>145.27</v>
       </c>
       <c r="K20" t="n">
-        <v>-47.58</v>
+        <v>-50.52</v>
       </c>
       <c r="L20" t="n">
-        <v>144.87</v>
+        <v>153.8</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.32</v>
+        <v>-7</v>
       </c>
       <c r="K21" t="n">
-        <v>-106.05</v>
+        <v>-117.37</v>
       </c>
       <c r="L21" t="n">
-        <v>106.24</v>
+        <v>117.58</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>20</v>
       </c>
       <c r="J22" t="n">
-        <v>19.15</v>
+        <v>23.47</v>
       </c>
       <c r="K22" t="n">
-        <v>67.23999999999999</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>69.91</v>
+        <v>85.70999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>18</v>
       </c>
       <c r="J23" t="n">
-        <v>3.62</v>
+        <v>4.33</v>
       </c>
       <c r="K23" t="n">
-        <v>-136.44</v>
+        <v>-163.46</v>
       </c>
       <c r="L23" t="n">
-        <v>136.49</v>
+        <v>163.52</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-119.11</v>
+        <v>-138.54</v>
       </c>
       <c r="K24" t="n">
-        <v>57.47</v>
+        <v>66.84</v>
       </c>
       <c r="L24" t="n">
-        <v>132.25</v>
+        <v>153.82</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>13.61</v>
+        <v>16.42</v>
       </c>
       <c r="K25" t="n">
-        <v>111.36</v>
+        <v>134.37</v>
       </c>
       <c r="L25" t="n">
-        <v>112.18</v>
+        <v>135.37</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>57.25</v>
+        <v>73.54000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>154.83</v>
+        <v>198.89</v>
       </c>
       <c r="L26" t="n">
-        <v>165.08</v>
+        <v>212.05</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>20</v>
       </c>
       <c r="J27" t="n">
-        <v>267.02</v>
+        <v>299.1</v>
       </c>
       <c r="K27" t="n">
-        <v>125.31</v>
+        <v>140.37</v>
       </c>
       <c r="L27" t="n">
-        <v>294.96</v>
+        <v>330.4</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>79.64</v>
+        <v>99.23</v>
       </c>
       <c r="K28" t="n">
-        <v>152.94</v>
+        <v>190.56</v>
       </c>
       <c r="L28" t="n">
-        <v>172.43</v>
+        <v>214.85</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-8.949999999999999</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>-44.26</v>
+        <v>-47.93</v>
       </c>
       <c r="L29" t="n">
-        <v>45.16</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-15.33</v>
+        <v>-16.19</v>
       </c>
       <c r="K30" t="n">
-        <v>51.37</v>
+        <v>54.27</v>
       </c>
       <c r="L30" t="n">
-        <v>53.61</v>
+        <v>56.64</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>21</v>
       </c>
       <c r="J31" t="n">
-        <v>-25.94</v>
+        <v>-27.9</v>
       </c>
       <c r="K31" t="n">
-        <v>-41.37</v>
+        <v>-44.5</v>
       </c>
       <c r="L31" t="n">
-        <v>48.83</v>
+        <v>52.52</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>15.41</v>
+        <v>16.92</v>
       </c>
       <c r="K32" t="n">
-        <v>75.75</v>
+        <v>83.17</v>
       </c>
       <c r="L32" t="n">
-        <v>77.3</v>
+        <v>84.87</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>46.65</v>
+        <v>53.99</v>
       </c>
       <c r="K33" t="n">
-        <v>-21.45</v>
+        <v>-24.82</v>
       </c>
       <c r="L33" t="n">
-        <v>51.34</v>
+        <v>59.42</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>-42.71</v>
+        <v>-51.79</v>
       </c>
       <c r="K34" t="n">
-        <v>16.32</v>
+        <v>19.79</v>
       </c>
       <c r="L34" t="n">
-        <v>45.72</v>
+        <v>55.44</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>63.34</v>
+        <v>74.78</v>
       </c>
       <c r="K35" t="n">
-        <v>59.52</v>
+        <v>70.27</v>
       </c>
       <c r="L35" t="n">
-        <v>86.92</v>
+        <v>102.62</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>18</v>
       </c>
       <c r="J36" t="n">
-        <v>95.39</v>
+        <v>112.71</v>
       </c>
       <c r="K36" t="n">
-        <v>-45.94</v>
+        <v>-54.29</v>
       </c>
       <c r="L36" t="n">
-        <v>105.88</v>
+        <v>125.1</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>18</v>
       </c>
       <c r="J37" t="n">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="K37" t="n">
-        <v>0.64</v>
+        <v>0.76</v>
       </c>
       <c r="L37" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-122.8</v>
+        <v>-143.84</v>
       </c>
       <c r="K38" t="n">
-        <v>51.19</v>
+        <v>59.97</v>
       </c>
       <c r="L38" t="n">
-        <v>133.04</v>
+        <v>155.84</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>-171.82</v>
+        <v>-189.12</v>
       </c>
       <c r="K39" t="n">
-        <v>-52.2</v>
+        <v>-57.45</v>
       </c>
       <c r="L39" t="n">
-        <v>179.57</v>
+        <v>197.65</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>74.77</v>
+        <v>93.59</v>
       </c>
       <c r="K40" t="n">
-        <v>70.62</v>
+        <v>88.39</v>
       </c>
       <c r="L40" t="n">
-        <v>102.85</v>
+        <v>128.73</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-128.46</v>
+        <v>-153.34</v>
       </c>
       <c r="K41" t="n">
-        <v>216.31</v>
+        <v>258.22</v>
       </c>
       <c r="L41" t="n">
-        <v>251.58</v>
+        <v>300.32</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>20</v>
       </c>
       <c r="J42" t="n">
-        <v>-209.89</v>
+        <v>-263.1</v>
       </c>
       <c r="K42" t="n">
-        <v>2.19</v>
+        <v>2.74</v>
       </c>
       <c r="L42" t="n">
-        <v>209.9</v>
+        <v>263.11</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>159.81</v>
+        <v>207.91</v>
       </c>
       <c r="K43" t="n">
-        <v>44.01</v>
+        <v>57.26</v>
       </c>
       <c r="L43" t="n">
-        <v>165.76</v>
+        <v>215.65</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-18.88</v>
+        <v>-21.22</v>
       </c>
       <c r="K44" t="n">
-        <v>61.57</v>
+        <v>69.19</v>
       </c>
       <c r="L44" t="n">
-        <v>64.40000000000001</v>
+        <v>72.37</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>18</v>
       </c>
       <c r="J45" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="K45" t="n">
-        <v>46.83</v>
+        <v>52.79</v>
       </c>
       <c r="L45" t="n">
-        <v>46.84</v>
+        <v>52.79</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>30.58</v>
+        <v>31.33</v>
       </c>
       <c r="K46" t="n">
-        <v>-56.98</v>
+        <v>-58.37</v>
       </c>
       <c r="L46" t="n">
-        <v>64.67</v>
+        <v>66.25</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>31.52</v>
+        <v>33.12</v>
       </c>
       <c r="K47" t="n">
-        <v>68.67</v>
+        <v>72.16</v>
       </c>
       <c r="L47" t="n">
-        <v>75.56</v>
+        <v>79.40000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>22</v>
       </c>
       <c r="J48" t="n">
-        <v>37.31</v>
+        <v>44.48</v>
       </c>
       <c r="K48" t="n">
-        <v>32.03</v>
+        <v>38.19</v>
       </c>
       <c r="L48" t="n">
-        <v>49.17</v>
+        <v>58.63</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-72.01000000000001</v>
+        <v>-76.09</v>
       </c>
       <c r="K49" t="n">
-        <v>-86.16</v>
+        <v>-91.04000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>112.29</v>
+        <v>118.65</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-29.82</v>
+        <v>-32.14</v>
       </c>
       <c r="K50" t="n">
-        <v>111.33</v>
+        <v>120</v>
       </c>
       <c r="L50" t="n">
-        <v>115.25</v>
+        <v>124.23</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>24</v>
       </c>
       <c r="J51" t="n">
-        <v>-104.42</v>
+        <v>-115.7</v>
       </c>
       <c r="K51" t="n">
-        <v>-43.57</v>
+        <v>-48.28</v>
       </c>
       <c r="L51" t="n">
-        <v>113.14</v>
+        <v>125.37</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-89.79000000000001</v>
+        <v>-103.2</v>
       </c>
       <c r="K52" t="n">
-        <v>-17.17</v>
+        <v>-19.73</v>
       </c>
       <c r="L52" t="n">
-        <v>91.42</v>
+        <v>105.07</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>24</v>
       </c>
       <c r="J53" t="n">
-        <v>147.46</v>
+        <v>167.18</v>
       </c>
       <c r="K53" t="n">
-        <v>-17.48</v>
+        <v>-19.82</v>
       </c>
       <c r="L53" t="n">
-        <v>148.5</v>
+        <v>168.35</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>20</v>
       </c>
       <c r="J54" t="n">
-        <v>-86.54000000000001</v>
+        <v>-103.58</v>
       </c>
       <c r="K54" t="n">
-        <v>105.73</v>
+        <v>126.55</v>
       </c>
       <c r="L54" t="n">
-        <v>136.64</v>
+        <v>163.54</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>56.18</v>
+        <v>68.3</v>
       </c>
       <c r="K55" t="n">
-        <v>-108.06</v>
+        <v>-131.37</v>
       </c>
       <c r="L55" t="n">
-        <v>121.79</v>
+        <v>148.06</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>110.59</v>
+        <v>153.28</v>
       </c>
       <c r="K56" t="n">
-        <v>-28.55</v>
+        <v>-39.57</v>
       </c>
       <c r="L56" t="n">
-        <v>114.22</v>
+        <v>158.31</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>20</v>
       </c>
       <c r="J57" t="n">
-        <v>107.35</v>
+        <v>131.44</v>
       </c>
       <c r="K57" t="n">
-        <v>-171.08</v>
+        <v>-209.49</v>
       </c>
       <c r="L57" t="n">
-        <v>201.97</v>
+        <v>247.31</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>140.17</v>
+        <v>176.54</v>
       </c>
       <c r="K58" t="n">
-        <v>-95.84</v>
+        <v>-120.71</v>
       </c>
       <c r="L58" t="n">
-        <v>169.8</v>
+        <v>213.86</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>21</v>
       </c>
       <c r="J59" t="n">
-        <v>4.4</v>
+        <v>4.95</v>
       </c>
       <c r="K59" t="n">
-        <v>-46.53</v>
+        <v>-52.31</v>
       </c>
       <c r="L59" t="n">
-        <v>46.74</v>
+        <v>52.54</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>-5.37</v>
+        <v>-5.57</v>
       </c>
       <c r="K60" t="n">
-        <v>-53.82</v>
+        <v>-55.73</v>
       </c>
       <c r="L60" t="n">
-        <v>54.09</v>
+        <v>56.01</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>19</v>
       </c>
       <c r="J61" t="n">
-        <v>23.94</v>
+        <v>27.27</v>
       </c>
       <c r="K61" t="n">
-        <v>32.04</v>
+        <v>36.49</v>
       </c>
       <c r="L61" t="n">
-        <v>40</v>
+        <v>45.56</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>18</v>
       </c>
       <c r="J62" t="n">
-        <v>-64.08</v>
+        <v>-70.31999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>33.54</v>
+        <v>36.8</v>
       </c>
       <c r="L62" t="n">
-        <v>72.33</v>
+        <v>79.36</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>-44.85</v>
+        <v>-51.05</v>
       </c>
       <c r="K63" t="n">
-        <v>33.25</v>
+        <v>37.85</v>
       </c>
       <c r="L63" t="n">
-        <v>55.83</v>
+        <v>63.55</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>-46.51</v>
+        <v>-51.63</v>
       </c>
       <c r="K64" t="n">
-        <v>47.81</v>
+        <v>53.07</v>
       </c>
       <c r="L64" t="n">
-        <v>66.7</v>
+        <v>74.05</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>85.02</v>
+        <v>99.69</v>
       </c>
       <c r="K65" t="n">
-        <v>30.68</v>
+        <v>35.98</v>
       </c>
       <c r="L65" t="n">
-        <v>90.38</v>
+        <v>105.99</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>126.29</v>
+        <v>133.78</v>
       </c>
       <c r="K66" t="n">
-        <v>27.19</v>
+        <v>28.8</v>
       </c>
       <c r="L66" t="n">
-        <v>129.18</v>
+        <v>136.85</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>18</v>
       </c>
       <c r="J67" t="n">
-        <v>-27.84</v>
+        <v>-31.76</v>
       </c>
       <c r="K67" t="n">
-        <v>107.03</v>
+        <v>122.14</v>
       </c>
       <c r="L67" t="n">
-        <v>110.59</v>
+        <v>126.2</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-81.73999999999999</v>
+        <v>-97.87</v>
       </c>
       <c r="K68" t="n">
-        <v>-81.37</v>
+        <v>-97.42</v>
       </c>
       <c r="L68" t="n">
-        <v>115.34</v>
+        <v>138.1</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>72.78</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>-73.05</v>
+        <v>-92.61</v>
       </c>
       <c r="L69" t="n">
-        <v>103.12</v>
+        <v>130.72</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-15.85</v>
+        <v>-18.5</v>
       </c>
       <c r="K70" t="n">
-        <v>-136.01</v>
+        <v>-158.81</v>
       </c>
       <c r="L70" t="n">
-        <v>136.93</v>
+        <v>159.88</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-90.7</v>
+        <v>-112.72</v>
       </c>
       <c r="K71" t="n">
-        <v>-151.64</v>
+        <v>-188.46</v>
       </c>
       <c r="L71" t="n">
-        <v>176.7</v>
+        <v>219.6</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>19</v>
       </c>
       <c r="J72" t="n">
-        <v>111.02</v>
+        <v>148.06</v>
       </c>
       <c r="K72" t="n">
-        <v>-111.1</v>
+        <v>-148.17</v>
       </c>
       <c r="L72" t="n">
-        <v>157.06</v>
+        <v>209.46</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>128.73</v>
+        <v>167.07</v>
       </c>
       <c r="K73" t="n">
-        <v>-41.99</v>
+        <v>-54.5</v>
       </c>
       <c r="L73" t="n">
-        <v>135.41</v>
+        <v>175.73</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>-37.01</v>
+        <v>-41.15</v>
       </c>
       <c r="K74" t="n">
-        <v>-19.88</v>
+        <v>-22.1</v>
       </c>
       <c r="L74" t="n">
-        <v>42.01</v>
+        <v>46.71</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>20</v>
       </c>
       <c r="J75" t="n">
-        <v>-51.49</v>
+        <v>-55.22</v>
       </c>
       <c r="K75" t="n">
-        <v>5.89</v>
+        <v>6.31</v>
       </c>
       <c r="L75" t="n">
-        <v>51.83</v>
+        <v>55.58</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>19</v>
       </c>
       <c r="J76" t="n">
-        <v>50.11</v>
+        <v>54.51</v>
       </c>
       <c r="K76" t="n">
-        <v>-12.35</v>
+        <v>-13.44</v>
       </c>
       <c r="L76" t="n">
-        <v>51.6</v>
+        <v>56.15</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-27.95</v>
+        <v>-29.86</v>
       </c>
       <c r="K77" t="n">
-        <v>-64.73</v>
+        <v>-69.17</v>
       </c>
       <c r="L77" t="n">
-        <v>70.51000000000001</v>
+        <v>75.34</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>18</v>
       </c>
       <c r="J78" t="n">
-        <v>43.85</v>
+        <v>44.83</v>
       </c>
       <c r="K78" t="n">
-        <v>94.95</v>
+        <v>97.06</v>
       </c>
       <c r="L78" t="n">
-        <v>104.58</v>
+        <v>106.91</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>22</v>
       </c>
       <c r="J79" t="n">
-        <v>-41.59</v>
+        <v>-46.17</v>
       </c>
       <c r="K79" t="n">
-        <v>54.45</v>
+        <v>60.44</v>
       </c>
       <c r="L79" t="n">
-        <v>68.52</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>24</v>
       </c>
       <c r="J80" t="n">
-        <v>49.88</v>
+        <v>58.72</v>
       </c>
       <c r="K80" t="n">
-        <v>-69.93000000000001</v>
+        <v>-82.33</v>
       </c>
       <c r="L80" t="n">
-        <v>85.90000000000001</v>
+        <v>101.12</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>19</v>
       </c>
       <c r="J81" t="n">
-        <v>-37.45</v>
+        <v>-45.32</v>
       </c>
       <c r="K81" t="n">
-        <v>-80.72</v>
+        <v>-97.68000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>88.98</v>
+        <v>107.68</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>24</v>
       </c>
       <c r="J82" t="n">
-        <v>-101.47</v>
+        <v>-114.94</v>
       </c>
       <c r="K82" t="n">
-        <v>-10.44</v>
+        <v>-11.83</v>
       </c>
       <c r="L82" t="n">
-        <v>102.01</v>
+        <v>115.54</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>126.75</v>
+        <v>151.88</v>
       </c>
       <c r="K83" t="n">
-        <v>40.38</v>
+        <v>48.39</v>
       </c>
       <c r="L83" t="n">
-        <v>133.03</v>
+        <v>159.41</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>79.09999999999999</v>
+        <v>92.38</v>
       </c>
       <c r="K84" t="n">
-        <v>109.52</v>
+        <v>127.91</v>
       </c>
       <c r="L84" t="n">
-        <v>135.09</v>
+        <v>157.78</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>-88.06</v>
+        <v>-115.43</v>
       </c>
       <c r="K85" t="n">
-        <v>-59.88</v>
+        <v>-78.48999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>106.49</v>
+        <v>139.58</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>20</v>
       </c>
       <c r="J86" t="n">
-        <v>200.51</v>
+        <v>242.65</v>
       </c>
       <c r="K86" t="n">
-        <v>71.52</v>
+        <v>86.55</v>
       </c>
       <c r="L86" t="n">
-        <v>212.88</v>
+        <v>257.62</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>44.27</v>
+        <v>56.41</v>
       </c>
       <c r="K87" t="n">
-        <v>-160.61</v>
+        <v>-204.69</v>
       </c>
       <c r="L87" t="n">
-        <v>166.6</v>
+        <v>212.32</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>107.78</v>
+        <v>139.58</v>
       </c>
       <c r="K88" t="n">
-        <v>-108.06</v>
+        <v>-139.94</v>
       </c>
       <c r="L88" t="n">
-        <v>152.63</v>
+        <v>197.65</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-08-22.xlsx
+++ b/output/2025-08-22.xlsx
@@ -724,13 +724,13 @@
         <v>23</v>
       </c>
       <c r="J16" t="n">
-        <v>-44.87</v>
+        <v>-45.01</v>
       </c>
       <c r="K16" t="n">
-        <v>59.93</v>
+        <v>60.11</v>
       </c>
       <c r="L16" t="n">
-        <v>74.87</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="17">
